--- a/docs/fastapi_r.xlsx
+++ b/docs/fastapi_r.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olegsemenov/Programming/python-learning/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433BB84F-F7DE-0E4E-AF4A-DDAB0F835AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B8F538-A7FE-8447-95B3-2DA1D84F0E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12260" yWindow="0" windowWidth="16540" windowHeight="18000" xr2:uid="{DB6DF64F-D978-E741-A4F2-3D28923A7931}"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
     <sheet name="Theory" sheetId="3" r:id="rId2"/>
-    <sheet name="Uvicorn" sheetId="6" r:id="rId3"/>
-    <sheet name="SQLAlchemy" sheetId="7" r:id="rId4"/>
-    <sheet name="DI" sheetId="8" r:id="rId5"/>
-    <sheet name="Alembic" sheetId="4" r:id="rId6"/>
-    <sheet name="Источники" sheetId="5" r:id="rId7"/>
-    <sheet name="Sheet" sheetId="9" r:id="rId8"/>
+    <sheet name="Status code" sheetId="10" r:id="rId3"/>
+    <sheet name="Uvicorn" sheetId="6" r:id="rId4"/>
+    <sheet name="SQLAlchemy" sheetId="7" r:id="rId5"/>
+    <sheet name="DI" sheetId="8" r:id="rId6"/>
+    <sheet name="Alembic" sheetId="4" r:id="rId7"/>
+    <sheet name="Источники" sheetId="5" r:id="rId8"/>
+    <sheet name="Sheet" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -47,7 +48,7 @@
     <author>Microsoft Office User</author>
   </authors>
   <commentList>
-    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{539AC657-4917-474F-936B-BDEA1F644E29}">
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{BCA8DD77-9560-314F-8E4F-BD3E965F3139}">
       <text>
         <r>
           <rPr>
@@ -57,6 +58,147 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
+          <t xml:space="preserve">В повседневной разработке чаще всего используем:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>get/post/put/delete,</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">include_router, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">on_event, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">add_middleware, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>exception_handler,</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>openapi.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{539AC657-4917-474F-936B-BDEA1F644E29}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t xml:space="preserve">Все они — </t>
         </r>
         <r>
@@ -89,6 +231,1504 @@
             <scheme val="minor"/>
           </rPr>
           <t>add_api_route.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0" shapeId="0" xr:uid="{52272BEA-EF55-1F42-A915-6124A59280F6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>🧠</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Применение на практике
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Если тебе нужно </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>простой ответ с контролем заголовков, куки или типа контента</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">, используй </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Response.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Если хочешь вернуть </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>JSON</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">используй </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">JSONResponse </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">или просто </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">return {"key": "value"} — FastAPI </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">сам создаст </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>JSON-</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>ответ.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D38" authorId="0" shapeId="0" xr:uid="{6517C201-1D9F-604C-BB43-58D412DE9651}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">"application/json"
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">"text/html"
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">"text/plain"
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>"application/octet-stream"</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0" shapeId="0" xr:uid="{3F9C09F8-6073-9042-BC4B-3EB85A669FF0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Когда использовать:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Когда нужен </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>ручной контроль ответа</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> (тип контента, заголовки, файлы, потоковая передача).</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Если нужно </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">вернуть не </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>JSON</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">или настроить </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">status_code, headers </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>вручную.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D45" authorId="0" shapeId="0" xr:uid="{529E9708-50AC-6C4D-802E-FB35FCABDD60}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Response</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> — </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">базовый ответ (используется для кастомных типов, бинарных данных и т. д.)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>JSONResponse</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> — </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">возвращает </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>JSON-</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">данные
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>HTMLResponse</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> — </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">возвращает </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>HTML-</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">страницы
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>PlainTextResponse</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> — </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">возвращает обычный текст
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>FileResponse</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> — </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">отправляет файл
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>RedirectResponse</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> — </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">перенаправляет на другой </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">URL
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>StreamingResponse</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> — </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>потоковая передача данных (например, больших файлов)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G46" authorId="0" shapeId="0" xr:uid="{57DF489B-7F6A-C247-8161-6B5F41C4A2A8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Класс</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">	</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Автосериализация </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>JSON</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">	</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Content-Type</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Когда использовать</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Response</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">	</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>❌</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">нет		Нет, надо самому	Текст, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">HTML, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">файлы, кастомные данные
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>JSONResponse</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>✅</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">есть		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>application/json</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		Возврат </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">JSON </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">вручную, кастомные </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">JSON </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ответы
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>/json</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> → </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">возвращает </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">JSON, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">заголовок </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Content-Type: application/json.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>/text</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> → </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">возвращает обычный текст, заголовок </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Content-Type: text/plain.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>/html</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> → </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">возвращает </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">HTML, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">заголовок </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Content-Type: text/html.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Если возвращаешь </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>словарь или список</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> → лучше </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">JSONResponse </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">или просто </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">dict (FastAPI </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">сам конвертирует).
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Если возвращаешь </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">строку или </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>HTML</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> → Response </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">с указанием </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">media_type.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B65" authorId="0" shapeId="0" xr:uid="{675AD5D9-5A3C-5142-B786-623C00472942}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Для обычного использования </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">FastAPI </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>основная и почти единственная нужная вещь</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> — это </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">jsonable_encoder. </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Остальные элементы (</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ENCODERS_BY_TYPE, decimal_encoder, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">типы </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Pydantic) </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">используются в </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>особых случаях</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>, когда ты кастомизируешь сериализацию или работаешь с нетиповыми объектами.</t>
         </r>
       </text>
     </comment>
@@ -844,7 +2484,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="552">
   <si>
     <t>Термин</t>
   </si>
@@ -880,6 +2520,15 @@
   </si>
   <si>
     <t>FastAPI</t>
+  </si>
+  <si>
+    <t>from fastapi import FastAPI</t>
+  </si>
+  <si>
+    <t>Современный, быстрый (high-performance) веб-фреймворк для создания API на Python с поддержкой async/await.</t>
+  </si>
+  <si>
+    <t>Основан на Starlette (для web-части) и Pydantic (для валидации данных).</t>
   </si>
   <si>
     <t>from typing import Union
@@ -1578,49 +3227,25 @@
     <t>Основные методы (наиболее часто используемые)</t>
   </si>
   <si>
-    <t>get(path)</t>
-  </si>
-  <si>
     <t>Регистрирует обработчик GET-запроса.</t>
   </si>
   <si>
     <t>@app.get("/items")</t>
   </si>
   <si>
-    <t>post(path)</t>
-  </si>
-  <si>
     <t>Регистрирует обработчик POST-запроса.</t>
   </si>
   <si>
     <t>@app.post("/items")</t>
   </si>
   <si>
-    <t>put(path)</t>
-  </si>
-  <si>
     <t>Обновление ресурса (PUT).</t>
   </si>
   <si>
-    <t>@app.put("/items/{id}")</t>
-  </si>
-  <si>
-    <t>delete(path)</t>
-  </si>
-  <si>
     <t>Удаление ресурса (DELETE).</t>
   </si>
   <si>
-    <t>@app.delete("/items/{id}")</t>
-  </si>
-  <si>
-    <t>patch(path)</t>
-  </si>
-  <si>
     <t>Частичное обновление (PATCH).</t>
-  </si>
-  <si>
-    <t>@app.patch("/items/{id}")</t>
   </si>
   <si>
     <t>Реже используемые HTTP-методы.</t>
@@ -1847,10 +3472,6 @@
 	•	формируется документация OpenAPI.</t>
   </si>
   <si>
-    <t xml:space="preserve">from fastapi import FastAPI
-</t>
-  </si>
-  <si>
     <t>Наследует возможности Starlette, поддерживает синхронные и асинхронные обработчики. Предоставляет методы: get, post, include_router, add_middleware, on_event, exception_handler, websocket, mount, openapi.</t>
   </si>
   <si>
@@ -1866,12 +3487,1241 @@
 def handle_http_error(request, exc):
     return {"error": exc.detail}</t>
   </si>
+  <si>
+    <t>app = FastAPI()</t>
+  </si>
+  <si>
+    <t>Uvicorn</t>
+  </si>
+  <si>
+    <t>ASGI-сервер, на котором запускается FastAPI-приложение.</t>
+  </si>
+  <si>
+    <t>Используется как middleware между приложением и сетью.</t>
+  </si>
+  <si>
+    <t>Запуск: uvicorn main:app --reload</t>
+  </si>
+  <si>
+    <t>ASGI</t>
+  </si>
+  <si>
+    <t>Асинхронный стандарт интерфейса между сервером и приложением (Asynchronous Server Gateway Interface).</t>
+  </si>
+  <si>
+    <t>Замена WSGI для асинхронных Python-фреймворков (FastAPI, Starlette).</t>
+  </si>
+  <si>
+    <t>Маршрут (Route)</t>
+  </si>
+  <si>
+    <t>@app.get("/path")</t>
+  </si>
+  <si>
+    <t>Путь (endpoint), по которому клиент обращается к API.</t>
+  </si>
+  <si>
+    <t>Каждый маршрут связан с HTTP-методом (GET, POST, PUT, DELETE и т.д.)</t>
+  </si>
+  <si>
+    <t>Эндпоинт (Endpoint)</t>
+  </si>
+  <si>
+    <t>def read_items(): ...</t>
+  </si>
+  <si>
+    <t>Функция-обработчик, вызываемая при обращении к маршруту.</t>
+  </si>
+  <si>
+    <t>Возвращает ответ клиенту (JSON, HTML, текст и т.д.).</t>
+  </si>
+  <si>
+    <t>HTTP-методы</t>
+  </si>
+  <si>
+    <t>@app.post, @app.get, @app.put, @app.delete</t>
+  </si>
+  <si>
+    <t>Определяют тип операции над ресурсом (чтение, создание, обновление, удаление).</t>
+  </si>
+  <si>
+    <t>CRUD = Create, Read, Update, Delete.</t>
+  </si>
+  <si>
+    <t>Путь (Path)</t>
+  </si>
+  <si>
+    <t>"/users/{user_id}"</t>
+  </si>
+  <si>
+    <t>Параметр, включённый в URL, используется для получения данных из запроса.</t>
+  </si>
+  <si>
+    <t>Объявляется в маршруте и как аргумент функции.</t>
+  </si>
+  <si>
+    <t>@app.get("/users/{user_id}")</t>
+  </si>
+  <si>
+    <t>Параметр запроса (Query)</t>
+  </si>
+  <si>
+    <t>def get_items(skip: int = 0, limit: int = 10)</t>
+  </si>
+  <si>
+    <t>Аргументы, передаваемые в URL после знака ?.</t>
+  </si>
+  <si>
+    <t>Используются для фильтрации, пагинации и т.д.</t>
+  </si>
+  <si>
+    <t>/items?skip=0&amp;limit=10</t>
+  </si>
+  <si>
+    <t>Pydantic-модель</t>
+  </si>
+  <si>
+    <t>from pydantic import BaseModel</t>
+  </si>
+  <si>
+    <t>Класс, описывающий структуру и типы данных запроса или ответа.</t>
+  </si>
+  <si>
+    <t>Автоматически валидирует данные.</t>
+  </si>
+  <si>
+    <t>Body (тело запроса)</t>
+  </si>
+  <si>
+    <t>def create_item(item: Item)</t>
+  </si>
+  <si>
+    <t>JSON-данные, передаваемые в теле POST/PUT-запроса.</t>
+  </si>
+  <si>
+    <t>FastAPI автоматически парсит и валидирует их.</t>
+  </si>
+  <si>
+    <t>Регистрирует обработчик HTTP GET-запроса по указанному маршруту.</t>
+  </si>
+  <si>
+    <t>from fastapi import FastAPI
+app = FastAPI()
+@app.get("/items/{item_id}")
+def read_item(item_id: int, q: str = None):
+    return {"item_id": item_id, "q": q}</t>
+  </si>
+  <si>
+    <t>@app.post("/items")
+def create_item(item: dict):
+    return {"message": "Item created", "item": item}</t>
+  </si>
+  <si>
+    <t>@app.put("/items/{id}")
+def update_item(id: int, item: dict):
+    return {"message": f"Item {id} updated", "item": item}</t>
+  </si>
+  <si>
+    <t>@app.delete("/items/{id}")
+def delete_item(id: int):
+    return {"message": f"Item {id} deleted"}</t>
+  </si>
+  <si>
+    <t>@app.patch("/items/{id}")
+def patch_item(id: int, item: dict):
+    return {"message": f"Item {id} partially updated", "item": item}</t>
+  </si>
+  <si>
+    <t>@app.post(path)</t>
+  </si>
+  <si>
+    <t>@app.delett(path/{item_id})</t>
+  </si>
+  <si>
+    <t>@app.get(path)</t>
+  </si>
+  <si>
+    <t>@app.get(path/{item_id})</t>
+  </si>
+  <si>
+    <t>@app.patcht(path/{item_id})</t>
+  </si>
+  <si>
+    <t>@app.put(path/{item_id})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pip install fastapi
+</t>
+  </si>
+  <si>
+    <t>pip install fastapi</t>
+  </si>
+  <si>
+    <t>Устанавливает только сам FastAPI — минимальный набор, чтобы можно было писать код с FastAPI.</t>
+  </si>
+  <si>
+    <t>Не устанавливает сервер ASGI, Pydantic extras и другие полезные пакеты.</t>
+  </si>
+  <si>
+    <t>Пример: после pip install fastapi вы не сможете сразу запустить fastapi CLI или команду uvicorn app:app --reload без установки ASGI сервера (например, uvicorn).</t>
+  </si>
+  <si>
+    <t>pip install "fastapi[standard]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Устанавливает FastAPI + набор стандартных дополнительных зависимостей, необходимых для полноценной работы:
+	•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pydantic</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (если нужно)
+	•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>email-validator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (для валидации email)
+	•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>jinja2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (для шаблонов, если используете HTMLResponse)
+	•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>python-multipart</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (для загрузки файлов)
+	•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>requests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> и другие мелкие утилиты
+	•	</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>uvicorn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> или uvicorn[standard] (ASGI сервер для запуска приложения)</t>
+    </r>
+  </si>
+  <si>
+    <t>После этого можно сразу использовать команду:
+fastapi run app:app --reload
+или запускать через 
+uvicorn app:app --reload без проблем.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	•	pip install fastapi → минимальная установка, только библиотека.
+	•	pip install "fastapi[standard]" → установка для полноценной разработки и запуска FastAPI приложений сразу.</t>
+  </si>
+  <si>
+    <t>@app.post("/items/") 
+def create_item(item: Item): 
+      return item</t>
+  </si>
+  <si>
+    <t>class Item(BaseModel): 
+    name: str; 
+    price: float</t>
+  </si>
+  <si>
+    <t>def read_items(): 
+     return {"item": "apple"}</t>
+  </si>
+  <si>
+    <t>Response</t>
+  </si>
+  <si>
+    <t>from fastapi import FastAPI, Response
+app = FastAPI()
+@app.get("/text")
+def get_text():    
+    return Response(
+ content="Plain text response",  media_type="text/plain")
+@app.get("/custom")
+def custom_response():
+   return Response(
+  content="Custom headers",     
+  media_type="text/plain", 
+  headers={"X-Custom": "value"},  
+  status_code=202
+)</t>
+  </si>
+  <si>
+    <t>Response(
+content=None, 
+status_code=200, 
+headers=None, 
+media_type=None, 
+background=None
+)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">По умолчанию FastAPI возвращает JSON, если вернуть dict или Pydantic-модель.- Response можно использовать для отправки текста, HTML, байтов, файлов.- Можно задавать status_code, headers, media_type.- Есть наследники: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>JSONResponse</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HTMLResponse</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FileResponse</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>StreamingResponse</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Response — это HTTP-ответ, который FastAPI (через Starlette) отправляет клиенту.
+Ты можешь вручную настроить:
+	•	тело (content)
+	•	заголовки (headers)
+	•	тип контента (media_type)
+	•	код ответа (status_code)
+	•	куки (set_cookie, delete_cookie)</t>
+  </si>
+  <si>
+    <t>Важные атрибуты и методы</t>
+  </si>
+  <si>
+    <t>media_type</t>
+  </si>
+  <si>
+    <t>MIME-тип контента (например "text/plain", "application/json").</t>
+  </si>
+  <si>
+    <t>Response(media_type="text/html")</t>
+  </si>
+  <si>
+    <t>charset</t>
+  </si>
+  <si>
+    <t>Кодировка текста (по умолчанию "utf-8").</t>
+  </si>
+  <si>
+    <t>headers</t>
+  </si>
+  <si>
+    <t>dict</t>
+  </si>
+  <si>
+    <t>Содержит заголовки ответа.</t>
+  </si>
+  <si>
+    <t>response.headers["X-Custom"] = "Value"</t>
+  </si>
+  <si>
+    <t>init_headers()</t>
+  </si>
+  <si>
+    <t>метод</t>
+  </si>
+  <si>
+    <t>Инициализация заголовков (внутренний метод Starlette).</t>
+  </si>
+  <si>
+    <t>render(content)</t>
+  </si>
+  <si>
+    <t>Преобразует данные в байты для отправки клиенту.</t>
+  </si>
+  <si>
+    <t>Переопределяется в дочерних классах (JSONResponse).</t>
+  </si>
+  <si>
+    <t>set_cookie(key, value, ...)</t>
+  </si>
+  <si>
+    <t>Устанавливает cookie в ответе.</t>
+  </si>
+  <si>
+    <t>response.set_cookie(key="session_id", value="123")</t>
+  </si>
+  <si>
+    <t>delete_cookie(key)</t>
+  </si>
+  <si>
+    <t>Удаляет cookie у клиента.</t>
+  </si>
+  <si>
+    <t>response.delete_cookie(key="session_id")</t>
+  </si>
+  <si>
+    <t>from fastapi import FastAPI, Response
+app = FastAPI()
+@app.get("/demo")
+def demo():
+    response = Response(content="Cookie set!", media_type="text/plain")
+    response.set_cookie(key="session_id", value="xyz123", max_age=3600)
+    response.headers["X-Example"] = "HeaderValue"
+    return response</t>
+  </si>
+  <si>
+    <t>from fastapi.responses import Response, JSONResponse, HTMLResponse, FileResponse, RedirectResponse</t>
+  </si>
+  <si>
+    <t>Модуль fastapi.responses — содержит классы для формирования HTTP-ответов различных типов (JSON, HTML, файлы, потоки и т. д.). Используется, когда нужно вернуть ответ вручную, а не через автоматическую сериализацию FastAPI.</t>
+  </si>
+  <si>
+    <t>responses</t>
+  </si>
+  <si>
+    <t>Любой из этих классов можно использовать в качестве типа возвращаемого значения (response_class=...):
+@app.get("/", response_class=HTMLResponse)
+def main():
+    return "&lt;h1&gt;Welcome!&lt;/h1&gt;"
+Параметры конструктора (для всех классов):
+Response(content=None, status_code=200, headers=None, media_type=None)
+Для установки cookies:
+response = Response("OK")
+response.set_cookie(key="token", value="abc123")</t>
+  </si>
+  <si>
+    <t>from fastapi import FastAPI
+from fastapi.responses import JSONResponse, HTMLResponse, FileResponse, RedirectResponse
+app = FastAPI()
+@app.get("/json")
+def get_json():
+    data = {"message": "Hello, JSON!"}
+    return JSONResponse(content=data, status_code=200)
+@app.get("/html")
+def get_html():
+    html = "&lt;h1&gt;Hello, HTML!&lt;/h1&gt;"
+    return HTMLResponse(content=html)
+@app.get("/file")
+def get_file():
+    return FileResponse("example.txt", media_type="text/plain", filename="download.txt")
+@app.get("/redirect")
+def redirect():
+    return RedirectResponse(url="/json")</t>
+  </si>
+  <si>
+    <t>Базовый ответ. Можно указать любой тип содержимого (text, bytes, json и т. д.).</t>
+  </si>
+  <si>
+    <t>return Response(content="OK", media_type="text/plain")</t>
+  </si>
+  <si>
+    <t>JSONResponse</t>
+  </si>
+  <si>
+    <t>Возвращает данные в формате JSON. Используется по умолчанию в FastAPI.</t>
+  </si>
+  <si>
+    <t>return JSONResponse(content={"msg": "success"})</t>
+  </si>
+  <si>
+    <t>HTMLResponse</t>
+  </si>
+  <si>
+    <t>Возвращает HTML-документ. Устанавливает Content-Type: text/html.</t>
+  </si>
+  <si>
+    <t>return HTMLResponse("&lt;h1&gt;Hello&lt;/h1&gt;")</t>
+  </si>
+  <si>
+    <t>PlainTextResponse</t>
+  </si>
+  <si>
+    <t>Возвращает простой текст без HTML-тегов.</t>
+  </si>
+  <si>
+    <t>return PlainTextResponse("Simple text")</t>
+  </si>
+  <si>
+    <t>FileResponse</t>
+  </si>
+  <si>
+    <t>Отправляет файл пользователю (например, изображения, документы).</t>
+  </si>
+  <si>
+    <t>return FileResponse("report.pdf", media_type="application/pdf")</t>
+  </si>
+  <si>
+    <t>RedirectResponse</t>
+  </si>
+  <si>
+    <t>Перенаправляет на другой URL (HTTP 307, 302 и др.).</t>
+  </si>
+  <si>
+    <t>return RedirectResponse(url="/home")</t>
+  </si>
+  <si>
+    <t>StreamingResponse</t>
+  </si>
+  <si>
+    <t>Позволяет отправлять поток данных (например, большие файлы, видео, стриминг).</t>
+  </si>
+  <si>
+    <t>return StreamingResponse(open("bigfile.bin", "rb"))</t>
+  </si>
+  <si>
+    <t>ORJSONResponse</t>
+  </si>
+  <si>
+    <t>Быстрая альтернатива JSONResponse, использует библиотеку orjson.</t>
+  </si>
+  <si>
+    <t>return ORJSONResponse({"msg": "fast"})</t>
+  </si>
+  <si>
+    <t>UJSONResponse</t>
+  </si>
+  <si>
+    <t>Аналогично, но с использованием ujson.</t>
+  </si>
+  <si>
+    <t>return UJSONResponse({"msg": "ultra fast"})</t>
+  </si>
+  <si>
+    <r>
+      <t>ResponseRedirect</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(устаревший)</t>
+    </r>
+  </si>
+  <si>
+    <t>Старое название RedirectResponse (для совместимости).</t>
+  </si>
+  <si>
+    <t>Основные классы из fastapi.responses</t>
+  </si>
+  <si>
+    <t>Output Layer</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>from fastapi import status</t>
+  </si>
+  <si>
+    <t>Модуль, содержащий константы HTTP-статусов для удобного использования в коде (например, status.HTTP_200_OK).</t>
+  </si>
+  <si>
+    <t>Позволяет писать код чище, без “магических чисел”. Содержит статусы для: успешных ответов, ошибок клиента, ошибок сервера, перенаправлений и т.д.</t>
+  </si>
+  <si>
+    <t>from fastapi import FastAPI, status, HTTPException
+app = FastAPI()
+@app.get("/item/{item_id}")
+def read_item(item_id: int):
+    if item_id != 1:
+        raise HTTPException(status_code=status.HTTP_404_NOT_FOUND, detail="Item not found")   
+    return {"item_id": item_id}</t>
+  </si>
+  <si>
+    <t>HTTP_200_OK</t>
+  </si>
+  <si>
+    <t>Успешный ответ</t>
+  </si>
+  <si>
+    <t>HTTP_201_CREATED</t>
+  </si>
+  <si>
+    <t>Создано</t>
+  </si>
+  <si>
+    <t>HTTP_204_NO_CONTENT</t>
+  </si>
+  <si>
+    <t>Нет содержимого</t>
+  </si>
+  <si>
+    <t>HTTP_400_BAD_REQUEST</t>
+  </si>
+  <si>
+    <t>Ошибка клиента</t>
+  </si>
+  <si>
+    <t>HTTP_401_UNAUTHORIZED</t>
+  </si>
+  <si>
+    <t>Неавторизован</t>
+  </si>
+  <si>
+    <t>HTTP_403_FORBIDDEN</t>
+  </si>
+  <si>
+    <t>Доступ запрещён</t>
+  </si>
+  <si>
+    <t>HTTP_404_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>Не найдено</t>
+  </si>
+  <si>
+    <t>HTTP_500_INTERNAL_SERVER_ERROR</t>
+  </si>
+  <si>
+    <t>Ошибка сервера</t>
+  </si>
+  <si>
+    <t>Константа</t>
+  </si>
+  <si>
+    <t>Код</t>
+  </si>
+  <si>
+    <t>Назначение</t>
+  </si>
+  <si>
+    <t>HTTP_100_CONTINUE</t>
+  </si>
+  <si>
+    <t>Продолжение, клиент должен продолжить запрос</t>
+  </si>
+  <si>
+    <t>HTTP_101_SWITCHING_PROTOCOLS</t>
+  </si>
+  <si>
+    <t>Переключение протокола (WebSocket и др.)</t>
+  </si>
+  <si>
+    <t>HTTP_102_PROCESSING</t>
+  </si>
+  <si>
+    <t>Сервер обрабатывает запрос, пока нет ответа</t>
+  </si>
+  <si>
+    <t>Успешный запрос</t>
+  </si>
+  <si>
+    <t>Ресурс создан</t>
+  </si>
+  <si>
+    <t>HTTP_202_ACCEPTED</t>
+  </si>
+  <si>
+    <t>Принят запрос, обработка продолжается</t>
+  </si>
+  <si>
+    <t>HTTP_203_NON_AUTHORITATIVE_INFORMATION</t>
+  </si>
+  <si>
+    <t>Неполная информация от сервера</t>
+  </si>
+  <si>
+    <t>Нет содержимого (например, DELETE)</t>
+  </si>
+  <si>
+    <t>HTTP_205_RESET_CONTENT</t>
+  </si>
+  <si>
+    <t>Сброс содержимого формы на клиенте</t>
+  </si>
+  <si>
+    <t>HTTP_206_PARTIAL_CONTENT</t>
+  </si>
+  <si>
+    <t>Частичный контент (range-запрос)</t>
+  </si>
+  <si>
+    <t>HTTP_300_MULTIPLE_CHOICES</t>
+  </si>
+  <si>
+    <t>Множественный выбор URL</t>
+  </si>
+  <si>
+    <t>HTTP_301_MOVED_PERMANENTLY</t>
+  </si>
+  <si>
+    <t>Перемещено навсегда</t>
+  </si>
+  <si>
+    <t>HTTP_302_FOUND</t>
+  </si>
+  <si>
+    <t>Найдено (редирект)</t>
+  </si>
+  <si>
+    <t>HTTP_303_SEE_OTHER</t>
+  </si>
+  <si>
+    <t>Смотрите другой URL</t>
+  </si>
+  <si>
+    <t>HTTP_304_NOT_MODIFIED</t>
+  </si>
+  <si>
+    <t>Не изменялось (кэш)</t>
+  </si>
+  <si>
+    <t>HTTP_307_TEMPORARY_REDIRECT</t>
+  </si>
+  <si>
+    <t>Временный редирект</t>
+  </si>
+  <si>
+    <t>HTTP_308_PERMANENT_REDIRECT</t>
+  </si>
+  <si>
+    <t>Постоянный редирект</t>
+  </si>
+  <si>
+    <t>Ошибка запроса клиента</t>
+  </si>
+  <si>
+    <t>Не авторизован</t>
+  </si>
+  <si>
+    <t>HTTP_402_PAYMENT_REQUIRED</t>
+  </si>
+  <si>
+    <t>Платёж требуется (редко)</t>
+  </si>
+  <si>
+    <t>HTTP_405_METHOD_NOT_ALLOWED</t>
+  </si>
+  <si>
+    <t>Метод запроса запрещён</t>
+  </si>
+  <si>
+    <t>HTTP_406_NOT_ACCEPTABLE</t>
+  </si>
+  <si>
+    <t>Неприемлемо</t>
+  </si>
+  <si>
+    <t>HTTP_407_PROXY_AUTHENTICATION_REQUIRED</t>
+  </si>
+  <si>
+    <t>Требуется авторизация через прокси</t>
+  </si>
+  <si>
+    <t>HTTP_408_REQUEST_TIMEOUT</t>
+  </si>
+  <si>
+    <t>Таймаут запроса</t>
+  </si>
+  <si>
+    <t>HTTP_409_CONFLICT</t>
+  </si>
+  <si>
+    <t>Конфликт при обработке</t>
+  </si>
+  <si>
+    <t>HTTP_410_GONE</t>
+  </si>
+  <si>
+    <t>Ресурс удалён</t>
+  </si>
+  <si>
+    <t>HTTP_411_LENGTH_REQUIRED</t>
+  </si>
+  <si>
+    <t>Требуется заголовок Content-Length</t>
+  </si>
+  <si>
+    <t>HTTP_412_PRECONDITION_FAILED</t>
+  </si>
+  <si>
+    <t>Прервано условие запроса</t>
+  </si>
+  <si>
+    <t>HTTP_413_PAYLOAD_TOO_LARGE</t>
+  </si>
+  <si>
+    <t>Слишком большой payload</t>
+  </si>
+  <si>
+    <t>HTTP_414_URI_TOO_LONG</t>
+  </si>
+  <si>
+    <t>URI слишком длинный</t>
+  </si>
+  <si>
+    <t>HTTP_415_UNSUPPORTED_MEDIA_TYPE</t>
+  </si>
+  <si>
+    <t>Неподдерживаемый тип контента</t>
+  </si>
+  <si>
+    <t>HTTP_416_RANGE_NOT_SATISFIABLE</t>
+  </si>
+  <si>
+    <t>Недопустимый диапазон</t>
+  </si>
+  <si>
+    <t>HTTP_417_EXPECTATION_FAILED</t>
+  </si>
+  <si>
+    <t>Ожидание не выполнено</t>
+  </si>
+  <si>
+    <t>HTTP_418_IM_A_TEAPOT</t>
+  </si>
+  <si>
+    <t>Я чайник (шутливый статус)</t>
+  </si>
+  <si>
+    <t>HTTP_422_UNPROCESSABLE_ENTITY</t>
+  </si>
+  <si>
+    <t>Невозможно обработать (валидация Pydantic)</t>
+  </si>
+  <si>
+    <t>HTTP_426_UPGRADE_REQUIRED</t>
+  </si>
+  <si>
+    <t>Требуется апгрейд протокола</t>
+  </si>
+  <si>
+    <t>HTTP_501_NOT_IMPLEMENTED</t>
+  </si>
+  <si>
+    <t>Не реализовано</t>
+  </si>
+  <si>
+    <t>HTTP_502_BAD_GATEWAY</t>
+  </si>
+  <si>
+    <t>Плохой шлюз</t>
+  </si>
+  <si>
+    <t>HTTP_503_SERVICE_UNAVAILABLE</t>
+  </si>
+  <si>
+    <t>Сервис недоступен</t>
+  </si>
+  <si>
+    <t>HTTP_504_GATEWAY_TIMEOUT</t>
+  </si>
+  <si>
+    <t>Таймаут шлюза</t>
+  </si>
+  <si>
+    <t>HTTP_505_HTTP_VERSION_NOT_SUPPORTED</t>
+  </si>
+  <si>
+    <t>Версия HTTP не поддерживается</t>
+  </si>
+  <si>
+    <t>from fastapi import FastAPI, HTTPException, status
+app = FastAPI()
+@app.get("/items/{item_id}")
+def read_item(item_id: int):
+    if item_id != 1:
+        raise HTTPException(status_code=status.HTTP_404_NOT_FOUND, detail="Item not found")
+    return {"item_id": item_id}</t>
+  </si>
+  <si>
+    <t>from fastapi.responses import HTMLResponse
+@app.get("/html", response_class=HTMLResponse)
+def get_html():
+    return "&lt;h1&gt;Hello, HTML!&lt;/h1&gt;"</t>
+  </si>
+  <si>
+    <t>Популярные константы</t>
+  </si>
+  <si>
+    <t>encoders</t>
+  </si>
+  <si>
+    <t>jsonable_encoder</t>
+  </si>
+  <si>
+    <t>Основная функция: конвертирует объекты Python (Pydantic-модели, datetime, Decimal, UUID и др.) в JSON-сериализуемые типы (dict, list, str, int, float, bool, None).</t>
+  </si>
+  <si>
+    <t>decimal_encoder</t>
+  </si>
+  <si>
+    <t>Вспомогательная функция для конвертации Decimal в float или str.</t>
+  </si>
+  <si>
+    <t>Главная функция для сериализации</t>
+  </si>
+  <si>
+    <t>Конфигурация/карта энкодеров</t>
+  </si>
+  <si>
+    <t>ENCODERS_BY_TYPE</t>
+  </si>
+  <si>
+    <t>Словарь, где ключи — типы Python, значения — функции для их конвертации в сериализуемый формат.</t>
+  </si>
+  <si>
+    <t>encoders_by_class_tuples</t>
+  </si>
+  <si>
+    <t>Вспомогательная структура для генерации энкодеров по классам.</t>
+  </si>
+  <si>
+    <t>generate_encoders_by_class_tuples</t>
+  </si>
+  <si>
+    <t>Функция для создания карты энкодеров для кастомных классов.</t>
+  </si>
+  <si>
+    <t>Вспомогательные функции и константы</t>
+  </si>
+  <si>
+    <t>isoformat</t>
+  </si>
+  <si>
+    <t>Преобразует datetime в ISO 8601 строку.</t>
+  </si>
+  <si>
+    <t>_is_undefined</t>
+  </si>
+  <si>
+    <t>Служебный флаг для внутренних проверок.</t>
+  </si>
+  <si>
+    <t>_model_dump</t>
+  </si>
+  <si>
+    <t>Вспомогательный метод для извлечения данных из Pydantic-модели (v2).</t>
+  </si>
+  <si>
+    <t>may_v1</t>
+  </si>
+  <si>
+    <t>Флаг совместимости с Pydantic v1.</t>
+  </si>
+  <si>
+    <t>Типы и аннотации (переэкспорт из Pydantic / стандартной библиотеки)</t>
+  </si>
+  <si>
+    <t>BaseModel, Field, Enum, UUID, IPv4Address, IPv6Address, Any, Callable, List, Dict, Tuple, Optional, Union, Annotated и др.</t>
+  </si>
+  <si>
+    <t>Используются в Pydantic-моделях и аннотациях типов. FastAPI импортирует их для удобства.</t>
+  </si>
+  <si>
+    <t>SecretStr, SecretBytes</t>
+  </si>
+  <si>
+    <t>Безопасные строки/байты (например, пароли) для сериализации.</t>
+  </si>
+  <si>
+    <t>dataclasses</t>
+  </si>
+  <si>
+    <t>Поддержка сериализации dataclass-объектов.</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>Для корректного преобразования datetime в JSON.</t>
+  </si>
+  <si>
+    <t>Color, NameEmail, AnyUrl, Url</t>
+  </si>
+  <si>
+    <t>Вспомогательные типы для валидации.</t>
+  </si>
+  <si>
+    <t>Структуры данных</t>
+  </si>
+  <si>
+    <t>defaultdict, deque</t>
+  </si>
+  <si>
+    <t>Для поддержки сериализации этих стандартных структур.</t>
+  </si>
+  <si>
+    <t>Pattern, PurePath</t>
+  </si>
+  <si>
+    <t>Вспомогательные типы (регулярные выражения, пути).</t>
+  </si>
+  <si>
+    <t>GeneratorType</t>
+  </si>
+  <si>
+    <t>Для корректной обработки генераторов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	•	jsonable_encoder полезен, когда нужно передать Pydantic-модель или объект с не-JSON типами в dict или JSONResponse.
+	•	Внутри функция рекурсивно конвертирует объекты, списки, словари и сложные типы.
+	•	Используется в сочетании с базами данных, например, перед вставкой в MongoDB или PostgreSQL (через JSONB).</t>
+  </si>
+  <si>
+    <t>from fastapi import FastAPI
+from fastapi.encoders import jsonable_encoder
+from pydantic import BaseModel
+from datetime import datetime
+app = FastAPI()
+class Item(BaseModel):
+    id: int
+    name: str
+    created_at: datetime
+@app.get("/item")
+def get_item():
+    item = Item(id=1, name="Test", created_at=datetime.now())
+    json_compatible_item = jsonable_encoder(item)
+    return json_compatible_item</t>
+  </si>
+  <si>
+    <t>from fastapi.encoders import jsonable_encod</t>
+  </si>
+  <si>
+    <t>head(path)</t>
+  </si>
+  <si>
+    <t>Регистрирует HEAD-эндпоинт</t>
+  </si>
+  <si>
+    <t>trace(path)</t>
+  </si>
+  <si>
+    <t>Регистрирует TRACE-эндпоинт</t>
+  </si>
+  <si>
+    <t>add_api_websocket_route(path, endpoint)</t>
+  </si>
+  <si>
+    <t>endpoint)
+Программная регистрация WebSocket маршрута</t>
+  </si>
+  <si>
+    <t>add_event_handler(event_type, func)</t>
+  </si>
+  <si>
+    <t>Ручная регистрация обработчика события</t>
+  </si>
+  <si>
+    <t>app.url_path_for("get_item", item_id=5)</t>
+  </si>
+  <si>
+    <t>app.openapi()</t>
+  </si>
+  <si>
+    <t>Назначение: функции для сериализации данных в JSON, поддержка Pydantic моделей.
+datetime, UUID в сложных структурах без Pydantic</t>
+  </si>
+  <si>
+    <t>Разница</t>
+  </si>
+  <si>
+    <t>from fastapi import FastAPI, Request, Response
+from fastapi.responses import JSONResponse
+app = FastAPI()
+@app.get("/data")
+def get_data(request: Request):
+    # Данные для ответа
+    data = {"message": "Hello, FastAPI!", "status": "success"}
+    # Проверяем заголовок Accept
+    accept = request.headers.get("accept", "")
+    if "text/html" in accept:
+        # Возвращаем HTML
+        html_content = f"""
+        &lt;html&gt;
+            &lt;head&gt;&lt;title&gt;FastAPI Example&lt;/title&gt;&lt;/head&gt;
+            &lt;body&gt;
+                &lt;h1&gt;{data['message']}&lt;/h1&gt;
+                &lt;p&gt;Status: {data['status']}&lt;/p&gt;
+            &lt;/body&gt;
+        &lt;/html&gt;
+        """
+        return Response(content=html_content, media_type="text/html")
+    return JSONResponse(content=data)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1930,6 +4780,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1957,7 +4815,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -2017,12 +4875,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2054,6 +4925,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2077,7 +4957,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2104,6 +4983,30 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2420,7 +5323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A0BD9ED-BBA3-C242-AD3C-6BF28F005CA3}">
-  <dimension ref="B2:G38"/>
+  <dimension ref="A2:G82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="4"/>
@@ -2429,8 +5332,9 @@
     <col min="4" max="4" width="36.33203125" style="4" customWidth="1"/>
     <col min="5" max="5" width="32.1640625" style="4" customWidth="1"/>
     <col min="6" max="6" width="35.6640625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="32.1640625" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="4"/>
+    <col min="7" max="7" width="41.33203125" customWidth="1"/>
+    <col min="8" max="9" width="41.33203125" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
@@ -2450,478 +5354,1237 @@
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" s="2" customFormat="1" ht="221" x14ac:dyDescent="0.2">
+      <c r="B3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" spans="2:7" s="2" customFormat="1" ht="85" x14ac:dyDescent="0.2">
+      <c r="B4" s="12"/>
+      <c r="C4" s="31" t="s">
+        <v>318</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>320</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5" spans="2:7" s="2" customFormat="1" ht="221" x14ac:dyDescent="0.2">
+      <c r="B5" s="13"/>
+      <c r="C5" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>323</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>324</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>325</v>
+      </c>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" spans="2:7" ht="272" x14ac:dyDescent="0.2">
+      <c r="B6" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" s="2" customFormat="1" ht="221" x14ac:dyDescent="0.2">
-      <c r="B3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>270</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="10"/>
-    </row>
-    <row r="4" spans="2:7" ht="272" x14ac:dyDescent="0.2">
-      <c r="B4" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B5" s="27"/>
-      <c r="C5" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="F5" s="11" t="s">
+      <c r="G6" s="23" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B7" s="29"/>
+      <c r="C7" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="G5" s="23"/>
-    </row>
-    <row r="6" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B6" s="27"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="22" t="s">
+      <c r="D7" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="E7" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="F7" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="G7" s="25"/>
+    </row>
+    <row r="8" spans="2:7" ht="136" x14ac:dyDescent="0.2">
+      <c r="B8" s="29"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="34" t="s">
+        <v>314</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="G8" s="25"/>
+    </row>
+    <row r="9" spans="2:7" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="29"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="E9" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="G6" s="23"/>
-    </row>
-    <row r="7" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B7" s="27"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="22" t="s">
+      <c r="F9" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="G9" s="25"/>
+    </row>
+    <row r="10" spans="2:7" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="29"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="F10" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="G10" s="25"/>
+    </row>
+    <row r="11" spans="2:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="B11" s="29"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="G11" s="25"/>
+    </row>
+    <row r="12" spans="2:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="B12" s="29"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="F12" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="G12" s="25"/>
+    </row>
+    <row r="13" spans="2:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B13" s="29"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="G13" s="25"/>
+    </row>
+    <row r="14" spans="2:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B14" s="29"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="24" t="s">
+        <v>539</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="G14" s="25"/>
+    </row>
+    <row r="15" spans="2:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B15" s="29"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="24" t="s">
+        <v>541</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="G15" s="25"/>
+    </row>
+    <row r="16" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B16" s="29"/>
+      <c r="C16" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="G16" s="25"/>
+    </row>
+    <row r="17" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B17" s="29"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="G17" s="25"/>
+    </row>
+    <row r="18" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B18" s="29"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="G18" s="25"/>
+    </row>
+    <row r="19" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B19" s="29"/>
+      <c r="C19" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G19" s="25"/>
+    </row>
+    <row r="20" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B20" s="29"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="G20" s="25"/>
+    </row>
+    <row r="21" spans="2:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="B21" s="29"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="14" t="s">
+        <v>543</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="F21" s="14"/>
+      <c r="G21" s="25"/>
+    </row>
+    <row r="22" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B22" s="29"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="14" t="s">
+        <v>545</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>546</v>
+      </c>
+      <c r="F22" s="14"/>
+      <c r="G22" s="25"/>
+    </row>
+    <row r="23" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B23" s="29"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="G23" s="25"/>
+    </row>
+    <row r="24" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B24" s="29"/>
+      <c r="C24" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="G24" s="25"/>
+    </row>
+    <row r="25" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B25" s="29"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="G25" s="25"/>
+    </row>
+    <row r="26" spans="2:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B26" s="29"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="G26" s="25"/>
+    </row>
+    <row r="27" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B27" s="29"/>
+      <c r="C27" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="G27" s="25"/>
+    </row>
+    <row r="28" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B28" s="29"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="G28" s="25"/>
+    </row>
+    <row r="29" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B29" s="29"/>
+      <c r="C29" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="G29" s="25"/>
+    </row>
+    <row r="30" spans="2:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B30" s="29"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>547</v>
+      </c>
+      <c r="G30" s="25"/>
+    </row>
+    <row r="31" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B31" s="29"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="F31" s="14"/>
+      <c r="G31" s="25"/>
+    </row>
+    <row r="32" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B32" s="29"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="F32" s="14"/>
+      <c r="G32" s="25"/>
+    </row>
+    <row r="33" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B33" s="29"/>
+      <c r="C33" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="F33" s="14"/>
+      <c r="G33" s="25"/>
+    </row>
+    <row r="34" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B34" s="29"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="F34" s="14"/>
+      <c r="G34" s="25"/>
+    </row>
+    <row r="35" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B35" s="29"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="F35" s="14"/>
+      <c r="G35" s="25"/>
+    </row>
+    <row r="36" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B36" s="30"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="F36" s="14"/>
+      <c r="G36" s="27"/>
+    </row>
+    <row r="37" spans="1:7" ht="306" x14ac:dyDescent="0.2">
+      <c r="A37" s="36" t="s">
+        <v>391</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A38" s="36"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="D38" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="G38" s="17" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A39" s="36"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A40" s="36"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="37" t="s">
+        <v>340</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="G40" s="17" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A41" s="36"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="G41" s="17" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A42" s="36"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="G42" s="17" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A43" s="36"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="37" t="s">
+        <v>350</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A44" s="36"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="37" t="s">
+        <v>353</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>354</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="409" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="36"/>
+      <c r="B45" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="G45" s="17" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A46" s="36"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="36" t="s">
+        <v>390</v>
+      </c>
+      <c r="D46" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="G46" s="38" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A47" s="36"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="36"/>
+      <c r="D47" s="37" t="s">
+        <v>364</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="G47" s="39"/>
+    </row>
+    <row r="48" spans="1:7" ht="102" x14ac:dyDescent="0.2">
+      <c r="A48" s="36"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="36"/>
+      <c r="D48" s="37" t="s">
+        <v>367</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="G48" s="17" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A49" s="36"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="37" t="s">
+        <v>370</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="G49" s="22"/>
+    </row>
+    <row r="50" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A50" s="36"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="37" t="s">
+        <v>373</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="G50" s="22"/>
+    </row>
+    <row r="51" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A51" s="36"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="36"/>
+      <c r="D51" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="G51" s="22"/>
+    </row>
+    <row r="52" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A52" s="36"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="37" t="s">
+        <v>379</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="G52" s="22"/>
+    </row>
+    <row r="53" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A53" s="36"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="37" t="s">
+        <v>382</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="F53" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="G53" s="22"/>
+    </row>
+    <row r="54" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A54" s="36"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="37" t="s">
+        <v>385</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="F54" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="G54" s="22"/>
+    </row>
+    <row r="55" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A55" s="36"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="37" t="s">
+        <v>388</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="G55" s="22"/>
+    </row>
+    <row r="56" spans="1:7" ht="221" x14ac:dyDescent="0.2">
+      <c r="A56" s="36"/>
+      <c r="B56" s="18" t="s">
+        <v>392</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="F56" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="G56" s="17" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="36"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="36" t="s">
+        <v>495</v>
+      </c>
+      <c r="D57" s="22" t="s">
+        <v>397</v>
+      </c>
+      <c r="E57" s="22">
         <v>200</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="F57" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="G57" s="22"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="36"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="36"/>
+      <c r="D58" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="E58" s="22">
         <v>201</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="G7" s="23"/>
-    </row>
-    <row r="8" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B8" s="27"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="E8" s="11" t="s">
+      <c r="F58" s="22" t="s">
+        <v>400</v>
+      </c>
+      <c r="G58" s="22"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="36"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="36"/>
+      <c r="D59" s="22" t="s">
+        <v>401</v>
+      </c>
+      <c r="E59" s="22">
         <v>204</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="G8" s="23"/>
-    </row>
-    <row r="9" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B9" s="27"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="G9" s="23"/>
-    </row>
-    <row r="10" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B10" s="27"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="G10" s="23"/>
-    </row>
-    <row r="11" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B11" s="27"/>
-      <c r="C11" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="G11" s="23"/>
-    </row>
-    <row r="12" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B12" s="27"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="G12" s="23"/>
-    </row>
-    <row r="13" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B13" s="27"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="G13" s="23"/>
-    </row>
-    <row r="14" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B14" s="27"/>
-      <c r="C14" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="G14" s="23"/>
-    </row>
-    <row r="15" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B15" s="27"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="G15" s="23"/>
-    </row>
-    <row r="16" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B16" s="27"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="G16" s="23"/>
-    </row>
-    <row r="17" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B17" s="27"/>
-      <c r="C17" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="G17" s="23"/>
-    </row>
-    <row r="18" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B18" s="27"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="G18" s="23"/>
-    </row>
-    <row r="19" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B19" s="27"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="G19" s="23"/>
-    </row>
-    <row r="20" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B20" s="27"/>
-      <c r="C20" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="G20" s="23"/>
-    </row>
-    <row r="21" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B21" s="27"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="G21" s="23"/>
-    </row>
-    <row r="22" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B22" s="27"/>
-      <c r="C22" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="F22" s="11"/>
-      <c r="G22" s="23"/>
-    </row>
-    <row r="23" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B23" s="27"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="23"/>
-    </row>
-    <row r="24" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B24" s="27"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="23"/>
-    </row>
-    <row r="25" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B25" s="27"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="23"/>
-    </row>
-    <row r="26" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B26" s="27"/>
-      <c r="C26" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="F26" s="11"/>
-      <c r="G26" s="23"/>
-    </row>
-    <row r="27" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B27" s="27"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="F27" s="11"/>
-      <c r="G27" s="23"/>
-    </row>
-    <row r="28" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B28" s="27"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="F28" s="11"/>
-      <c r="G28" s="23"/>
-    </row>
-    <row r="29" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B29" s="28"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="F29" s="11"/>
-      <c r="G29" s="25"/>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="20"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="20"/>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="20"/>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="20"/>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="20"/>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="20"/>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="20"/>
+      <c r="F59" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="G59" s="22"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="36"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="36"/>
+      <c r="D60" s="22" t="s">
+        <v>403</v>
+      </c>
+      <c r="E60" s="22">
+        <v>400</v>
+      </c>
+      <c r="F60" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="G60" s="22"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="36"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="36"/>
+      <c r="D61" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="E61" s="22">
+        <v>401</v>
+      </c>
+      <c r="F61" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="G61" s="22"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="36"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="22" t="s">
+        <v>407</v>
+      </c>
+      <c r="E62" s="22">
+        <v>403</v>
+      </c>
+      <c r="F62" s="22" t="s">
+        <v>408</v>
+      </c>
+      <c r="G62" s="22"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="36"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="36"/>
+      <c r="D63" s="22" t="s">
+        <v>409</v>
+      </c>
+      <c r="E63" s="22">
+        <v>404</v>
+      </c>
+      <c r="F63" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="G63" s="22"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="36"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="22" t="s">
+        <v>411</v>
+      </c>
+      <c r="E64" s="22">
+        <v>500</v>
+      </c>
+      <c r="F64" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="G64" s="22"/>
+    </row>
+    <row r="65" spans="1:7" ht="340" x14ac:dyDescent="0.2">
+      <c r="A65" s="36"/>
+      <c r="B65" s="18" t="s">
+        <v>496</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>538</v>
+      </c>
+      <c r="D65" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>536</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>537</v>
+      </c>
+      <c r="G65" s="22"/>
+    </row>
+    <row r="66" spans="1:7" ht="85" x14ac:dyDescent="0.2">
+      <c r="A66" s="36"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="36" t="s">
+        <v>501</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="E66" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="F66" s="17"/>
+      <c r="G66" s="22"/>
+    </row>
+    <row r="67" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A67" s="36"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="36"/>
+      <c r="D67" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>500</v>
+      </c>
+      <c r="F67" s="17"/>
+      <c r="G67" s="22"/>
+    </row>
+    <row r="68" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="A68" s="36"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="36" t="s">
+        <v>502</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>503</v>
+      </c>
+      <c r="E68" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="F68" s="17"/>
+      <c r="G68" s="22"/>
+    </row>
+    <row r="69" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A69" s="36"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="36"/>
+      <c r="D69" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="E69" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="F69" s="17"/>
+      <c r="G69" s="22"/>
+    </row>
+    <row r="70" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A70" s="36"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="E70" s="17" t="s">
+        <v>508</v>
+      </c>
+      <c r="F70" s="17"/>
+      <c r="G70" s="22"/>
+    </row>
+    <row r="71" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A71" s="36"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="36" t="s">
+        <v>509</v>
+      </c>
+      <c r="D71" s="17" t="s">
+        <v>510</v>
+      </c>
+      <c r="E71" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="F71" s="17"/>
+      <c r="G71" s="22"/>
+    </row>
+    <row r="72" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A72" s="36"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="E72" s="17" t="s">
+        <v>513</v>
+      </c>
+      <c r="F72" s="17"/>
+      <c r="G72" s="22"/>
+    </row>
+    <row r="73" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A73" s="36"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="36"/>
+      <c r="D73" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="E73" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="F73" s="17"/>
+      <c r="G73" s="22"/>
+    </row>
+    <row r="74" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A74" s="36"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="17" t="s">
+        <v>516</v>
+      </c>
+      <c r="E74" s="17" t="s">
+        <v>517</v>
+      </c>
+      <c r="F74" s="17"/>
+      <c r="G74" s="22"/>
+    </row>
+    <row r="75" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="A75" s="36"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="36" t="s">
+        <v>518</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>519</v>
+      </c>
+      <c r="E75" s="17" t="s">
+        <v>520</v>
+      </c>
+      <c r="F75" s="17"/>
+      <c r="G75" s="22"/>
+    </row>
+    <row r="76" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A76" s="36"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="36"/>
+      <c r="D76" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="E76" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="F76" s="17"/>
+      <c r="G76" s="22"/>
+    </row>
+    <row r="77" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A77" s="36"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="36"/>
+      <c r="D77" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="E77" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="F77" s="17"/>
+      <c r="G77" s="22"/>
+    </row>
+    <row r="78" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A78" s="36"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="17" t="s">
+        <v>525</v>
+      </c>
+      <c r="E78" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="F78" s="17"/>
+      <c r="G78" s="22"/>
+    </row>
+    <row r="79" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A79" s="36"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="17" t="s">
+        <v>527</v>
+      </c>
+      <c r="E79" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="F79" s="17"/>
+      <c r="G79" s="22"/>
+    </row>
+    <row r="80" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A80" s="36"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="36" t="s">
+        <v>529</v>
+      </c>
+      <c r="D80" s="17" t="s">
+        <v>530</v>
+      </c>
+      <c r="E80" s="17" t="s">
+        <v>531</v>
+      </c>
+      <c r="F80" s="17"/>
+      <c r="G80" s="22"/>
+    </row>
+    <row r="81" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A81" s="36"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="36"/>
+      <c r="D81" s="17" t="s">
+        <v>532</v>
+      </c>
+      <c r="E81" s="17" t="s">
+        <v>533</v>
+      </c>
+      <c r="F81" s="17"/>
+      <c r="G81" s="22"/>
+    </row>
+    <row r="82" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A82" s="36"/>
+      <c r="B82" s="18"/>
+      <c r="C82" s="36"/>
+      <c r="D82" s="17" t="s">
+        <v>534</v>
+      </c>
+      <c r="E82" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="F82" s="17"/>
+      <c r="G82" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="B4:B29"/>
-    <mergeCell ref="G4:G29"/>
-    <mergeCell ref="C5:C10"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="C22:C25"/>
+  <mergeCells count="24">
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="C75:C79"/>
+    <mergeCell ref="C80:C82"/>
+    <mergeCell ref="C71:C74"/>
+    <mergeCell ref="B65:B82"/>
+    <mergeCell ref="C46:C55"/>
+    <mergeCell ref="B45:B55"/>
+    <mergeCell ref="C57:C64"/>
+    <mergeCell ref="B56:B64"/>
+    <mergeCell ref="A37:A82"/>
+    <mergeCell ref="C33:C36"/>
+    <mergeCell ref="B6:B36"/>
+    <mergeCell ref="G6:G36"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C38:C44"/>
+    <mergeCell ref="B37:B44"/>
+    <mergeCell ref="C7:C15"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C19:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C29:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -2960,93 +6623,193 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3" t="s">
+    <row r="3" spans="2:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="B5" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G6" s="32" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+    <row r="7" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B7" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="3"/>
@@ -3229,6 +6992,515 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B16C996-A567-504E-8107-D2FEAE35EE4E}">
+  <dimension ref="B2:D46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="47.1640625" customWidth="1"/>
+    <col min="4" max="4" width="52" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B3" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C3" s="3">
+        <v>100</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B4" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C4" s="3">
+        <v>101</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B5" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C5" s="3">
+        <v>102</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B6" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C6" s="3">
+        <v>200</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B7" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C7" s="3">
+        <v>201</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B8" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C8" s="3">
+        <v>202</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B9" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C9" s="3">
+        <v>203</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B10" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C10" s="3">
+        <v>204</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B11" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C11" s="3">
+        <v>205</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B12" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C12" s="3">
+        <v>206</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B13" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C13" s="3">
+        <v>300</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B14" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C14" s="3">
+        <v>301</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B15" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C15" s="3">
+        <v>302</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B16" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C16" s="3">
+        <v>303</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B17" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C17" s="3">
+        <v>304</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B18" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C18" s="3">
+        <v>307</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B19" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C19" s="3">
+        <v>308</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B20" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C20" s="3">
+        <v>400</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B21" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C21" s="3">
+        <v>401</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B22" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C22" s="3">
+        <v>402</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B23" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C23" s="3">
+        <v>403</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B24" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C24" s="3">
+        <v>404</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B25" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C25" s="3">
+        <v>405</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B26" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C26" s="3">
+        <v>406</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B27" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C27" s="3">
+        <v>407</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B28" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C28" s="3">
+        <v>408</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B29" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C29" s="3">
+        <v>409</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B30" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C30" s="3">
+        <v>410</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B31" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C31" s="3">
+        <v>411</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B32" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C32" s="3">
+        <v>412</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B33" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C33" s="3">
+        <v>413</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B34" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C34" s="3">
+        <v>414</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B35" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C35" s="3">
+        <v>415</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B36" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C36" s="3">
+        <v>416</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B37" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="C37" s="3">
+        <v>417</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B38" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C38" s="3">
+        <v>418</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B39" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C39" s="3">
+        <v>422</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B40" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C40" s="3">
+        <v>426</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B41" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C41" s="3">
+        <v>500</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B42" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C42" s="3">
+        <v>501</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B43" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C43" s="3">
+        <v>502</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B44" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C44" s="3">
+        <v>503</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B45" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C45" s="3">
+        <v>504</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B46" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C46" s="3">
+        <v>505</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>492</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E05CED-0F99-CF4B-A45D-0AC420A97B6D}">
   <dimension ref="B2:G73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3260,966 +7532,966 @@
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" customFormat="1" ht="204" x14ac:dyDescent="0.2">
+      <c r="B3" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="20"/>
+      <c r="G5" s="21"/>
+    </row>
+    <row r="6" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="14"/>
+      <c r="G6" s="21"/>
+    </row>
+    <row r="7" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="14"/>
+      <c r="G7" s="21"/>
+    </row>
+    <row r="8" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="21"/>
+    </row>
+    <row r="9" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="14"/>
+      <c r="G9" s="21"/>
+    </row>
+    <row r="10" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="14"/>
+      <c r="G10" s="21"/>
+    </row>
+    <row r="11" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="21"/>
+    </row>
+    <row r="12" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="21"/>
+    </row>
+    <row r="13" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="20"/>
+      <c r="G13" s="21"/>
+    </row>
+    <row r="14" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="14"/>
+      <c r="G14" s="21"/>
+    </row>
+    <row r="15" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="14"/>
+      <c r="G15" s="21"/>
+    </row>
+    <row r="16" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="14"/>
+      <c r="G16" s="21"/>
+    </row>
+    <row r="17" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="21"/>
+    </row>
+    <row r="18" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="14"/>
+      <c r="G18" s="21"/>
+    </row>
+    <row r="19" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="14"/>
+      <c r="G19" s="21"/>
+    </row>
+    <row r="20" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" s="21"/>
+    </row>
+    <row r="21" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="14"/>
+      <c r="G21" s="21"/>
+    </row>
+    <row r="22" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="14"/>
+      <c r="G22" s="21"/>
+    </row>
+    <row r="23" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="14"/>
+      <c r="G23" s="21"/>
+    </row>
+    <row r="24" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" s="14"/>
+      <c r="G24" s="21"/>
+    </row>
+    <row r="25" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="14"/>
+      <c r="G25" s="21"/>
+    </row>
+    <row r="26" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F26" s="14"/>
+      <c r="G26" s="21"/>
+    </row>
+    <row r="27" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="G27" s="21"/>
+    </row>
+    <row r="28" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="14"/>
+      <c r="G28" s="21"/>
+    </row>
+    <row r="29" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="14"/>
+      <c r="G29" s="21"/>
+    </row>
+    <row r="30" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="F30" s="14"/>
+      <c r="G30" s="21"/>
+    </row>
+    <row r="31" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" s="14"/>
+      <c r="G31" s="21"/>
+    </row>
+    <row r="32" spans="2:7" customFormat="1" ht="306" x14ac:dyDescent="0.2">
+      <c r="B32" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="G32" s="22"/>
+    </row>
+    <row r="33" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B33" s="18"/>
+      <c r="C33" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="34" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="G34" s="22"/>
+    </row>
+    <row r="35" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="G35" s="22"/>
+    </row>
+    <row r="36" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="G36" s="22"/>
+    </row>
+    <row r="37" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="G37" s="22"/>
+    </row>
+    <row r="38" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="G38" s="22"/>
+    </row>
+    <row r="39" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="G39" s="22"/>
+    </row>
+    <row r="40" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="G40" s="22"/>
+    </row>
+    <row r="41" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="G41" s="22"/>
+    </row>
+    <row r="42" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="G42" s="22"/>
+    </row>
+    <row r="43" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="G43" s="22"/>
+    </row>
+    <row r="44" spans="2:7" customFormat="1" ht="388" x14ac:dyDescent="0.2">
+      <c r="B44" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="G44" s="21"/>
+    </row>
+    <row r="45" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B45" s="19"/>
+      <c r="C45" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F45" s="14"/>
+      <c r="G45" s="21"/>
+    </row>
+    <row r="46" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="F46" s="14"/>
+      <c r="G46" s="21"/>
+    </row>
+    <row r="47" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F47" s="14"/>
+      <c r="G47" s="21"/>
+    </row>
+    <row r="48" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="F48" s="14"/>
+      <c r="G48" s="21"/>
+    </row>
+    <row r="49" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="F49" s="14"/>
+      <c r="G49" s="21"/>
+    </row>
+    <row r="50" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="F50" s="14"/>
+      <c r="G50" s="21"/>
+    </row>
+    <row r="51" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="F51" s="14"/>
+      <c r="G51" s="21"/>
+    </row>
+    <row r="52" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="F52" s="14"/>
+      <c r="G52" s="21"/>
+    </row>
+    <row r="53" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B53" s="19"/>
+      <c r="C53" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="G53" s="21"/>
+    </row>
+    <row r="54" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="G54" s="21"/>
+    </row>
+    <row r="55" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="G55" s="21"/>
+    </row>
+    <row r="56" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="F56" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="G56" s="21"/>
+    </row>
+    <row r="57" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B57" s="19"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="F57" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="G57" s="21"/>
+    </row>
+    <row r="58" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="F58" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="G58" s="21"/>
+    </row>
+    <row r="59" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="B59" s="19"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="F59" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G59" s="21"/>
+    </row>
+    <row r="60" spans="2:7" ht="272" x14ac:dyDescent="0.2">
+      <c r="B60" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C60" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="D60" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="E60" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="F60" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="G60" s="22"/>
+    </row>
+    <row r="61" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B61" s="18"/>
+      <c r="C61" s="18" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" customFormat="1" ht="204" x14ac:dyDescent="0.2">
-      <c r="B3" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B4" s="16"/>
-      <c r="C4" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="G4" s="18"/>
-    </row>
-    <row r="5" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="18"/>
-    </row>
-    <row r="6" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="18"/>
-    </row>
-    <row r="7" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="18"/>
-    </row>
-    <row r="8" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="G8" s="18"/>
-    </row>
-    <row r="9" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="18"/>
-    </row>
-    <row r="10" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="18"/>
-    </row>
-    <row r="11" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G11" s="18"/>
-    </row>
-    <row r="12" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="18"/>
-    </row>
-    <row r="13" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="18"/>
-    </row>
-    <row r="15" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="18"/>
-    </row>
-    <row r="16" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" s="11"/>
-      <c r="G16" s="18"/>
-    </row>
-    <row r="17" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="18"/>
-    </row>
-    <row r="18" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="18"/>
-    </row>
-    <row r="19" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="18"/>
-    </row>
-    <row r="20" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G20" s="18"/>
-    </row>
-    <row r="21" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="18"/>
-    </row>
-    <row r="22" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F22" s="11"/>
-      <c r="G22" s="18"/>
-    </row>
-    <row r="23" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="18"/>
-    </row>
-    <row r="24" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="18"/>
-    </row>
-    <row r="25" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="18"/>
-    </row>
-    <row r="26" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="F26" s="11"/>
-      <c r="G26" s="18"/>
-    </row>
-    <row r="27" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="11"/>
-      <c r="G27" s="18"/>
-    </row>
-    <row r="28" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="F28" s="11"/>
-      <c r="G28" s="18"/>
-    </row>
-    <row r="29" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F29" s="11"/>
-      <c r="G29" s="18"/>
-    </row>
-    <row r="30" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F30" s="11"/>
-      <c r="G30" s="18"/>
-    </row>
-    <row r="31" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="F31" s="11"/>
-      <c r="G31" s="18"/>
-    </row>
-    <row r="32" spans="2:7" customFormat="1" ht="306" x14ac:dyDescent="0.2">
-      <c r="B32" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="G32" s="19"/>
-    </row>
-    <row r="33" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B33" s="15"/>
-      <c r="C33" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="G33" s="19"/>
-    </row>
-    <row r="34" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="14" t="s">
+      <c r="D61" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="E34" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="G34" s="19"/>
-    </row>
-    <row r="35" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="14" t="s">
+      <c r="E61" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="G61" s="22"/>
+    </row>
+    <row r="62" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E62" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="F35" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="G35" s="19"/>
-    </row>
-    <row r="36" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="14" t="s">
+      <c r="F62" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="G62" s="22"/>
+    </row>
+    <row r="63" spans="2:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E63" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="F36" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G36" s="19"/>
-    </row>
-    <row r="37" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="14" t="s">
+      <c r="F63" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="G63" s="22"/>
+    </row>
+    <row r="64" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E64" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="F64" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="G64" s="22"/>
+    </row>
+    <row r="65" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="G65" s="22"/>
+    </row>
+    <row r="66" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="E66" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F66" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="G66" s="22"/>
+    </row>
+    <row r="67" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="E67" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F67" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="G67" s="22"/>
+    </row>
+    <row r="68" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E68" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="G37" s="19"/>
-    </row>
-    <row r="38" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="G38" s="19"/>
-    </row>
-    <row r="39" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F39" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="G39" s="19"/>
-    </row>
-    <row r="40" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="G40" s="19"/>
-    </row>
-    <row r="41" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F41" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="G41" s="19"/>
-    </row>
-    <row r="42" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="F42" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="G42" s="19"/>
-    </row>
-    <row r="43" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="E43" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F43" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="G43" s="19"/>
-    </row>
-    <row r="44" spans="2:7" customFormat="1" ht="388" x14ac:dyDescent="0.2">
-      <c r="B44" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="G44" s="18"/>
-    </row>
-    <row r="45" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B45" s="16"/>
-      <c r="C45" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="F45" s="11"/>
-      <c r="G45" s="18"/>
-    </row>
-    <row r="46" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B46" s="16"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="F46" s="11"/>
-      <c r="G46" s="18"/>
-    </row>
-    <row r="47" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B47" s="16"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="F47" s="11"/>
-      <c r="G47" s="18"/>
-    </row>
-    <row r="48" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="F48" s="11"/>
-      <c r="G48" s="18"/>
-    </row>
-    <row r="49" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B49" s="16"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="F49" s="11"/>
-      <c r="G49" s="18"/>
-    </row>
-    <row r="50" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="F50" s="11"/>
-      <c r="G50" s="18"/>
-    </row>
-    <row r="51" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B51" s="16"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="F51" s="11"/>
-      <c r="G51" s="18"/>
-    </row>
-    <row r="52" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F52" s="11"/>
-      <c r="G52" s="18"/>
-    </row>
-    <row r="53" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B53" s="16"/>
-      <c r="C53" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="F53" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="G53" s="18"/>
-    </row>
-    <row r="54" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B54" s="16"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="G54" s="18"/>
-    </row>
-    <row r="55" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F55" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="G55" s="18"/>
-    </row>
-    <row r="56" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F56" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="G56" s="18"/>
-    </row>
-    <row r="57" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B57" s="16"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="E57" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="F57" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="G57" s="18"/>
-    </row>
-    <row r="58" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B58" s="16"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="F58" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="G58" s="18"/>
-    </row>
-    <row r="59" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B59" s="16"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="E59" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="F59" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="G59" s="18"/>
-    </row>
-    <row r="60" spans="2:7" ht="272" x14ac:dyDescent="0.2">
-      <c r="B60" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="D60" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="E60" s="14" t="s">
+      <c r="F68" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="F60" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="G60" s="19"/>
-    </row>
-    <row r="61" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B61" s="15"/>
-      <c r="C61" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="E61" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="F61" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="G61" s="19"/>
-    </row>
-    <row r="62" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B62" s="15"/>
-      <c r="C62" s="15"/>
-      <c r="D62" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E62" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F62" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="G62" s="19"/>
-    </row>
-    <row r="63" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B63" s="15"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E63" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F63" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="G63" s="19"/>
-    </row>
-    <row r="64" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B64" s="15"/>
-      <c r="C64" s="15"/>
-      <c r="D64" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="E64" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="F64" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="G64" s="19"/>
-    </row>
-    <row r="65" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B65" s="15"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="E65" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F65" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="G65" s="19"/>
-    </row>
-    <row r="66" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B66" s="15"/>
-      <c r="C66" s="15"/>
-      <c r="D66" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E66" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F66" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="G66" s="19"/>
-    </row>
-    <row r="67" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B67" s="15"/>
-      <c r="C67" s="15"/>
-      <c r="D67" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="E67" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F67" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="G67" s="19"/>
-    </row>
-    <row r="68" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B68" s="15"/>
-      <c r="C68" s="15"/>
-      <c r="D68" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="E68" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="F68" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="G68" s="19"/>
+      <c r="G68" s="22"/>
     </row>
     <row r="69" spans="2:7" ht="153" x14ac:dyDescent="0.2">
-      <c r="B69" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="C69" s="11"/>
-      <c r="D69" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="F69" s="11" t="s">
+      <c r="B69" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="G69" s="11" t="s">
+      <c r="C69" s="14"/>
+      <c r="D69" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="E69" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="F69" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="G69" s="14" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B70" s="19"/>
+      <c r="C70" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="D70" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="E70" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="F70" s="14"/>
+      <c r="G70" s="21"/>
+    </row>
+    <row r="71" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B71" s="19"/>
+      <c r="C71" s="20"/>
+      <c r="D71" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="E71" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="F71" s="14"/>
+      <c r="G71" s="21"/>
+    </row>
+    <row r="72" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B72" s="19"/>
+      <c r="C72" s="20"/>
+      <c r="D72" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="F72" s="14"/>
+      <c r="G72" s="21"/>
+    </row>
+    <row r="73" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B73" s="19"/>
+      <c r="C73" s="20"/>
+      <c r="D73" s="14" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="70" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B70" s="16"/>
-      <c r="C70" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="D70" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="E70" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="F70" s="11"/>
-      <c r="G70" s="18"/>
-    </row>
-    <row r="71" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B71" s="16"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="E71" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F71" s="11"/>
-      <c r="G71" s="18"/>
-    </row>
-    <row r="72" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B72" s="16"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="F72" s="11"/>
-      <c r="G72" s="18"/>
-    </row>
-    <row r="73" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B73" s="16"/>
-      <c r="C73" s="17"/>
-      <c r="D73" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="F73" s="11"/>
-      <c r="G73" s="18"/>
+      <c r="E73" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="F73" s="14"/>
+      <c r="G73" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -4242,7 +8514,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4143BDB-FB7E-8843-97AA-51468F0BF63B}">
   <dimension ref="B2:G37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -4524,7 +8796,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94000BF4-24FD-D54C-AF55-ED7D1362D2A5}">
   <dimension ref="B2:G37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -4806,7 +9078,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A334114-9268-4F47-B145-2CAA3A298EB9}">
   <dimension ref="B2:G37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5088,7 +9360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{986A325C-AE41-FC40-A327-F639092A429A}">
   <dimension ref="B2:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5124,13 +9396,13 @@
     </row>
     <row r="4" spans="2:4" ht="17" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -5142,7 +9414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117FE231-9AC0-974C-9988-F8ACFADF5FFE}">
   <dimension ref="B2:G37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/docs/fastapi_r.xlsx
+++ b/docs/fastapi_r.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olegsemenov/Programming/python-learning/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B8F538-A7FE-8447-95B3-2DA1D84F0E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F348055-2464-E049-80E7-B980A516F573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12260" yWindow="0" windowWidth="16540" windowHeight="18000" xr2:uid="{DB6DF64F-D978-E741-A4F2-3D28923A7931}"/>
   </bookViews>
@@ -234,7 +234,2054 @@
         </r>
       </text>
     </comment>
-    <comment ref="B37" authorId="0" shapeId="0" xr:uid="{52272BEA-EF55-1F42-A915-6124A59280F6}">
+    <comment ref="B37" authorId="0" shapeId="0" xr:uid="{D1907CD7-878E-0346-A86B-85916877F0F1}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">get, post, put, delete, patch — </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">определяют </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>CRUD-</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>эндпоинты</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">include_router — </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">делает проект </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>модульным и читаемым</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">add_api_route — </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">полезен при </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>динамической регистрации маршрутов</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">on_event — </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">для </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>инициализации и освобождения ресурсов</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">websocket — </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">при работе с </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>реальным временем</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> (чат, уведомления).</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>get()</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Регистрирует обработчик </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>HTTP GET-</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>запроса.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>@</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">router.get("/users")
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>post()</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Регистрирует обработчик </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>POST-</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>запроса.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>@</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">router.post("/users")
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>put()</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Регистрирует обработчик </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>PUT-</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>запроса.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>@</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">router.put("/users/{id}")
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>delete()</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Регистрирует обработчик </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>DELETE-</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>запроса.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>@</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">router.delete("/users/{id}")
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>patch()</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Регистрирует обработчик </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>PATCH-</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>запроса.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>@</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">router.patch("/users/{id}")
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">include_router()	</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Подключает другой </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">APIRouter </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">к текущему. Используется для модульной структуры.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">						router.include_router(auth_router, prefix="/auth")
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>add_api_route()</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">	</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Программно добавляет маршрут (без декоратора).</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">	</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">router.add_api_route("/info", endpoint=get_info)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>on_event()</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Добавляет обработчик событий приложения (например, при старте).</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">	
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">						</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>@</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">router.on_event("startup")
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>url_path_for()</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Возвращает путь по имени маршрута (удобно при динамической генерации ссылок).
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">						router.url_path_for("read_user", user_id=1)
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F37" authorId="0" shapeId="0" xr:uid="{6EC07672-0B85-3943-8860-8D1C5E089070}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Результат:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">GET /items/ </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">вернёт список элементов.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Эндпоинты автоматически сгруппируются под тегом “</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">items” </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">в </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Swagger UI.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C38" authorId="0" shapeId="0" xr:uid="{94096CA2-FB57-9141-AC4E-76279B2DCAAC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Используются для регистрации эндпоинтов конкретных </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HTTP-</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">методов.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Аналогичны одноимённым методам у </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>FastAPI</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E43" authorId="0" shapeId="0" xr:uid="{7017A811-C0C1-0B4E-8204-5EC8116A2259}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Дополнение:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Аналог @</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">router.get(), @router.post(), </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>но используется, если нужно динамически добавлять пути (например, на основе конфигурации).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{ACF7B46A-3624-C54F-AF52-451AD3C814EF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Дополнение:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Используется редко, когда нужна ручная регистрация без </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">OpenAPI </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">или зависимостей.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Похож на </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Starlette Router.add_route().</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{FF7613C8-3E84-504E-BF56-30EAA59D6A90}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Дополнение:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Позволяет объединять несколько </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>HTTP-</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>методов в одном обработчике.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E46" authorId="0" shapeId="0" xr:uid="{4F518038-8351-2045-910E-F340D5B0B148}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Дополнение:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Аналог @</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">router.websocket() </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">без декоратора.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Используется для динамической регистрации </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>WS-</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>путей.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{ADFB62FC-15C6-1147-9C5D-C88443DDCB68}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Дополнение:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">У каждого подключаемого роутера может быть свой </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">prefix, tags, dependencies, responses.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Позволяет писать код по принципу </t>
+        </r>
+        <r>
+          <rPr>
+            <i/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>“1 модуль = 1 функциональная часть”</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Обычно вызывается в </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">main.py </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">через </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>app.include_router(...).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{2A8BEF6E-0974-C64B-A703-1B32723F8274}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">GET /users/ </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>вернёт список пользователей.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F50" authorId="0" shapeId="0" xr:uid="{FFDF18D6-A0BA-B741-B2D2-8197211031C9}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Все файлы из папки </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">static </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>будут доступны по пути /</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="18"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>static/...</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G50" authorId="0" shapeId="0" xr:uid="{5BBCE5EB-5DF3-214C-B8F4-189C657130A8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Все файлы из папки </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">static </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>будут доступны по пути /</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>static/...</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{797FFEB0-1BDB-DC45-96C4-3633B4A0E0AF}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Позволяет роутеру обращаться к контексту приложения (например, к </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">middleware, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">событиям, конфигурации).
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Используется редко в прикладном коде, но полезен для расширений и интеграций.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{ACB31994-ABD7-724E-8CE3-9C0F81833EE6}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>GET /ping → {"app_name": "MyApp"}</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E53" authorId="0" shapeId="0" xr:uid="{063D4608-F1FB-E64D-A80B-3543EFCB31A1}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Выполняется </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>до</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> обработки первого запроса (</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">startup).
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Или </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>после завершения работы сервера</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> (</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">shutdown).
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Работает и на уровне </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">FastAPI, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">и на уровне </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>APIRouter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F56" authorId="0" shapeId="0" xr:uid="{582A033B-0E38-7644-B973-7F589A7A9A1E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Результат:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">При запуске приложения выведется:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Starting up
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">А при остановке:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Shutting down</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F57" authorId="0" shapeId="0" xr:uid="{FEB292ED-75A5-8941-8DE9-FE9C8E82C5C1}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>GET /link → {"link": "/users/5"}</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{7A9F1DDD-F5A7-7648-81F8-1FAB3EE4476C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>GET /check/2 → {"detail": "Not Found"}</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{D2024832-91A7-EE44-8F61-220DD6EE415C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Этот роут будет обрабатываться </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>только</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> если запрос пришёл на домен </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">admin.example.com.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B60" authorId="0" shapeId="0" xr:uid="{52272BEA-EF55-1F42-A915-6124A59280F6}">
       <text>
         <r>
           <rPr>
@@ -449,7 +2496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D38" authorId="0" shapeId="0" xr:uid="{6517C201-1D9F-604C-BB43-58D412DE9651}">
+    <comment ref="D61" authorId="0" shapeId="0" xr:uid="{6517C201-1D9F-604C-BB43-58D412DE9651}">
       <text>
         <r>
           <rPr>
@@ -496,7 +2543,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B45" authorId="0" shapeId="0" xr:uid="{3F9C09F8-6073-9042-BC4B-3EB85A669FF0}">
+    <comment ref="B68" authorId="0" shapeId="0" xr:uid="{3F9C09F8-6073-9042-BC4B-3EB85A669FF0}">
       <text>
         <r>
           <rPr>
@@ -647,7 +2694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D45" authorId="0" shapeId="0" xr:uid="{529E9708-50AC-6C4D-802E-FB35FCABDD60}">
+    <comment ref="D68" authorId="0" shapeId="0" xr:uid="{529E9708-50AC-6C4D-802E-FB35FCABDD60}">
       <text>
         <r>
           <rPr>
@@ -924,7 +2971,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G46" authorId="0" shapeId="0" xr:uid="{57DF489B-7F6A-C247-8161-6B5F41C4A2A8}">
+    <comment ref="G69" authorId="0" shapeId="0" xr:uid="{57DF489B-7F6A-C247-8161-6B5F41C4A2A8}">
       <text>
         <r>
           <rPr>
@@ -1606,7 +3653,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B65" authorId="0" shapeId="0" xr:uid="{675AD5D9-5A3C-5142-B786-623C00472942}">
+    <comment ref="B88" authorId="0" shapeId="0" xr:uid="{675AD5D9-5A3C-5142-B786-623C00472942}">
       <text>
         <r>
           <rPr>
@@ -1729,6 +3776,642 @@
             <scheme val="minor"/>
           </rPr>
           <t>, когда ты кастомизируешь сериализацию или работаешь с нетиповыми объектами.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{4F116D38-60DF-8D41-81E8-4CBFF51643EF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Основные атрибуты и свойства
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Атрибут</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Тип</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Описание</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>request.method</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>str</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		Метод запроса ("</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">GET", "POST", …).
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>request.url</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>starlette.datastructures.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">	Полный </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">URL </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">запроса.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>request.base_url</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">	</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>URL</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		Базовый </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">URL </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">без пути.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>request.headers</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">	</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Headers</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		Заголовки запроса.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>request.cookies</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>dict</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Cookies, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">отправленные клиентом.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>request.query_params</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">	</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>QueryParams</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		Параметры строки запроса (?</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">key=value).
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>request.path_params</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">	</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>dict</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		Параметры пути (/</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">items/{id}).
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>request.client</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>tuple(ip, port)</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>IP-</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">адрес клиента.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>request.app</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>FastAPI</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		Ссылка на текущее приложение.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>request.state</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>object</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">		Контейнер для пользовательских данных (можно хранить что угодно в течение 				запроса).
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B146" authorId="0" shapeId="0" xr:uid="{E36A3629-E2CB-FD4F-8631-B6F8A84CA1AD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Microsoft Office User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
         </r>
       </text>
     </comment>
@@ -2484,7 +5167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="837">
   <si>
     <t>Термин</t>
   </si>
@@ -4716,12 +7399,1583 @@
         return Response(content=html_content, media_type="text/html")
     return JSONResponse(content=data)</t>
   </si>
+  <si>
+    <t>APIRouter</t>
+  </si>
+  <si>
+    <t>APIRouter — это класс FastAPI, предназначенный для организации маршрутов в модули. Позволяет структурировать приложение, разделяя эндпоинты по функциональным областям (пользователи, товары, заказы и т. д.).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Помогает избегать перегрузки основного файла main.py.
+	•	Поддерживает параметры prefix, tags, dependencies, responses.
+	•	Можно подключать к основному приложению через app.include_router(router).
+	•	Удобен при создании модульной архитектуры или микросервисов.</t>
+  </si>
+  <si>
+    <t>from fastapi import APIRouter
+router = APIRouter(
+    prefix="/users",
+    tags=["users"],
+    responses={404: {"description": "Not found"}},
+)</t>
+  </si>
+  <si>
+    <t>from fastapi import FastAPI, APIRouter
+router = APIRouter(prefix="/items", tags=["items"])
+@router.get("/")
+def read_items():
+    return [{"item_id": 1, "name": "Book"}, {"item_id": 2, "name": "Pen"}]
+app = FastAPI()
+app.include_router(router)</t>
+  </si>
+  <si>
+    <t>Методы HTTP (для определения маршрутов)</t>
+  </si>
+  <si>
+    <t>Управление маршрутами и WebSocket’ами</t>
+  </si>
+  <si>
+    <t>Подключение и вложенность</t>
+  </si>
+  <si>
+    <t>События жизненного цикла</t>
+  </si>
+  <si>
+    <t>Утилиты и навигация</t>
+  </si>
+  <si>
+    <t>get()</t>
+  </si>
+  <si>
+    <t>Регистрирует обработчик HTTP GET-запроса.</t>
+  </si>
+  <si>
+    <t>@router.get("/users")</t>
+  </si>
+  <si>
+    <t>post()</t>
+  </si>
+  <si>
+    <t>@router.post("/users")</t>
+  </si>
+  <si>
+    <t>put()</t>
+  </si>
+  <si>
+    <t>Регистрирует обработчик PUT-запроса.</t>
+  </si>
+  <si>
+    <t>@router.put("/users/{id}")</t>
+  </si>
+  <si>
+    <t>delete()</t>
+  </si>
+  <si>
+    <t>Регистрирует обработчик DELETE-запроса.</t>
+  </si>
+  <si>
+    <t>@router.delete("/users/{id}")</t>
+  </si>
+  <si>
+    <t>patch()</t>
+  </si>
+  <si>
+    <t>Регистрирует обработчик PATCH-запроса.</t>
+  </si>
+  <si>
+    <t>@router.patch("/users/{id}")</t>
+  </si>
+  <si>
+    <t>Определение:
+Регистрирует HTTP-маршрут программно, без использования декоратора.</t>
+  </si>
+  <si>
+    <t>def info():
+    return {"msg": "Hello"}
+router.add_api_route("/info", info, methods=["GET"])</t>
+  </si>
+  <si>
+    <t>Более низкоуровневый способ добавить маршрут — минует часть FastAPI-специфики (например, валидацию моделей).</t>
+  </si>
+  <si>
+    <t>async def homepage(request):
+    return PlainTextResponse("Welcome")
+router.add_route("/", homepage, methods=["GET"])</t>
+  </si>
+  <si>
+    <r>
+      <t>router.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add_api_route</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(path, endpoint, methods=["GET"], response_model=Model)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>router.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add_route</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(path, endpoint, methods=["GET"])</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>@router.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>api_route</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>("/path", methods=["GET", "POST"])</t>
+    </r>
+  </si>
+  <si>
+    <t>Определение:
+Декоратор для добавления маршрутов с несколькими методами.</t>
+  </si>
+  <si>
+    <t>@router.api_route("/items", methods=["GET", "POST"])
+def manage_items():
+    return {"action": "handled"}</t>
+  </si>
+  <si>
+    <r>
+      <t>router.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add_websocket_route</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(path, endpoint)</t>
+    </r>
+  </si>
+  <si>
+    <t>Добавляет маршрут WebSocket-соединения программно.</t>
+  </si>
+  <si>
+    <t>async def websocket_endpoint(websocket: WebSocket):
+    await websocket.accept()
+    await websocket.send_text("Connected")
+router.add_websocket_route("/ws", websocket_endpoint)</t>
+  </si>
+  <si>
+    <r>
+      <t>@router.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>websocket</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>("/ws")
+async def websocket_endpoint(websocket: WebSocket):
+    ...</t>
+    </r>
+  </si>
+  <si>
+    <t>Декоратор для регистрации WebSocket-маршрута.
+Дополнение:
+	•	Используется чаще всего (удобнее, чем add_websocket_route).
+	•	Позволяет создавать чаты, live-обновления, уведомления.</t>
+  </si>
+  <si>
+    <t>@router.websocket("/ws")
+async def websocket_endpoint(ws: WebSocket):
+    await ws.accept()
+    await ws.send_text("Hello WebSocket!")</t>
+  </si>
+  <si>
+    <t>Более низкоуровневый аналог websocket(). Позволяет объявить маршрут вручную без декоратора.
+Дополнение:
+	•	Используется редко, в основном внутри фреймворка или для генерации роутов через функции.</t>
+  </si>
+  <si>
+    <r>
+      <t>router.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>websocket_route</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(path)</t>
+    </r>
+  </si>
+  <si>
+    <t>@router.websocket_route("/stream")
+async def stream(ws: WebSocket):
+    await ws.accept()
+    await ws.send_text("stream started")</t>
+  </si>
+  <si>
+    <r>
+      <t>router.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>include_router</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(other_router, prefix="/path", tags=["group"])</t>
+    </r>
+  </si>
+  <si>
+    <t>Подключает другой экземпляр APIRouter (или несколько) к текущему роутеру или приложению FastAPI.
+Используется для модульной структуры приложения — деления логики по файлам и областям ответственности.</t>
+  </si>
+  <si>
+    <t># users.py
+from fastapi import APIRouter
+router = APIRouter(prefix="/users", tags=["users"])
+@router.get("/")
+def get_users():
+    return [{"name": "Alice"}, {"name": "Bob"}]
+# main.py
+from fastapi import FastAPI
+from .users import router as users_router
+app = FastAPI()
+app.include_router(users_router)</t>
+  </si>
+  <si>
+    <r>
+      <t>app.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>("/static", StaticFiles(directory="static"), name="static")</t>
+    </r>
+  </si>
+  <si>
+    <t>Монтирует внешнее ASGI-приложение (например, Starlette-приложение, FastAPI-приложение или StaticFiles) внутрь текущего приложения.
+	•	Используется для встраивания подприложений, например, документации, фронтенда или админ-панели.
+	•	mount работает на уровне ASGI, то есть не только HTTP.
+	•	Можно подключать другие FastAPI-приложения как подмодули.</t>
+  </si>
+  <si>
+    <t>from fastapi import FastAPI
+from fastapi.staticfiles import StaticFiles
+app = FastAPI()
+app.mount("/static", StaticFiles(directory="static"), name="static")</t>
+  </si>
+  <si>
+    <t>Ссылка на объект приложения, к которому подключён данный APIRouter.
+Доступен после того, как роутер был включён в FastAPI() с помощью include_router().</t>
+  </si>
+  <si>
+    <t>from fastapi import APIRouter, FastAPI
+router = APIRouter()
+@router.get("/ping")
+def ping():
+    return {"app_name": router.app.title}
+app = FastAPI(title="MyApp")
+app.include_router(router)</t>
+  </si>
+  <si>
+    <r>
+      <t>router.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>app</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>router.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add_event</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_handler(event_type, func)</t>
+    </r>
+  </si>
+  <si>
+    <t>Добавляет обработчик событий приложения вручную (например, при старте или завершении).
+Это низкоуровневый способ регистрации событий.
+Дополнение:
+	•	event_type может быть "startup" или "shutdown".
+	•	Аналог декоратора @router.on_event(), но используется программно (например, при динамическом подключении событий).</t>
+  </si>
+  <si>
+    <t>def init_db():
+    print("Database connected")
+router.add_event_handler("startup", init_db)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@router.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>on_event</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>("startup")
+async def startup_event():
+    ...</t>
+    </r>
+  </si>
+  <si>
+    <t>Декоратор для регистрации функции, выполняемой при определённом событии жизненного цикла (startup или shutdown).
+Используется чаще всего.</t>
+  </si>
+  <si>
+    <t>@router.on_event("startup")
+async def connect_db():
+    print("Connecting to database...")
+@router.on_event("shutdown")
+async def disconnect_db():
+    print("Disconnecting database...")</t>
+  </si>
+  <si>
+    <r>
+      <t>@router.on_event("</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>startup</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>")
+async def startup_func():
+    ...</t>
+    </r>
+  </si>
+  <si>
+    <t>Событие, которое выполняется один раз при запуске приложения.
+Обычно используется для инициализации ресурсов (подключение к БД, загрузка конфигурации).
+Дополнение:
+	•	Выполняется перед началом обработки HTTP-запросов.
+	•	Подходит для асинхронных и синхронных функций.</t>
+  </si>
+  <si>
+    <t>@router.on_event("startup")
+async def startup_event():
+    print("App started")</t>
+  </si>
+  <si>
+    <r>
+      <t>@router.on_event("</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shutdown</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>")
+async def shutdown_func():
+    ...</t>
+    </r>
+  </si>
+  <si>
+    <t>Событие, выполняемое при завершении приложения.
+Используется для освобождения ресурсов (закрытие соединений, сохранение состояния и т.п.).
+	•	Выполняется перед остановкой Uvicorn / Gunicorn.
+	•	Гарантирует корректное завершение асинхронных задач.</t>
+  </si>
+  <si>
+    <t>@router.on_event("shutdown")
+async def shutdown_event():
+    print("App is shutting down")</t>
+  </si>
+  <si>
+    <t>Определение:
+Современная альтернатива on_event.
+Позволяет описать всю логику жизненного цикла (startup и shutdown) в виде единого контекстного менеджера.
+Дополнение:
+	•	Более читаем и детерминирован, чем пара startup/shutdown.
+	•	Поддерживается с FastAPI ≥ 0.95.
+	•	Рекомендуется использовать в новых проектах.</t>
+  </si>
+  <si>
+    <t>from fastapi import FastAPI
+from contextlib import asynccontextmanager
+@asynccontextmanager
+async def lifespan(app: FastAPI):
+    print("Starting up")
+    yield
+    print("Shutting down")
+app = FastAPI(lifespan=lifespan)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">from contextlib import asynccontextmanager
+@asynccontextmanager
+async def </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lifespan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(app: FastAPI):
+    print("Startup actions")
+    yield
+    print("Shutdown actions")
+app = FastAPI(lifespan=lifespan)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>router.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>url_path_for</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(name: str, **path_params)</t>
+    </r>
+  </si>
+  <si>
+    <t>Возвращает URL-путь для маршрута по его имени.
+Позволяет динамически строить ссылки внутри приложения, не “зашивая” пути вручную.
+	•	Работает только после регистрации маршрута (@router.get(..., name="...")).
+	•	Учитывает prefix роутера и параметры пути.
+	•	Полезен для генерации ссылок в ответах API или редиректах.</t>
+  </si>
+  <si>
+    <t>@router.get("/users/{user_id}", name="get_user")
+def get_user(user_id: int):
+    return {"user_id": user_id}
+@router.get("/link")
+def get_link():
+    url = router.url_path_for("get_user", user_id=5)
+    return {"link": url}</t>
+  </si>
+  <si>
+    <t>router.not_found(request)</t>
+  </si>
+  <si>
+    <t>Возвращает стандартный ответ 404 Not Found для случаев, когда путь не найден.
+Обычно используется внутри FastAPI автоматически, но можно вызвать вручную для кастомной обработки.
+	•	Является функцией-обработчиком, возвращающей Response(status_code=404).
+	•	Может быть переопределён при создании собственного обработчика ошибок.
+	•	В чистом приложении вызывается редко, чаще — во фреймворк-подсистеме.</t>
+  </si>
+  <si>
+    <t>from fastapi import Request
+from fastapi.responses import JSONResponse
+@router.get("/check/{item_id}")
+async def check_item(item_id: int):
+    if item_id != 1:
+        return await router.not_found(Request({"type": "http"}))
+    return {"item_id": 1}</t>
+  </si>
+  <si>
+    <t>router = APIRouter(host="example.com")</t>
+  </si>
+  <si>
+    <t>Позволяет ограничить работу роутера только для определённого хоста (доменного имени).
+Используется для маршрутизации запросов на разные поддомены или домены.
+	•	Удобно при работе с мультидоменными API (например, api.example.com и admin.example.com).
+	•	Работает на уровне Starlette.
+	•	Можно использовать регулярные выражения в имени хоста.</t>
+  </si>
+  <si>
+    <t>router = APIRouter(host="admin.example.com")
+@router.get("/dashboard")
+def admin_dashboard():
+    return {"msg": "Admin zone"}</t>
+  </si>
+  <si>
+    <t>Input Layer</t>
+  </si>
+  <si>
+    <t>Request</t>
+  </si>
+  <si>
+    <t>UploadFile</t>
+  </si>
+  <si>
+    <t>Depends</t>
+  </si>
+  <si>
+    <t>from fastapi import Request</t>
+  </si>
+  <si>
+    <t>fastapi.Request — это класс, представляющий входящий HTTP-запрос в FastAPI. Он предоставляет доступ к данным запроса: методу (GET, POST и т. д.), заголовкам, телу, cookies, URL-параметрам и т. д.</t>
+  </si>
+  <si>
+    <t>from fastapi import FastAPI, Request
+app = FastAPI()
+@app.post("/items/")
+async def create_item(request: Request):
+    data = await request.json()  # тело запроса как dict
+    user_agent = request.headers.get("user-agent")
+    client_host = request.client.host
+    return {
+        "received_data": data,
+        "user_agent": user_agent,
+        "client_host": client_host
+    }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	•	Request часто используется для доступа к данным, не описанным в параметрах функции, например заголовкам, телу произвольного формата или контексту приложения.
+	•	В middleware можно использовать request.state для передачи данных между компонентами.
+	•	Request применяется в Dependency Injection, например:
+Основные атрибуты и свойства</t>
+  </si>
+  <si>
+    <t>Базовые свойства запроса</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>HTTP-метод запроса.</t>
+  </si>
+  <si>
+    <t>GET, POST, PUT</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>Полный URL запроса.</t>
+  </si>
+  <si>
+    <t>http://127.0.0.1:8000/items/1?q=book</t>
+  </si>
+  <si>
+    <t>base_url</t>
+  </si>
+  <si>
+    <t>Базовый URL без пути.</t>
+  </si>
+  <si>
+    <t>http://127.0.0.1:8000/</t>
+  </si>
+  <si>
+    <t>Ссылка на текущее приложение.</t>
+  </si>
+  <si>
+    <t>request.app.title</t>
+  </si>
+  <si>
+    <t>client</t>
+  </si>
+  <si>
+    <t>IP и порт клиента.</t>
+  </si>
+  <si>
+    <t>('127.0.0.1', 56743)</t>
+  </si>
+  <si>
+    <t>path_params</t>
+  </si>
+  <si>
+    <t>Значения параметров пути.</t>
+  </si>
+  <si>
+    <t>{"item_id": 5}</t>
+  </si>
+  <si>
+    <t>query_params</t>
+  </si>
+  <si>
+    <t>Параметры из ?key=value.</t>
+  </si>
+  <si>
+    <t>request.query_params["q"]</t>
+  </si>
+  <si>
+    <t>@app.get("/users/{user_id}")
+async def get_user(user_id: int, request: Request):
+    return {
+        "method": request.method,
+        "url": str(request.url),
+        "client": request.client.host,
+        "params": dict(request.query_params),
+        "path": request.path_params
+    }</t>
+  </si>
+  <si>
+    <t>Метаданные и данные клиента</t>
+  </si>
+  <si>
+    <t>Все HTTP-заголовки (Authorization, User-Agent, и т. д.).</t>
+  </si>
+  <si>
+    <t>cookies</t>
+  </si>
+  <si>
+    <t>Словарь cookies, отправленных клиентом.</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>Объект пользователя (если реализована аутентификация).</t>
+  </si>
+  <si>
+    <t>auth</t>
+  </si>
+  <si>
+    <t>Информация об авторизации (например, BasicAuthCredentials).</t>
+  </si>
+  <si>
+    <t>session</t>
+  </si>
+  <si>
+    <t>Сессия пользователя (если включена middleware для сессий).</t>
+  </si>
+  <si>
+    <t>@app.get("/info")
+async def client_info(request: Request):
+    return {
+        "headers": dict(request.headers),
+        "cookies": request.cookies,
+        "user_agent": request.headers.get("user-agent")
+    }</t>
+  </si>
+  <si>
+    <t>await body()</t>
+  </si>
+  <si>
+    <t>bytes</t>
+  </si>
+  <si>
+    <t>Получить сырое тело запроса.</t>
+  </si>
+  <si>
+    <t>await json()</t>
+  </si>
+  <si>
+    <t>Преобразовать тело в JSON.</t>
+  </si>
+  <si>
+    <t>await form()</t>
+  </si>
+  <si>
+    <t>FormData</t>
+  </si>
+  <si>
+    <t>Прочитать данные формы.</t>
+  </si>
+  <si>
+    <t>await stream()</t>
+  </si>
+  <si>
+    <t>AsyncIterator</t>
+  </si>
+  <si>
+    <t>Асинхронный доступ к потоку тела</t>
+  </si>
+  <si>
+    <t>Тело запроса и формы</t>
+  </si>
+  <si>
+    <t>@app.post("/upload/")
+async def upload_data(request: Request):
+    body = await request.body()  # bytes
+    try:
+        data = await request.json()  # dict
+    except Exception:
+        data = None
+    return {"size": len(body), "json": data}</t>
+  </si>
+  <si>
+    <t>Работа с состоянием и контекстом</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>Контейнер для пользовательских данных на время запроса.</t>
+  </si>
+  <si>
+    <t>@app.middleware("http")
+async def add_request_id(request: Request, call_next):
+    request.state.request_id = "abc-123"
+    response = await call_next(request)
+    response.headers["X-Request-ID"] = request.state.request_id
+    return response</t>
+  </si>
+  <si>
+    <t>Методы и служебные функции</t>
+  </si>
+  <si>
+    <t>get(key)</t>
+  </si>
+  <si>
+    <t>Получить значение параметра из query/path/формы.</t>
+  </si>
+  <si>
+    <t>keys(), items(), values()</t>
+  </si>
+  <si>
+    <t>Итерация по данным запроса.</t>
+  </si>
+  <si>
+    <t>url_for(name, **path_params)</t>
+  </si>
+  <si>
+    <t>Сформировать URL по имени маршрута.</t>
+  </si>
+  <si>
+    <t>is_disconnected()</t>
+  </si>
+  <si>
+    <t>Проверить, закрыл ли клиент соединение.</t>
+  </si>
+  <si>
+    <t>send_push_promise()</t>
+  </si>
+  <si>
+    <t>HTTP/2 push (используется редко).</t>
+  </si>
+  <si>
+    <t>close()</t>
+  </si>
+  <si>
+    <t>Явно закрывает запрос (вручную почти не вызывается).</t>
+  </si>
+  <si>
+    <t>@app.get("/users/{id}", name="get_user")
+async def get_user(id: int):
+    return {"user_id": id}
+@app.get("/links")
+async def links(request: Request):
+    return {"user_url": request.url_for("get_user", id=42)}</t>
+  </si>
+  <si>
+    <t>@app.post("/process/{item_id}")
+async def process_item(item_id: int, request: Request):
+    json_data = await request.json()
+    client_ip = request.client.host
+    headers = dict(request.headers)
+    user_agent = headers.get("user-agent")
+    return {
+        "path": request.url.path,
+        "method": request.method,
+        "params": request.query_params,
+        "json": json_data,
+        "client_ip": client_ip,
+        "user_agent": user_agent,
+    }</t>
+  </si>
+  <si>
+    <t>Body</t>
+  </si>
+  <si>
+    <t>from fastapi import Body
+@app.post("/items/")
+async def create_item(
+    name: str = Body(...),
+    description: str = Body(None),
+    price: float = Body(..., gt=0)
+):
+    return {"name": name, "description": description, "price": price}</t>
+  </si>
+  <si>
+    <t>Body — специальный “маркер” для FastAPI, указывающий, что параметр должен быть получен из тела запроса (body), обычно в формате JSON.
+Позволяет:
+	•	задавать валидацию (через Pydantic);
+	•	определять обязательные / необязательные поля;
+	•	добавлять метаданные (описания, примеры).</t>
+  </si>
+  <si>
+    <t>Параметры Body:
+	•	default — значение по умолчанию (... означает обязательный);
+	•	embed=True — оборачивает тело в объект (например, {"item": {...}});
+	•	example / examples — пример для OpenAPI;
+	•	media_type — MIME-тип (application/json по умолчанию).</t>
+  </si>
+  <si>
+    <t>@app.post("/login/")
+async def login(data: dict = Body(..., embed=True)):
+    return data
+# JSON: {"data": {"username": "oleg", "password": "123"}}</t>
+  </si>
+  <si>
+    <t>Form</t>
+  </si>
+  <si>
+    <t>from fastapi import Form
+@app.post("/login/")
+async def login(username: str = Form(...), password: str = Form(...)):
+    return {"username": username}</t>
+  </si>
+  <si>
+    <t>Form сообщает FastAPI, что данные приходят из HTML-формы (application/x-www-form-urlencoded).
+Используется для отправки данных через формы, не через JSON.</t>
+  </si>
+  <si>
+    <t>➕ Дополнение
+	•	Требует установить пакет python-multipart (pip install python-multipart).
+	•	Поддерживает валидацию аналогично Body.
+	•	Часто используется вместе с File для загрузки файлов и текстовых полей одновременно.</t>
+  </si>
+  <si>
+    <t>@app.post("/register/")
+async def register(
+    name: str = Form(...),
+    email: str = Form(...),
+    age: int = Form(...)
+):
+    return {"user": name, "email": email, "age": age}</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>from fastapi import File, UploadFile
+@app.post("/upload/")
+async def upload(file: UploadFile = File(...)):
+    contents = await file.read()
+    return {"filename": file.filename, "size": len(contents)}</t>
+  </si>
+  <si>
+    <t>File используется для получения файлов, отправленных клиентом (через multipart/form-data).
+FastAPI автоматически обрабатывает бинарные данные и предоставляет объект UploadFile.</t>
+  </si>
+  <si>
+    <t>UploadFile имеет атрибуты:
+	.read(), .write(), .seek() — методы работы с потоком.
+	•	Можно загружать несколько файлов: List[UploadFile] = File(...).</t>
+  </si>
+  <si>
+    <t>JSON, raw body</t>
+  </si>
+  <si>
+    <t>application/json</t>
+  </si>
+  <si>
+    <t>dict / obj</t>
+  </si>
+  <si>
+    <t>API-запросы</t>
+  </si>
+  <si>
+    <t>HTML-формы</t>
+  </si>
+  <si>
+    <t>application/x-www-form-urlencoded</t>
+  </si>
+  <si>
+    <t>str / int / bool</t>
+  </si>
+  <si>
+    <t>Логины, формы</t>
+  </si>
+  <si>
+    <t>Файлы</t>
+  </si>
+  <si>
+    <t>multipart/form-data</t>
+  </si>
+  <si>
+    <t>Загрузка файлов</t>
+  </si>
+  <si>
+    <t>from typing import List
+from fastapi import File, UploadFile
+@app.post("/multi-upload/")
+async def upload_files(files: List[UploadFile] = File(...)):
+    return {"filenames": [f.filename for f in files]}</t>
+  </si>
+  <si>
+    <t>Query</t>
+  </si>
+  <si>
+    <t>from fastapi import Query
+@app.get("/items/")
+async def read_items(q: str = Query(None, min_length=3, max_length=50, regex="^item")):
+    return {"query": q}</t>
+  </si>
+  <si>
+    <t>Query указывает, что значение параметра берётся из строки запроса (?q=value).
+Позволяет задавать валидацию, значения по умолчанию, описание и пример.</t>
+  </si>
+  <si>
+    <t>Аргументы:
+	•	default: значение по умолчанию (... — обязательный параметр)
+	•	alias: альтернативное имя параметра (q ↔ query-string)
+	•	title, description: для документации
+	•	min_length, max_length: длина строки
+	•	ge, le, gt, lt: числовые ограничения
+	•	regex: регулярное выражение
+	•	deprecated=True: помечает параметр устаревшим</t>
+  </si>
+  <si>
+    <t>@app.get("/search/")
+async def search(
+    keyword: str = Query(..., min_length=2, description="Поисковый запрос"),
+    limit: int = Query(10, ge=1, le=50)
+):
+    return {"keyword": keyword, "limit": limit}</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>from fastapi import Path
+@app.get("/items/{item_id}")
+async def get_item(item_id: int = Path(..., ge=1)):
+    return {"item_id": item_id}</t>
+  </si>
+  <si>
+    <t>Path обозначает параметр, извлекаемый из пути URL (/items/42).
+Поддерживает ту же валидацию, что и Query, но используется исключительно для переменных пути.</t>
+  </si>
+  <si>
+    <t>Аргументы:
+	•	default — значение по умолчанию (обычно ... — обязательное);
+	•	title, description — для документации;
+	•	ge, le, regex — числовые и строковые ограничения;
+	•	alias — альтернативное имя (редко используется в пути).</t>
+  </si>
+  <si>
+    <t>@app.get("/users/{user_id}")
+async def read_user(user_id: int = Path(..., description="ID пользователя", ge=1)):
+    return {"user_id": user_id}</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>from fastapi import Header
+@app.get("/agent/")
+async def get_agent(user_agent: str = Header(None)):
+    return {"User-Agent": user_agent}</t>
+  </si>
+  <si>
+    <t>Header сообщает FastAPI, что параметр должен быть взят из заголовков HTTP.
+FastAPI автоматически преобразует имя переменной из snake_case в заголовочный формат (user_agent → User-Agent).</t>
+  </si>
+  <si>
+    <t>Аргументы:
+	•	convert_underscores=True — включает авто-конвертацию _ в -
+	•	default, alias, description — аналогично Query
+	•	deprecated=True — для документации</t>
+  </si>
+  <si>
+    <t>@app.get("/token/")
+async def read_token(x_token: str = Header(...)):
+    return {"X-Token": x_token}</t>
+  </si>
+  <si>
+    <t>Cookie</t>
+  </si>
+  <si>
+    <t>from fastapi import Cookie
+@app.get("/preferences/")
+async def read_cookies(theme: str = Cookie(None)):
+    return {"theme": theme}</t>
+  </si>
+  <si>
+    <t>Cookie сообщает FastAPI, что параметр берётся из cookies запроса.
+Поддерживает все стандартные параметры валидации (default, alias, description и т.д.).</t>
+  </si>
+  <si>
+    <t>➕ Дополнение
+	•	Используется для доступа к cookie, отправленным клиентом.
+	•	Часто применяется для аутентификации сессий.</t>
+  </si>
+  <si>
+    <t>@app.get("/user/")
+async def read_user(session_id: str = Cookie(..., description="ID сессии пользователя")):
+    return {"session_id": session_id}</t>
+  </si>
+  <si>
+    <t>строка запроса</t>
+  </si>
+  <si>
+    <t>/items?q=apple</t>
+  </si>
+  <si>
+    <t>фильтры, поиск</t>
+  </si>
+  <si>
+    <t>путь запроса</t>
+  </si>
+  <si>
+    <t>/items/42</t>
+  </si>
+  <si>
+    <t>доступ к ресурсу</t>
+  </si>
+  <si>
+    <t>заголовок запроса</t>
+  </si>
+  <si>
+    <t>Authorization: Bearer ...</t>
+  </si>
+  <si>
+    <t>токены, агенты</t>
+  </si>
+  <si>
+    <t>session_id=abc123</t>
+  </si>
+  <si>
+    <t>сессии, предпочтения</t>
+  </si>
+  <si>
+    <t>UploadFile — это объект-обёртка над временным файлом, который создаётся FastAPI при загрузке данных через multipart/form-data.
+Он предоставляет асинхронные методы для чтения, записи и перемещения файла, не загружая его полностью в память (работает через SpooledTemporaryFile).</t>
+  </si>
+  <si>
+    <t>from fastapi import UploadFile, File
+@app.post("/upload/")
+async def upload(file: UploadFile = File(...)):
+    contents = await file.read()
+    return {"filename": file.filename, "size": len(contents)}</t>
+  </si>
+  <si>
+    <t>file</t>
+  </si>
+  <si>
+    <t>_io.BufferedRandom</t>
+  </si>
+  <si>
+    <t>Файловый объект, с которым можно работать напрямую (file.read(), file.write(), file.seek()).</t>
+  </si>
+  <si>
+    <t>filename</t>
+  </si>
+  <si>
+    <t>Имя загружаемого файла (например, "photo.jpg").</t>
+  </si>
+  <si>
+    <t>content_type</t>
+  </si>
+  <si>
+    <t>MIME-тип (например, "image/png", "text/plain").</t>
+  </si>
+  <si>
+    <t>Headers</t>
+  </si>
+  <si>
+    <t>Заголовки, относящиеся к этому файлу (например, Content-Disposition).</t>
+  </si>
+  <si>
+    <t>Основные атрибуты</t>
+  </si>
+  <si>
+    <t>Асинхронные методы</t>
+  </si>
+  <si>
+    <t>await file.read(size: int = -1)</t>
+  </si>
+  <si>
+    <t>Читает содержимое файла (всё или указанное количество байт).</t>
+  </si>
+  <si>
+    <t>await file.write(data: bytes)</t>
+  </si>
+  <si>
+    <t>Записывает данные в файл.</t>
+  </si>
+  <si>
+    <t>await file.seek(offset: int)</t>
+  </si>
+  <si>
+    <t>Перемещает курсор чтения/записи (например, await file.seek(0) для начала).</t>
+  </si>
+  <si>
+    <t>await file.close()</t>
+  </si>
+  <si>
+    <t>Закрывает файл и освобождает ресурсы.</t>
+  </si>
+  <si>
+    <t>@app.post("/uploadfile/")
+async def upload_file(file: UploadFile = File(...)):
+    content = await file.read()
+    return {
+        "filename": file.filename,
+        "type": file.content_type,
+        "size": len(content)
+    }</t>
+  </si>
+  <si>
+    <t>from typing import List
+@app.post("/upload-multiple/")
+async def upload_multiple(files: List[UploadFile] = File(...)):
+    return {"filenames": [f.filename for f in files]}</t>
+  </si>
+  <si>
+    <t>import shutil
+@app.post("/savefile/")
+async def save_file(file: UploadFile = File(...)):
+    file_path = f"uploads/{file.filename}"
+    with open(file_path, "wb") as buffer:
+        shutil.copyfileobj(file.file, buffer)
+    return {"saved_to": file_path}</t>
+  </si>
+  <si>
+    <t>@app.post("/binary/")
+async def handle_binary(file: UploadFile = File(...)):
+    data = await file.read()
+    first_bytes = data[:10]
+    return {"filename": file.filename, "first_bytes": list(first_bytes)}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	•	Используется только с File() — иначе FastAPI не распознает multipart-запрос.
+	•	Работает эффективно, так как не загружает весь файл в память.
+	•	Для загрузки файлов требуется библиотека:
+pip install python-multipart
+	•	В отличие от bytes = File(...), UploadFile — предпочтительнее, т.к. позволяет работать с потоком и не блокирует памят</t>
+  </si>
+  <si>
+    <t>Особенность</t>
+  </si>
+  <si>
+    <t>File(bytes)</t>
+  </si>
+  <si>
+    <t>Тип данных</t>
+  </si>
+  <si>
+    <t>файловый объект</t>
+  </si>
+  <si>
+    <t>Хранение</t>
+  </si>
+  <si>
+    <t>целиком в памяти</t>
+  </si>
+  <si>
+    <t>во временном файле</t>
+  </si>
+  <si>
+    <t>Скорость</t>
+  </si>
+  <si>
+    <t>ниже для больших файлов</t>
+  </si>
+  <si>
+    <t>высокая, потоковая</t>
+  </si>
+  <si>
+    <t>Использование</t>
+  </si>
+  <si>
+    <t>мелкие данные</t>
+  </si>
+  <si>
+    <t>крупные файлы, изображения, видео</t>
+  </si>
+  <si>
+    <t>from fastapi import Depends, FastAPI
+app = FastAPI()
+def get_token_header(x_token: str):
+    if x_token != "secret-token":
+        raise HTTPException(status_code=400, detail="Invalid token")
+    return x_token
+@app.get("/items/")
+async def read_items(token: str = Depends(get_token_header)):
+    return {"token": token}</t>
+  </si>
+  <si>
+    <t>Depends — это механизм внедрения зависимостей в FastAPI.
+Он позволяет автоматически вызывать функции-зависимости, обрабатывать результаты и передавать их в эндпоинты, другие зависимости или middleware.
+Иными словами, Depends() сообщает FastAPI:
+“Перед вызовом этой функции, сначала вызови указанную зависимость и передай её результат в аргумент”.</t>
+  </si>
+  <si>
+    <t>Depends используется для:
+	•	авторизации и проверки токенов,
+	•	подключения к базе данных,
+	•	внедрения сервисов (repository, logger и т.д.),
+	•	повторного использования логики между эндпоинтами,
+	•	тестирования (подмена зависимостей).</t>
+  </si>
+  <si>
+    <t>def dependency_function(param: str = "default"):
+    # некоторая логика
+    return value
+Использование:
+@app.get("/endpoint/")
+async def endpoint(data = Depends(dependency_function)):
+    return {"data": data}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Простая зависимость</t>
+  </si>
+  <si>
+    <t>def common_params(q: str | None = None, skip: int = 0, limit: int = 10):
+    return {"q": q, "skip": skip, "limit": limit}
+@app.get("/items/")
+async def read_items(commons: dict = Depends(common_params)):
+    return commons</t>
+  </si>
+  <si>
+    <t>FastAPI сам вызывает common_params() и передаёт результат в commons.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Авторизация через зависимость</t>
+  </si>
+  <si>
+    <t>from fastapi import Header, HTTPException
+def verify_token(x_token: str = Header(...)):
+    if x_token != "secret-token":
+        raise HTTPException(status_code=403, detail="Forbidden")
+    return x_token
+@app.get("/secure/", dependencies=[Depends(verify_token)])
+async def secure_route():
+    return {"status": "ok"}</t>
+  </si>
+  <si>
+    <t>Зависимость вызывается без передачи результата в параметры, но проверяет доступ.</t>
+  </si>
+  <si>
+    <t>Зависимости с другими зависимостями</t>
+  </si>
+  <si>
+    <t>def get_db():
+    db = {"users": ["alice", "bob"]}
+    return db
+def get_user(db = Depends(get_db)):
+    return db["users"][0]
+@app.get("/user/")
+async def user(user: str = Depends(get_user)):
+    return {"user": user}</t>
+  </si>
+  <si>
+    <t>get_user зависит от get_db, а FastAPI сам выстраивает цепочку вызовов.</t>
+  </si>
+  <si>
+    <t>Асинхронные зависимости</t>
+  </si>
+  <si>
+    <t>async def get_data():
+    return {"msg": "async dependency"}
+@app.get("/data/")
+async def read_data(dep = Depends(get_data)):
+    return dep</t>
+  </si>
+  <si>
+    <t>Асинхронные зависимости (async def) полностью поддерживаются.</t>
+  </si>
+  <si>
+    <t>Классы как зависимости</t>
+  </si>
+  <si>
+    <t>class CommonQueryParams:
+    def __init__(self, q: str | None = None, skip: int = 0, limit: int = 10):
+        self.q = q
+        self.skip = skip
+        self.limit = limit
+@app.get("/class/")
+async def read_class(commons: CommonQueryParams = Depends()):
+    return commons.__dict__</t>
+  </si>
+  <si>
+    <t>FastAPI сам создаёт экземпляр класса, подставив нужные параметры.</t>
+  </si>
+  <si>
+    <t>Зависимость с yield (контекст, подключение к БД)</t>
+  </si>
+  <si>
+    <t>async def get_db():
+    db = "db_connection"
+    try:
+        yield db
+    finally:
+        print("Закрываем соединение с БД")
+@app.get("/db/")
+async def use_db(db = Depends(get_db)):
+    return {"db": db}</t>
+  </si>
+  <si>
+    <t>yield позволяет выполнять код до и после использования зависимости.</t>
+  </si>
+  <si>
+    <t>Параметры Depends</t>
+  </si>
+  <si>
+    <t>dependency</t>
+  </si>
+  <si>
+    <t>функция или класс, вызываемый как зависимость</t>
+  </si>
+  <si>
+    <t>use_cache=True</t>
+  </si>
+  <si>
+    <t>повторное использование результата зависимости в одном запросе</t>
+  </si>
+  <si>
+    <t>Depends(None)</t>
+  </si>
+  <si>
+    <t>можно отключить зависимость динамически</t>
+  </si>
+  <si>
+    <t>Пример с DI на уровне приложения
+def get_logger():
+    return lambda msg: print(f"[LOG]: {msg}")
+@app.get("/log/")
+async def log_endpoint(log = Depends(get_logger)):
+    log("Запрос получен")
+    return {"status": "logged"}</t>
+  </si>
+  <si>
+    <t>Примеры</t>
+  </si>
+  <si>
+    <t>В параметре</t>
+  </si>
+  <si>
+    <t>param: Type = Depends(func)</t>
+  </si>
+  <si>
+    <t>Результат func()</t>
+  </si>
+  <si>
+    <t>В декораторе</t>
+  </si>
+  <si>
+    <t>dependencies=[Depends(func)]</t>
+  </si>
+  <si>
+    <t>Только вызывает func()</t>
+  </si>
+  <si>
+    <t>В зависимости</t>
+  </si>
+  <si>
+    <t>Depends(другая_зависимость)</t>
+  </si>
+  <si>
+    <t>Вложенные зависимости</t>
+  </si>
+  <si>
+    <t>Сравнение: способы применения</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4759,6 +9013,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4788,8 +9048,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4814,8 +9097,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -4877,6 +9166,15 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -4893,7 +9191,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4957,6 +9255,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4984,7 +9286,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4995,6 +9297,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -5008,6 +9316,46 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5323,18 +9671,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A0BD9ED-BBA3-C242-AD3C-6BF28F005CA3}">
-  <dimension ref="A2:G82"/>
+  <dimension ref="A2:K159"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="4"/>
     <col min="2" max="2" width="38.83203125" style="4" customWidth="1"/>
     <col min="3" max="3" width="32.5" style="4" customWidth="1"/>
     <col min="4" max="4" width="36.33203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="32.1640625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="36.6640625" style="4" customWidth="1"/>
     <col min="6" max="6" width="35.6640625" style="4" customWidth="1"/>
     <col min="7" max="7" width="41.33203125" customWidth="1"/>
     <col min="8" max="9" width="41.33203125" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="4"/>
+    <col min="10" max="10" width="10.83203125" style="4"/>
+    <col min="11" max="11" width="19.1640625" style="4" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
@@ -5361,54 +9711,54 @@
       <c r="B3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="10"/>
     </row>
     <row r="4" spans="2:7" s="2" customFormat="1" ht="85" x14ac:dyDescent="0.2">
       <c r="B4" s="12"/>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="33" t="s">
         <v>318</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="33" t="s">
         <v>319</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="33" t="s">
         <v>320</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="33" t="s">
         <v>321</v>
       </c>
       <c r="G4" s="10"/>
     </row>
     <row r="5" spans="2:7" s="2" customFormat="1" ht="221" x14ac:dyDescent="0.2">
       <c r="B5" s="13"/>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="33" t="s">
         <v>322</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="33" t="s">
         <v>323</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="33" t="s">
         <v>324</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="33" t="s">
         <v>325</v>
       </c>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="2:7" ht="272" x14ac:dyDescent="0.2">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="30" t="s">
         <v>263</v>
       </c>
       <c r="C6" s="14" t="s">
@@ -5423,16 +9773,16 @@
       <c r="F6" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="25" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B7" s="29"/>
+      <c r="B7" s="31"/>
       <c r="C7" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="36" t="s">
         <v>313</v>
       </c>
       <c r="E7" s="14" t="s">
@@ -5441,12 +9791,12 @@
       <c r="F7" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="27"/>
     </row>
     <row r="8" spans="2:7" ht="136" x14ac:dyDescent="0.2">
-      <c r="B8" s="29"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="34" t="s">
+      <c r="B8" s="31"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="36" t="s">
         <v>314</v>
       </c>
       <c r="E8" s="14" t="s">
@@ -5455,68 +9805,68 @@
       <c r="F8" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="G8" s="25"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9" spans="2:7" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="29"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="34" t="s">
+      <c r="B9" s="31"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="36" t="s">
         <v>311</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="35" t="s">
         <v>307</v>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" spans="2:7" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="29"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="34" t="s">
+      <c r="B10" s="31"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="36" t="s">
         <v>316</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="F10" s="33" t="s">
+      <c r="F10" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="G10" s="25"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" spans="2:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="B11" s="29"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="34" t="s">
+      <c r="B11" s="31"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="36" t="s">
         <v>312</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="35" t="s">
         <v>309</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="27"/>
     </row>
     <row r="12" spans="2:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="B12" s="29"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="34" t="s">
+      <c r="B12" s="31"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="36" t="s">
         <v>315</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="F12" s="33" t="s">
+      <c r="F12" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="G12" s="25"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B13" s="29"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="24" t="s">
+      <c r="B13" s="31"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="26" t="s">
         <v>216</v>
       </c>
       <c r="E13" s="14" t="s">
@@ -5525,12 +9875,12 @@
       <c r="F13" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="27"/>
     </row>
     <row r="14" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B14" s="29"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="24" t="s">
+      <c r="B14" s="31"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="26" t="s">
         <v>539</v>
       </c>
       <c r="E14" s="14" t="s">
@@ -5539,12 +9889,12 @@
       <c r="F14" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="G14" s="25"/>
+      <c r="G14" s="27"/>
     </row>
     <row r="15" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B15" s="29"/>
+      <c r="B15" s="31"/>
       <c r="C15" s="16"/>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="26" t="s">
         <v>541</v>
       </c>
       <c r="E15" s="14" t="s">
@@ -5553,10 +9903,10 @@
       <c r="F15" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="G15" s="25"/>
+      <c r="G15" s="27"/>
     </row>
     <row r="16" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B16" s="29"/>
+      <c r="B16" s="31"/>
       <c r="C16" s="15" t="s">
         <v>206</v>
       </c>
@@ -5569,11 +9919,11 @@
       <c r="F16" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="G16" s="25"/>
+      <c r="G16" s="27"/>
     </row>
     <row r="17" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B17" s="29"/>
-      <c r="C17" s="26"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="28"/>
       <c r="D17" s="14" t="s">
         <v>210</v>
       </c>
@@ -5583,10 +9933,10 @@
       <c r="F17" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="G17" s="25"/>
+      <c r="G17" s="27"/>
     </row>
     <row r="18" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B18" s="29"/>
+      <c r="B18" s="31"/>
       <c r="C18" s="16"/>
       <c r="D18" s="14" t="s">
         <v>213</v>
@@ -5597,10 +9947,10 @@
       <c r="F18" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="G18" s="25"/>
+      <c r="G18" s="27"/>
     </row>
     <row r="19" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B19" s="29"/>
+      <c r="B19" s="31"/>
       <c r="C19" s="15" t="s">
         <v>225</v>
       </c>
@@ -5613,11 +9963,11 @@
       <c r="F19" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="G19" s="25"/>
+      <c r="G19" s="27"/>
     </row>
     <row r="20" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B20" s="29"/>
-      <c r="C20" s="26"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="28"/>
       <c r="D20" s="14" t="s">
         <v>220</v>
       </c>
@@ -5627,11 +9977,11 @@
       <c r="F20" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="G20" s="25"/>
+      <c r="G20" s="27"/>
     </row>
     <row r="21" spans="2:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="B21" s="29"/>
-      <c r="C21" s="26"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="28"/>
       <c r="D21" s="14" t="s">
         <v>543</v>
       </c>
@@ -5639,11 +9989,11 @@
         <v>544</v>
       </c>
       <c r="F21" s="14"/>
-      <c r="G21" s="25"/>
+      <c r="G21" s="27"/>
     </row>
     <row r="22" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B22" s="29"/>
-      <c r="C22" s="26"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="28"/>
       <c r="D22" s="14" t="s">
         <v>545</v>
       </c>
@@ -5651,10 +10001,10 @@
         <v>546</v>
       </c>
       <c r="F22" s="14"/>
-      <c r="G22" s="25"/>
+      <c r="G22" s="27"/>
     </row>
     <row r="23" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B23" s="29"/>
+      <c r="B23" s="31"/>
       <c r="C23" s="16"/>
       <c r="D23" s="14" t="s">
         <v>222</v>
@@ -5665,10 +10015,10 @@
       <c r="F23" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="G23" s="25"/>
+      <c r="G23" s="27"/>
     </row>
     <row r="24" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B24" s="29"/>
+      <c r="B24" s="31"/>
       <c r="C24" s="15" t="s">
         <v>226</v>
       </c>
@@ -5681,11 +10031,11 @@
       <c r="F24" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="G24" s="25"/>
+      <c r="G24" s="27"/>
     </row>
     <row r="25" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B25" s="29"/>
-      <c r="C25" s="26"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="28"/>
       <c r="D25" s="14" t="s">
         <v>230</v>
       </c>
@@ -5695,10 +10045,10 @@
       <c r="F25" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="G25" s="25"/>
+      <c r="G25" s="27"/>
     </row>
     <row r="26" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B26" s="29"/>
+      <c r="B26" s="31"/>
       <c r="C26" s="16"/>
       <c r="D26" s="14" t="s">
         <v>233</v>
@@ -5709,10 +10059,10 @@
       <c r="F26" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="G26" s="25"/>
+      <c r="G26" s="27"/>
     </row>
     <row r="27" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B27" s="29"/>
+      <c r="B27" s="31"/>
       <c r="C27" s="15" t="s">
         <v>236</v>
       </c>
@@ -5725,10 +10075,10 @@
       <c r="F27" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="G27" s="25"/>
+      <c r="G27" s="27"/>
     </row>
     <row r="28" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B28" s="29"/>
+      <c r="B28" s="31"/>
       <c r="C28" s="16"/>
       <c r="D28" s="14" t="s">
         <v>240</v>
@@ -5739,10 +10089,10 @@
       <c r="F28" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="G28" s="25"/>
+      <c r="G28" s="27"/>
     </row>
     <row r="29" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B29" s="29"/>
+      <c r="B29" s="31"/>
       <c r="C29" s="15" t="s">
         <v>243</v>
       </c>
@@ -5755,11 +10105,11 @@
       <c r="F29" s="14" t="s">
         <v>548</v>
       </c>
-      <c r="G29" s="25"/>
+      <c r="G29" s="27"/>
     </row>
     <row r="30" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B30" s="29"/>
-      <c r="C30" s="26"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="28"/>
       <c r="D30" s="14" t="s">
         <v>246</v>
       </c>
@@ -5769,11 +10119,11 @@
       <c r="F30" s="14" t="s">
         <v>547</v>
       </c>
-      <c r="G30" s="25"/>
+      <c r="G30" s="27"/>
     </row>
     <row r="31" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B31" s="29"/>
-      <c r="C31" s="26"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="28"/>
       <c r="D31" s="14" t="s">
         <v>248</v>
       </c>
@@ -5781,10 +10131,10 @@
         <v>249</v>
       </c>
       <c r="F31" s="14"/>
-      <c r="G31" s="25"/>
+      <c r="G31" s="27"/>
     </row>
     <row r="32" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B32" s="29"/>
+      <c r="B32" s="31"/>
       <c r="C32" s="16"/>
       <c r="D32" s="14" t="s">
         <v>250</v>
@@ -5793,10 +10143,10 @@
         <v>251</v>
       </c>
       <c r="F32" s="14"/>
-      <c r="G32" s="25"/>
-    </row>
-    <row r="33" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B33" s="29"/>
+      <c r="G32" s="27"/>
+    </row>
+    <row r="33" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B33" s="31"/>
       <c r="C33" s="15" t="s">
         <v>252</v>
       </c>
@@ -5807,11 +10157,11 @@
         <v>254</v>
       </c>
       <c r="F33" s="14"/>
-      <c r="G33" s="25"/>
-    </row>
-    <row r="34" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B34" s="29"/>
-      <c r="C34" s="26"/>
+      <c r="G33" s="27"/>
+    </row>
+    <row r="34" spans="2:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B34" s="31"/>
+      <c r="C34" s="28"/>
       <c r="D34" s="14" t="s">
         <v>255</v>
       </c>
@@ -5819,11 +10169,11 @@
         <v>256</v>
       </c>
       <c r="F34" s="14"/>
-      <c r="G34" s="25"/>
-    </row>
-    <row r="35" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B35" s="29"/>
-      <c r="C35" s="26"/>
+      <c r="G34" s="27"/>
+    </row>
+    <row r="35" spans="2:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B35" s="31"/>
+      <c r="C35" s="28"/>
       <c r="D35" s="14" t="s">
         <v>257</v>
       </c>
@@ -5831,10 +10181,10 @@
         <v>258</v>
       </c>
       <c r="F35" s="14"/>
-      <c r="G35" s="25"/>
-    </row>
-    <row r="36" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B36" s="30"/>
+      <c r="G35" s="27"/>
+    </row>
+    <row r="36" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B36" s="32"/>
       <c r="C36" s="16"/>
       <c r="D36" s="14" t="s">
         <v>259</v>
@@ -5843,743 +10193,1998 @@
         <v>260</v>
       </c>
       <c r="F36" s="14"/>
-      <c r="G36" s="27"/>
-    </row>
-    <row r="37" spans="1:7" ht="306" x14ac:dyDescent="0.2">
-      <c r="A37" s="36" t="s">
+      <c r="G36" s="29"/>
+    </row>
+    <row r="37" spans="2:7" ht="204" x14ac:dyDescent="0.2">
+      <c r="B37" s="30" t="s">
+        <v>552</v>
+      </c>
+      <c r="C37" s="39" t="s">
+        <v>555</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>553</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>554</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>556</v>
+      </c>
+      <c r="G37" s="44"/>
+    </row>
+    <row r="38" spans="2:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="31"/>
+      <c r="C38" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="D38" s="45" t="s">
+        <v>562</v>
+      </c>
+      <c r="E38" s="46" t="s">
+        <v>563</v>
+      </c>
+      <c r="F38" s="46" t="s">
+        <v>564</v>
+      </c>
+      <c r="G38" s="44"/>
+    </row>
+    <row r="39" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B39" s="31"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="45" t="s">
+        <v>565</v>
+      </c>
+      <c r="E39" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="F39" s="46" t="s">
+        <v>566</v>
+      </c>
+      <c r="G39" s="44"/>
+    </row>
+    <row r="40" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B40" s="31"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="45" t="s">
+        <v>567</v>
+      </c>
+      <c r="E40" s="46" t="s">
+        <v>568</v>
+      </c>
+      <c r="F40" s="46" t="s">
+        <v>569</v>
+      </c>
+      <c r="G40" s="44"/>
+    </row>
+    <row r="41" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B41" s="31"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="45" t="s">
+        <v>570</v>
+      </c>
+      <c r="E41" s="46" t="s">
+        <v>571</v>
+      </c>
+      <c r="F41" s="46" t="s">
+        <v>572</v>
+      </c>
+      <c r="G41" s="44"/>
+    </row>
+    <row r="42" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B42" s="31"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="45" t="s">
+        <v>573</v>
+      </c>
+      <c r="E42" s="46" t="s">
+        <v>574</v>
+      </c>
+      <c r="F42" s="46" t="s">
+        <v>575</v>
+      </c>
+      <c r="G42" s="44"/>
+    </row>
+    <row r="43" spans="2:7" ht="85" x14ac:dyDescent="0.2">
+      <c r="B43" s="31"/>
+      <c r="C43" s="15" t="s">
+        <v>558</v>
+      </c>
+      <c r="D43" s="48" t="s">
+        <v>580</v>
+      </c>
+      <c r="E43" s="47" t="s">
+        <v>576</v>
+      </c>
+      <c r="F43" s="47" t="s">
+        <v>577</v>
+      </c>
+      <c r="G43" s="44"/>
+    </row>
+    <row r="44" spans="2:7" ht="85" x14ac:dyDescent="0.2">
+      <c r="B44" s="31"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="14" t="s">
+        <v>581</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>578</v>
+      </c>
+      <c r="F44" s="35" t="s">
+        <v>579</v>
+      </c>
+      <c r="G44" s="44"/>
+    </row>
+    <row r="45" spans="2:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="B45" s="31"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="35" t="s">
+        <v>582</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>583</v>
+      </c>
+      <c r="F45" s="35" t="s">
+        <v>584</v>
+      </c>
+      <c r="G45" s="44"/>
+    </row>
+    <row r="46" spans="2:7" ht="153" x14ac:dyDescent="0.2">
+      <c r="B46" s="31"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="35" t="s">
+        <v>585</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>586</v>
+      </c>
+      <c r="F46" s="35" t="s">
+        <v>587</v>
+      </c>
+      <c r="G46" s="44"/>
+    </row>
+    <row r="47" spans="2:7" ht="136" x14ac:dyDescent="0.2">
+      <c r="B47" s="31"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="49" t="s">
+        <v>588</v>
+      </c>
+      <c r="E47" s="46" t="s">
+        <v>589</v>
+      </c>
+      <c r="F47" s="49" t="s">
+        <v>590</v>
+      </c>
+      <c r="G47" s="44"/>
+    </row>
+    <row r="48" spans="2:7" ht="119" x14ac:dyDescent="0.2">
+      <c r="B48" s="31"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="14" t="s">
+        <v>592</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>591</v>
+      </c>
+      <c r="F48" s="35" t="s">
+        <v>593</v>
+      </c>
+      <c r="G48" s="44"/>
+    </row>
+    <row r="49" spans="1:7" ht="289" x14ac:dyDescent="0.2">
+      <c r="B49" s="31"/>
+      <c r="C49" s="15" t="s">
+        <v>559</v>
+      </c>
+      <c r="D49" s="46" t="s">
+        <v>594</v>
+      </c>
+      <c r="E49" s="46" t="s">
+        <v>595</v>
+      </c>
+      <c r="F49" s="46" t="s">
+        <v>596</v>
+      </c>
+      <c r="G49" s="44"/>
+    </row>
+    <row r="50" spans="1:7" ht="255" x14ac:dyDescent="0.2">
+      <c r="B50" s="31"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="14" t="s">
+        <v>597</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>598</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>599</v>
+      </c>
+      <c r="G50" s="44"/>
+    </row>
+    <row r="51" spans="1:7" ht="170" x14ac:dyDescent="0.2">
+      <c r="B51" s="31"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="14" t="s">
+        <v>602</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>600</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>601</v>
+      </c>
+      <c r="G51" s="44"/>
+    </row>
+    <row r="52" spans="1:7" ht="238" x14ac:dyDescent="0.2">
+      <c r="B52" s="31"/>
+      <c r="C52" s="15" t="s">
+        <v>560</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>603</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>604</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="G52" s="44"/>
+    </row>
+    <row r="53" spans="1:7" ht="119" x14ac:dyDescent="0.2">
+      <c r="B53" s="31"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="50" t="s">
+        <v>606</v>
+      </c>
+      <c r="E53" s="46" t="s">
+        <v>607</v>
+      </c>
+      <c r="F53" s="49" t="s">
+        <v>608</v>
+      </c>
+      <c r="G53" s="44"/>
+    </row>
+    <row r="54" spans="1:7" ht="204" x14ac:dyDescent="0.2">
+      <c r="B54" s="31"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="35" t="s">
+        <v>609</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="F54" s="35" t="s">
+        <v>611</v>
+      </c>
+      <c r="G54" s="44"/>
+    </row>
+    <row r="55" spans="1:7" ht="170" x14ac:dyDescent="0.2">
+      <c r="B55" s="31"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="35" t="s">
+        <v>612</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="F55" s="35" t="s">
+        <v>614</v>
+      </c>
+      <c r="G55" s="44"/>
+    </row>
+    <row r="56" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+      <c r="B56" s="31"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="14" t="s">
+        <v>617</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>615</v>
+      </c>
+      <c r="F56" s="35" t="s">
+        <v>616</v>
+      </c>
+      <c r="G56" s="44"/>
+    </row>
+    <row r="57" spans="1:7" ht="221" x14ac:dyDescent="0.2">
+      <c r="B57" s="31"/>
+      <c r="C57" s="15" t="s">
+        <v>561</v>
+      </c>
+      <c r="D57" s="46" t="s">
+        <v>618</v>
+      </c>
+      <c r="E57" s="46" t="s">
+        <v>619</v>
+      </c>
+      <c r="F57" s="49" t="s">
+        <v>620</v>
+      </c>
+      <c r="G57" s="44"/>
+    </row>
+    <row r="58" spans="1:7" ht="289" x14ac:dyDescent="0.2">
+      <c r="B58" s="31"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="14" t="s">
+        <v>621</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>622</v>
+      </c>
+      <c r="F58" s="14" t="s">
+        <v>623</v>
+      </c>
+      <c r="G58" s="44"/>
+    </row>
+    <row r="59" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+      <c r="B59" s="32"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="14" t="s">
+        <v>624</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>625</v>
+      </c>
+      <c r="F59" s="14" t="s">
+        <v>626</v>
+      </c>
+      <c r="G59" s="44"/>
+    </row>
+    <row r="60" spans="1:7" ht="306" x14ac:dyDescent="0.2">
+      <c r="A60" s="40" t="s">
         <v>391</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="B60" s="18" t="s">
         <v>329</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C60" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D60" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E60" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F60" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="G37" s="17" t="s">
+      <c r="G60" s="17" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A38" s="36"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="36" t="s">
+    <row r="61" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A61" s="40"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="40" t="s">
         <v>334</v>
       </c>
-      <c r="D38" s="37" t="s">
+      <c r="D61" s="41" t="s">
         <v>335</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E61" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F61" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="G38" s="17" t="s">
+      <c r="G61" s="17" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A39" s="36"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="37" t="s">
+    <row r="62" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A62" s="40"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="41" t="s">
         <v>338</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E62" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F62" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G62" s="17" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A40" s="36"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="37" t="s">
+    <row r="63" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A63" s="40"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="40"/>
+      <c r="D63" s="41" t="s">
         <v>340</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E63" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="F40" s="17" t="s">
+      <c r="F63" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="G40" s="17" t="s">
+      <c r="G63" s="17" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A41" s="36"/>
-      <c r="B41" s="18"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="37" t="s">
+    <row r="64" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A64" s="40"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="40"/>
+      <c r="D64" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E64" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="F41" s="17" t="s">
+      <c r="F64" s="17" t="s">
         <v>346</v>
       </c>
-      <c r="G41" s="17" t="s">
+      <c r="G64" s="17" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A42" s="36"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="37" t="s">
+    <row r="65" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A65" s="40"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="41" t="s">
         <v>347</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E65" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="F65" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="G42" s="17" t="s">
+      <c r="G65" s="17" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A43" s="36"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="37" t="s">
+    <row r="66" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A66" s="40"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="41" t="s">
         <v>350</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E66" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="F43" s="17" t="s">
+      <c r="F66" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="G43" s="17" t="s">
+      <c r="G66" s="17" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A44" s="36"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="37" t="s">
+    <row r="67" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A67" s="40"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="40"/>
+      <c r="D67" s="41" t="s">
         <v>353</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E67" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="F44" s="17" t="s">
+      <c r="F67" s="17" t="s">
         <v>354</v>
       </c>
-      <c r="G44" s="17" t="s">
+      <c r="G67" s="17" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="36"/>
-      <c r="B45" s="18" t="s">
+    <row r="68" spans="1:7" ht="409" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="40"/>
+      <c r="B68" s="18" t="s">
         <v>359</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C68" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D68" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="E45" s="17" t="s">
+      <c r="E68" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="F45" s="17" t="s">
+      <c r="F68" s="17" t="s">
         <v>361</v>
       </c>
-      <c r="G45" s="17" t="s">
+      <c r="G68" s="17" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A46" s="36"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="36" t="s">
+    <row r="69" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A69" s="40"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="40" t="s">
         <v>390</v>
       </c>
-      <c r="D46" s="37" t="s">
+      <c r="D69" s="41" t="s">
         <v>329</v>
       </c>
-      <c r="E46" s="17" t="s">
+      <c r="E69" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="F46" s="17" t="s">
+      <c r="F69" s="17" t="s">
         <v>363</v>
       </c>
-      <c r="G46" s="38" t="s">
+      <c r="G69" s="42" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A47" s="36"/>
-      <c r="B47" s="18"/>
-      <c r="C47" s="36"/>
-      <c r="D47" s="37" t="s">
+    <row r="70" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A70" s="40"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="40"/>
+      <c r="D70" s="41" t="s">
         <v>364</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E70" s="17" t="s">
         <v>365</v>
       </c>
-      <c r="F47" s="17" t="s">
+      <c r="F70" s="17" t="s">
         <v>366</v>
       </c>
-      <c r="G47" s="39"/>
-    </row>
-    <row r="48" spans="1:7" ht="102" x14ac:dyDescent="0.2">
-      <c r="A48" s="36"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="36"/>
-      <c r="D48" s="37" t="s">
+      <c r="G70" s="43"/>
+    </row>
+    <row r="71" spans="1:7" ht="102" x14ac:dyDescent="0.2">
+      <c r="A71" s="40"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="40"/>
+      <c r="D71" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="E71" s="17" t="s">
         <v>368</v>
       </c>
-      <c r="F48" s="17" t="s">
+      <c r="F71" s="17" t="s">
         <v>369</v>
       </c>
-      <c r="G48" s="17" t="s">
+      <c r="G71" s="17" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A49" s="36"/>
-      <c r="B49" s="18"/>
-      <c r="C49" s="36"/>
-      <c r="D49" s="37" t="s">
+    <row r="72" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A72" s="40"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="40"/>
+      <c r="D72" s="41" t="s">
         <v>370</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E72" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="F49" s="17" t="s">
+      <c r="F72" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="G49" s="22"/>
-    </row>
-    <row r="50" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A50" s="36"/>
-      <c r="B50" s="18"/>
-      <c r="C50" s="36"/>
-      <c r="D50" s="37" t="s">
+      <c r="G72" s="22"/>
+    </row>
+    <row r="73" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A73" s="40"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="40"/>
+      <c r="D73" s="41" t="s">
         <v>373</v>
       </c>
-      <c r="E50" s="17" t="s">
+      <c r="E73" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="F50" s="17" t="s">
+      <c r="F73" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="G50" s="22"/>
-    </row>
-    <row r="51" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A51" s="36"/>
-      <c r="B51" s="18"/>
-      <c r="C51" s="36"/>
-      <c r="D51" s="37" t="s">
+      <c r="G73" s="22"/>
+    </row>
+    <row r="74" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A74" s="40"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="40"/>
+      <c r="D74" s="41" t="s">
         <v>376</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E74" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="F51" s="17" t="s">
+      <c r="F74" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="G51" s="22"/>
-    </row>
-    <row r="52" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A52" s="36"/>
-      <c r="B52" s="18"/>
-      <c r="C52" s="36"/>
-      <c r="D52" s="37" t="s">
+      <c r="G74" s="22"/>
+    </row>
+    <row r="75" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A75" s="40"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="41" t="s">
         <v>379</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E75" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="F52" s="17" t="s">
+      <c r="F75" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="G52" s="22"/>
-    </row>
-    <row r="53" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A53" s="36"/>
-      <c r="B53" s="18"/>
-      <c r="C53" s="36"/>
-      <c r="D53" s="37" t="s">
+      <c r="G75" s="22"/>
+    </row>
+    <row r="76" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A76" s="40"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="41" t="s">
         <v>382</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E76" s="17" t="s">
         <v>383</v>
       </c>
-      <c r="F53" s="17" t="s">
+      <c r="F76" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="G53" s="22"/>
-    </row>
-    <row r="54" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A54" s="36"/>
-      <c r="B54" s="18"/>
-      <c r="C54" s="36"/>
-      <c r="D54" s="37" t="s">
+      <c r="G76" s="22"/>
+    </row>
+    <row r="77" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A77" s="40"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="40"/>
+      <c r="D77" s="41" t="s">
         <v>385</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E77" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="F54" s="17" t="s">
+      <c r="F77" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="G54" s="22"/>
-    </row>
-    <row r="55" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A55" s="36"/>
-      <c r="B55" s="18"/>
-      <c r="C55" s="36"/>
-      <c r="D55" s="37" t="s">
+      <c r="G77" s="22"/>
+    </row>
+    <row r="78" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A78" s="40"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="40"/>
+      <c r="D78" s="41" t="s">
         <v>388</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E78" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="F55" s="17" t="s">
+      <c r="F78" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="G55" s="22"/>
-    </row>
-    <row r="56" spans="1:7" ht="221" x14ac:dyDescent="0.2">
-      <c r="A56" s="36"/>
-      <c r="B56" s="18" t="s">
+      <c r="G78" s="22"/>
+    </row>
+    <row r="79" spans="1:7" ht="221" x14ac:dyDescent="0.2">
+      <c r="A79" s="40"/>
+      <c r="B79" s="18" t="s">
         <v>392</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C79" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D79" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="E79" s="17" t="s">
         <v>395</v>
       </c>
-      <c r="F56" s="17" t="s">
+      <c r="F79" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="G56" s="17" t="s">
+      <c r="G79" s="17" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" s="36"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="36" t="s">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="40"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="40" t="s">
         <v>495</v>
       </c>
-      <c r="D57" s="22" t="s">
+      <c r="D80" s="22" t="s">
         <v>397</v>
       </c>
-      <c r="E57" s="22">
+      <c r="E80" s="22">
         <v>200</v>
       </c>
-      <c r="F57" s="22" t="s">
+      <c r="F80" s="22" t="s">
         <v>398</v>
       </c>
-      <c r="G57" s="22"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58" s="36"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="36"/>
-      <c r="D58" s="22" t="s">
+      <c r="G80" s="22"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" s="40"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="40"/>
+      <c r="D81" s="22" t="s">
         <v>399</v>
       </c>
-      <c r="E58" s="22">
+      <c r="E81" s="22">
         <v>201</v>
       </c>
-      <c r="F58" s="22" t="s">
+      <c r="F81" s="22" t="s">
         <v>400</v>
       </c>
-      <c r="G58" s="22"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59" s="36"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="36"/>
-      <c r="D59" s="22" t="s">
+      <c r="G81" s="22"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" s="40"/>
+      <c r="B82" s="18"/>
+      <c r="C82" s="40"/>
+      <c r="D82" s="22" t="s">
         <v>401</v>
       </c>
-      <c r="E59" s="22">
+      <c r="E82" s="22">
         <v>204</v>
       </c>
-      <c r="F59" s="22" t="s">
+      <c r="F82" s="22" t="s">
         <v>402</v>
       </c>
-      <c r="G59" s="22"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60" s="36"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="36"/>
-      <c r="D60" s="22" t="s">
+      <c r="G82" s="22"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" s="40"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="40"/>
+      <c r="D83" s="22" t="s">
         <v>403</v>
       </c>
-      <c r="E60" s="22">
+      <c r="E83" s="22">
         <v>400</v>
       </c>
-      <c r="F60" s="22" t="s">
+      <c r="F83" s="22" t="s">
         <v>404</v>
       </c>
-      <c r="G60" s="22"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61" s="36"/>
-      <c r="B61" s="18"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="22" t="s">
+      <c r="G83" s="22"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" s="40"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="22" t="s">
         <v>405</v>
       </c>
-      <c r="E61" s="22">
+      <c r="E84" s="22">
         <v>401</v>
       </c>
-      <c r="F61" s="22" t="s">
+      <c r="F84" s="22" t="s">
         <v>406</v>
       </c>
-      <c r="G61" s="22"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A62" s="36"/>
-      <c r="B62" s="18"/>
-      <c r="C62" s="36"/>
-      <c r="D62" s="22" t="s">
+      <c r="G84" s="22"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" s="40"/>
+      <c r="B85" s="18"/>
+      <c r="C85" s="40"/>
+      <c r="D85" s="22" t="s">
         <v>407</v>
       </c>
-      <c r="E62" s="22">
+      <c r="E85" s="22">
         <v>403</v>
       </c>
-      <c r="F62" s="22" t="s">
+      <c r="F85" s="22" t="s">
         <v>408</v>
       </c>
-      <c r="G62" s="22"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63" s="36"/>
-      <c r="B63" s="18"/>
-      <c r="C63" s="36"/>
-      <c r="D63" s="22" t="s">
+      <c r="G85" s="22"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" s="40"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="40"/>
+      <c r="D86" s="22" t="s">
         <v>409</v>
       </c>
-      <c r="E63" s="22">
+      <c r="E86" s="22">
         <v>404</v>
       </c>
-      <c r="F63" s="22" t="s">
+      <c r="F86" s="22" t="s">
         <v>410</v>
       </c>
-      <c r="G63" s="22"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A64" s="36"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="36"/>
-      <c r="D64" s="22" t="s">
+      <c r="G86" s="22"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" s="40"/>
+      <c r="B87" s="18"/>
+      <c r="C87" s="40"/>
+      <c r="D87" s="22" t="s">
         <v>411</v>
       </c>
-      <c r="E64" s="22">
+      <c r="E87" s="22">
         <v>500</v>
       </c>
-      <c r="F64" s="22" t="s">
+      <c r="F87" s="22" t="s">
         <v>412</v>
       </c>
-      <c r="G64" s="22"/>
-    </row>
-    <row r="65" spans="1:7" ht="340" x14ac:dyDescent="0.2">
-      <c r="A65" s="36"/>
-      <c r="B65" s="18" t="s">
+      <c r="G87" s="22"/>
+    </row>
+    <row r="88" spans="1:7" ht="340" x14ac:dyDescent="0.2">
+      <c r="A88" s="40"/>
+      <c r="B88" s="18" t="s">
         <v>496</v>
       </c>
-      <c r="C65" s="17" t="s">
+      <c r="C88" s="17" t="s">
         <v>538</v>
       </c>
-      <c r="D65" s="17" t="s">
+      <c r="D88" s="17" t="s">
         <v>549</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E88" s="17" t="s">
         <v>536</v>
       </c>
-      <c r="F65" s="17" t="s">
+      <c r="F88" s="17" t="s">
         <v>537</v>
       </c>
-      <c r="G65" s="22"/>
-    </row>
-    <row r="66" spans="1:7" ht="85" x14ac:dyDescent="0.2">
-      <c r="A66" s="36"/>
-      <c r="B66" s="18"/>
-      <c r="C66" s="36" t="s">
+      <c r="G88" s="22"/>
+    </row>
+    <row r="89" spans="1:7" ht="85" x14ac:dyDescent="0.2">
+      <c r="A89" s="40"/>
+      <c r="B89" s="18"/>
+      <c r="C89" s="40" t="s">
         <v>501</v>
       </c>
-      <c r="D66" s="17" t="s">
+      <c r="D89" s="17" t="s">
         <v>497</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E89" s="17" t="s">
         <v>498</v>
       </c>
-      <c r="F66" s="17"/>
-      <c r="G66" s="22"/>
-    </row>
-    <row r="67" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A67" s="36"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="36"/>
-      <c r="D67" s="17" t="s">
+      <c r="F89" s="17"/>
+      <c r="G89" s="22"/>
+    </row>
+    <row r="90" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A90" s="40"/>
+      <c r="B90" s="18"/>
+      <c r="C90" s="40"/>
+      <c r="D90" s="17" t="s">
         <v>499</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E90" s="17" t="s">
         <v>500</v>
       </c>
-      <c r="F67" s="17"/>
-      <c r="G67" s="22"/>
-    </row>
-    <row r="68" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A68" s="36"/>
-      <c r="B68" s="18"/>
-      <c r="C68" s="36" t="s">
+      <c r="F90" s="17"/>
+      <c r="G90" s="22"/>
+    </row>
+    <row r="91" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="A91" s="40"/>
+      <c r="B91" s="18"/>
+      <c r="C91" s="40" t="s">
         <v>502</v>
       </c>
-      <c r="D68" s="17" t="s">
+      <c r="D91" s="17" t="s">
         <v>503</v>
       </c>
-      <c r="E68" s="17" t="s">
+      <c r="E91" s="17" t="s">
         <v>504</v>
       </c>
-      <c r="F68" s="17"/>
-      <c r="G68" s="22"/>
-    </row>
-    <row r="69" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A69" s="36"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="36"/>
-      <c r="D69" s="17" t="s">
+      <c r="F91" s="17"/>
+      <c r="G91" s="22"/>
+    </row>
+    <row r="92" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A92" s="40"/>
+      <c r="B92" s="18"/>
+      <c r="C92" s="40"/>
+      <c r="D92" s="17" t="s">
         <v>505</v>
       </c>
-      <c r="E69" s="17" t="s">
+      <c r="E92" s="17" t="s">
         <v>506</v>
       </c>
-      <c r="F69" s="17"/>
-      <c r="G69" s="22"/>
-    </row>
-    <row r="70" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A70" s="36"/>
-      <c r="B70" s="18"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="17" t="s">
+      <c r="F92" s="17"/>
+      <c r="G92" s="22"/>
+    </row>
+    <row r="93" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A93" s="40"/>
+      <c r="B93" s="18"/>
+      <c r="C93" s="40"/>
+      <c r="D93" s="17" t="s">
         <v>507</v>
       </c>
-      <c r="E70" s="17" t="s">
+      <c r="E93" s="17" t="s">
         <v>508</v>
       </c>
-      <c r="F70" s="17"/>
-      <c r="G70" s="22"/>
-    </row>
-    <row r="71" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A71" s="36"/>
-      <c r="B71" s="18"/>
-      <c r="C71" s="36" t="s">
+      <c r="F93" s="17"/>
+      <c r="G93" s="22"/>
+    </row>
+    <row r="94" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A94" s="40"/>
+      <c r="B94" s="18"/>
+      <c r="C94" s="40" t="s">
         <v>509</v>
       </c>
-      <c r="D71" s="17" t="s">
+      <c r="D94" s="17" t="s">
         <v>510</v>
       </c>
-      <c r="E71" s="17" t="s">
+      <c r="E94" s="17" t="s">
         <v>511</v>
       </c>
-      <c r="F71" s="17"/>
-      <c r="G71" s="22"/>
-    </row>
-    <row r="72" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A72" s="36"/>
-      <c r="B72" s="18"/>
-      <c r="C72" s="36"/>
-      <c r="D72" s="17" t="s">
+      <c r="F94" s="17"/>
+      <c r="G94" s="22"/>
+    </row>
+    <row r="95" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A95" s="40"/>
+      <c r="B95" s="18"/>
+      <c r="C95" s="40"/>
+      <c r="D95" s="17" t="s">
         <v>512</v>
       </c>
-      <c r="E72" s="17" t="s">
+      <c r="E95" s="17" t="s">
         <v>513</v>
       </c>
-      <c r="F72" s="17"/>
-      <c r="G72" s="22"/>
-    </row>
-    <row r="73" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A73" s="36"/>
-      <c r="B73" s="18"/>
-      <c r="C73" s="36"/>
-      <c r="D73" s="17" t="s">
+      <c r="F95" s="17"/>
+      <c r="G95" s="22"/>
+    </row>
+    <row r="96" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A96" s="40"/>
+      <c r="B96" s="18"/>
+      <c r="C96" s="40"/>
+      <c r="D96" s="17" t="s">
         <v>514</v>
       </c>
-      <c r="E73" s="17" t="s">
+      <c r="E96" s="17" t="s">
         <v>515</v>
       </c>
-      <c r="F73" s="17"/>
-      <c r="G73" s="22"/>
-    </row>
-    <row r="74" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A74" s="36"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="36"/>
-      <c r="D74" s="17" t="s">
+      <c r="F96" s="17"/>
+      <c r="G96" s="22"/>
+    </row>
+    <row r="97" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A97" s="40"/>
+      <c r="B97" s="18"/>
+      <c r="C97" s="40"/>
+      <c r="D97" s="17" t="s">
         <v>516</v>
       </c>
-      <c r="E74" s="17" t="s">
+      <c r="E97" s="17" t="s">
         <v>517</v>
       </c>
-      <c r="F74" s="17"/>
-      <c r="G74" s="22"/>
-    </row>
-    <row r="75" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A75" s="36"/>
-      <c r="B75" s="18"/>
-      <c r="C75" s="36" t="s">
+      <c r="F97" s="17"/>
+      <c r="G97" s="22"/>
+    </row>
+    <row r="98" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="A98" s="40"/>
+      <c r="B98" s="18"/>
+      <c r="C98" s="40" t="s">
         <v>518</v>
       </c>
-      <c r="D75" s="17" t="s">
+      <c r="D98" s="17" t="s">
         <v>519</v>
       </c>
-      <c r="E75" s="17" t="s">
+      <c r="E98" s="17" t="s">
         <v>520</v>
       </c>
-      <c r="F75" s="17"/>
-      <c r="G75" s="22"/>
-    </row>
-    <row r="76" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A76" s="36"/>
-      <c r="B76" s="18"/>
-      <c r="C76" s="36"/>
-      <c r="D76" s="17" t="s">
+      <c r="F98" s="17"/>
+      <c r="G98" s="22"/>
+    </row>
+    <row r="99" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A99" s="40"/>
+      <c r="B99" s="18"/>
+      <c r="C99" s="40"/>
+      <c r="D99" s="17" t="s">
         <v>521</v>
       </c>
-      <c r="E76" s="17" t="s">
+      <c r="E99" s="17" t="s">
         <v>522</v>
       </c>
-      <c r="F76" s="17"/>
-      <c r="G76" s="22"/>
-    </row>
-    <row r="77" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A77" s="36"/>
-      <c r="B77" s="18"/>
-      <c r="C77" s="36"/>
-      <c r="D77" s="17" t="s">
+      <c r="F99" s="17"/>
+      <c r="G99" s="22"/>
+    </row>
+    <row r="100" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A100" s="40"/>
+      <c r="B100" s="18"/>
+      <c r="C100" s="40"/>
+      <c r="D100" s="17" t="s">
         <v>523</v>
       </c>
-      <c r="E77" s="17" t="s">
+      <c r="E100" s="17" t="s">
         <v>524</v>
       </c>
-      <c r="F77" s="17"/>
-      <c r="G77" s="22"/>
-    </row>
-    <row r="78" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A78" s="36"/>
-      <c r="B78" s="18"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="17" t="s">
+      <c r="F100" s="17"/>
+      <c r="G100" s="22"/>
+    </row>
+    <row r="101" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A101" s="40"/>
+      <c r="B101" s="18"/>
+      <c r="C101" s="40"/>
+      <c r="D101" s="17" t="s">
         <v>525</v>
       </c>
-      <c r="E78" s="17" t="s">
+      <c r="E101" s="17" t="s">
         <v>526</v>
       </c>
-      <c r="F78" s="17"/>
-      <c r="G78" s="22"/>
-    </row>
-    <row r="79" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A79" s="36"/>
-      <c r="B79" s="18"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="17" t="s">
+      <c r="F101" s="17"/>
+      <c r="G101" s="22"/>
+    </row>
+    <row r="102" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A102" s="40"/>
+      <c r="B102" s="18"/>
+      <c r="C102" s="40"/>
+      <c r="D102" s="17" t="s">
         <v>527</v>
       </c>
-      <c r="E79" s="17" t="s">
+      <c r="E102" s="17" t="s">
         <v>528</v>
       </c>
-      <c r="F79" s="17"/>
-      <c r="G79" s="22"/>
-    </row>
-    <row r="80" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A80" s="36"/>
-      <c r="B80" s="18"/>
-      <c r="C80" s="36" t="s">
+      <c r="F102" s="17"/>
+      <c r="G102" s="22"/>
+    </row>
+    <row r="103" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A103" s="40"/>
+      <c r="B103" s="18"/>
+      <c r="C103" s="40" t="s">
         <v>529</v>
       </c>
-      <c r="D80" s="17" t="s">
+      <c r="D103" s="17" t="s">
         <v>530</v>
       </c>
-      <c r="E80" s="17" t="s">
+      <c r="E103" s="17" t="s">
         <v>531</v>
       </c>
-      <c r="F80" s="17"/>
-      <c r="G80" s="22"/>
-    </row>
-    <row r="81" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A81" s="36"/>
-      <c r="B81" s="18"/>
-      <c r="C81" s="36"/>
-      <c r="D81" s="17" t="s">
+      <c r="F103" s="17"/>
+      <c r="G103" s="22"/>
+    </row>
+    <row r="104" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A104" s="40"/>
+      <c r="B104" s="18"/>
+      <c r="C104" s="40"/>
+      <c r="D104" s="17" t="s">
         <v>532</v>
       </c>
-      <c r="E81" s="17" t="s">
+      <c r="E104" s="17" t="s">
         <v>533</v>
       </c>
-      <c r="F81" s="17"/>
-      <c r="G81" s="22"/>
-    </row>
-    <row r="82" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A82" s="36"/>
-      <c r="B82" s="18"/>
-      <c r="C82" s="36"/>
-      <c r="D82" s="17" t="s">
+      <c r="F104" s="17"/>
+      <c r="G104" s="22"/>
+    </row>
+    <row r="105" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A105" s="40"/>
+      <c r="B105" s="18"/>
+      <c r="C105" s="40"/>
+      <c r="D105" s="17" t="s">
         <v>534</v>
       </c>
-      <c r="E82" s="17" t="s">
+      <c r="E105" s="17" t="s">
         <v>535</v>
       </c>
-      <c r="F82" s="17"/>
-      <c r="G82" s="22"/>
+      <c r="F105" s="17"/>
+      <c r="G105" s="22"/>
+    </row>
+    <row r="106" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+      <c r="A106" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="B106" s="38" t="s">
+        <v>628</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="E106" s="51" t="s">
+        <v>634</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="G106" s="56" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B107" s="23"/>
+      <c r="C107" s="52" t="s">
+        <v>635</v>
+      </c>
+      <c r="D107" t="s">
+        <v>636</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="F107" t="s">
+        <v>638</v>
+      </c>
+      <c r="G107" s="53" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B108" s="23"/>
+      <c r="C108" s="52"/>
+      <c r="D108" t="s">
+        <v>639</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="F108" t="s">
+        <v>641</v>
+      </c>
+      <c r="G108" s="54"/>
+    </row>
+    <row r="109" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B109" s="23"/>
+      <c r="C109" s="52"/>
+      <c r="D109" t="s">
+        <v>642</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="F109" t="s">
+        <v>644</v>
+      </c>
+      <c r="G109" s="54"/>
+    </row>
+    <row r="110" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B110" s="23"/>
+      <c r="C110" s="52"/>
+      <c r="D110" t="s">
+        <v>101</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="F110" t="s">
+        <v>646</v>
+      </c>
+      <c r="G110" s="54"/>
+    </row>
+    <row r="111" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B111" s="23"/>
+      <c r="C111" s="52"/>
+      <c r="D111" t="s">
+        <v>647</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="F111" t="s">
+        <v>649</v>
+      </c>
+      <c r="G111" s="54"/>
+    </row>
+    <row r="112" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B112" s="23"/>
+      <c r="C112" s="52"/>
+      <c r="D112" t="s">
+        <v>650</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="F112" t="s">
+        <v>652</v>
+      </c>
+      <c r="G112" s="54"/>
+    </row>
+    <row r="113" spans="2:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B113" s="23"/>
+      <c r="C113" s="52"/>
+      <c r="D113" t="s">
+        <v>653</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="F113" t="s">
+        <v>655</v>
+      </c>
+      <c r="G113" s="54"/>
+    </row>
+    <row r="114" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B114" s="23"/>
+      <c r="C114" s="23" t="s">
+        <v>657</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="G114" s="53" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="115" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B115" s="23"/>
+      <c r="C115" s="23"/>
+      <c r="D115" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="G115" s="54"/>
+    </row>
+    <row r="116" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B116" s="23"/>
+      <c r="C116" s="23"/>
+      <c r="D116" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="G116" s="54"/>
+    </row>
+    <row r="117" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B117" s="23"/>
+      <c r="C117" s="23"/>
+      <c r="D117" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="G117" s="54"/>
+    </row>
+    <row r="118" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B118" s="23"/>
+      <c r="C118" s="23"/>
+      <c r="D118" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="G118" s="54"/>
+    </row>
+    <row r="119" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B119" s="23"/>
+      <c r="C119" s="23" t="s">
+        <v>679</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="G119" s="53" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7" ht="31" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B120" s="23"/>
+      <c r="C120" s="23"/>
+      <c r="D120" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="G120" s="55"/>
+    </row>
+    <row r="121" spans="2:7" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B121" s="23"/>
+      <c r="C121" s="23"/>
+      <c r="D121" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="G121" s="55"/>
+    </row>
+    <row r="122" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B122" s="23"/>
+      <c r="C122" s="23"/>
+      <c r="D122" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="G122" s="55"/>
+    </row>
+    <row r="123" spans="2:7" ht="136" x14ac:dyDescent="0.2">
+      <c r="B123" s="23"/>
+      <c r="C123" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="D123" t="s">
+        <v>682</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="G123" s="56" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="124" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B124" s="23"/>
+      <c r="C124" s="23" t="s">
+        <v>685</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="G124" s="53" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="125" spans="2:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B125" s="23"/>
+      <c r="C125" s="23"/>
+      <c r="D125" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="G125" s="54"/>
+    </row>
+    <row r="126" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B126" s="23"/>
+      <c r="C126" s="23"/>
+      <c r="D126" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="G126" s="54"/>
+    </row>
+    <row r="127" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B127" s="23"/>
+      <c r="C127" s="23"/>
+      <c r="D127" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="G127" s="54"/>
+    </row>
+    <row r="128" spans="2:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B128" s="23"/>
+      <c r="C128" s="23"/>
+      <c r="D128" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="G128" s="54"/>
+    </row>
+    <row r="129" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B129" s="23"/>
+      <c r="C129" s="23"/>
+      <c r="D129" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="G129" s="54"/>
+    </row>
+    <row r="130" spans="2:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="B130" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="F130" s="56" t="s">
+        <v>704</v>
+      </c>
+      <c r="G130" t="s">
+        <v>700</v>
+      </c>
+      <c r="H130" t="s">
+        <v>714</v>
+      </c>
+      <c r="I130" t="s">
+        <v>715</v>
+      </c>
+      <c r="J130" t="s">
+        <v>716</v>
+      </c>
+      <c r="K130" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="131" spans="2:11" ht="153" x14ac:dyDescent="0.2">
+      <c r="B131" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="F131" s="56" t="s">
+        <v>709</v>
+      </c>
+      <c r="G131" t="s">
+        <v>705</v>
+      </c>
+      <c r="H131" t="s">
+        <v>718</v>
+      </c>
+      <c r="I131" t="s">
+        <v>719</v>
+      </c>
+      <c r="J131" t="s">
+        <v>720</v>
+      </c>
+      <c r="K131" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="132" spans="2:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="B132" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="G132" t="s">
+        <v>710</v>
+      </c>
+      <c r="H132" t="s">
+        <v>722</v>
+      </c>
+      <c r="I132" t="s">
+        <v>723</v>
+      </c>
+      <c r="J132" t="s">
+        <v>629</v>
+      </c>
+      <c r="K132" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="133" spans="2:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="B133" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="F133" s="56" t="s">
+        <v>730</v>
+      </c>
+      <c r="G133" t="s">
+        <v>726</v>
+      </c>
+      <c r="H133" t="s">
+        <v>746</v>
+      </c>
+      <c r="I133" t="s">
+        <v>747</v>
+      </c>
+      <c r="J133" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="134" spans="2:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="B134" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="F134" s="56" t="s">
+        <v>735</v>
+      </c>
+      <c r="G134" t="s">
+        <v>731</v>
+      </c>
+      <c r="H134" t="s">
+        <v>749</v>
+      </c>
+      <c r="I134" t="s">
+        <v>750</v>
+      </c>
+      <c r="J134" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="135" spans="2:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="B135" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="F135" s="56" t="s">
+        <v>740</v>
+      </c>
+      <c r="G135" t="s">
+        <v>736</v>
+      </c>
+      <c r="H135" t="s">
+        <v>752</v>
+      </c>
+      <c r="I135" t="s">
+        <v>753</v>
+      </c>
+      <c r="J135" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="136" spans="2:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="B136" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="F136" s="56" t="s">
+        <v>745</v>
+      </c>
+      <c r="G136" t="s">
+        <v>741</v>
+      </c>
+      <c r="H136" t="s">
+        <v>659</v>
+      </c>
+      <c r="I136" t="s">
+        <v>755</v>
+      </c>
+      <c r="J136" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="137" spans="2:11" ht="238" x14ac:dyDescent="0.2">
+      <c r="B137" s="23" t="s">
+        <v>629</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="E137" s="56" t="s">
+        <v>782</v>
+      </c>
+      <c r="F137" s="56" t="s">
+        <v>778</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="I137" s="56" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="138" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="B138" s="23"/>
+      <c r="C138" s="23" t="s">
+        <v>768</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="G138" s="57" t="s">
+        <v>783</v>
+      </c>
+      <c r="H138" s="57" t="s">
+        <v>784</v>
+      </c>
+      <c r="I138" s="57" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="139" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B139" s="23"/>
+      <c r="C139" s="23"/>
+      <c r="D139" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="E139" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="G139" s="24" t="s">
+        <v>785</v>
+      </c>
+      <c r="H139" s="24" t="s">
+        <v>669</v>
+      </c>
+      <c r="I139" s="24" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="140" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B140" s="23"/>
+      <c r="C140" s="23"/>
+      <c r="D140" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="G140" s="24" t="s">
+        <v>787</v>
+      </c>
+      <c r="H140" s="24" t="s">
+        <v>788</v>
+      </c>
+      <c r="I140" s="24" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="141" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B141" s="23"/>
+      <c r="C141" s="23"/>
+      <c r="D141" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="G141" s="24" t="s">
+        <v>790</v>
+      </c>
+      <c r="H141" s="24" t="s">
+        <v>791</v>
+      </c>
+      <c r="I141" s="24" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="142" spans="2:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="B142" s="23"/>
+      <c r="C142" s="23" t="s">
+        <v>769</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="G142" s="24" t="s">
+        <v>793</v>
+      </c>
+      <c r="H142" s="24" t="s">
+        <v>794</v>
+      </c>
+      <c r="I142" s="24" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="143" spans="2:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="B143" s="23"/>
+      <c r="C143" s="23"/>
+      <c r="D143" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="144" spans="2:11" ht="51" x14ac:dyDescent="0.2">
+      <c r="B144" s="23"/>
+      <c r="C144" s="23"/>
+      <c r="D144" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="145" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B145" s="23"/>
+      <c r="C145" s="23"/>
+      <c r="D145" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="146" spans="2:7" ht="272" x14ac:dyDescent="0.2">
+      <c r="B146" s="23" t="s">
+        <v>630</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="147" spans="2:7" ht="136" x14ac:dyDescent="0.2">
+      <c r="B147" s="23"/>
+      <c r="C147" s="23" t="s">
+        <v>826</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="148" spans="2:7" ht="255" x14ac:dyDescent="0.2">
+      <c r="B148" s="23"/>
+      <c r="C148" s="23"/>
+      <c r="D148" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="149" spans="2:7" ht="187" x14ac:dyDescent="0.2">
+      <c r="B149" s="23"/>
+      <c r="C149" s="23"/>
+      <c r="D149" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="150" spans="2:7" ht="119" x14ac:dyDescent="0.2">
+      <c r="B150" s="23"/>
+      <c r="C150" s="23"/>
+      <c r="D150" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="151" spans="2:7" ht="187" x14ac:dyDescent="0.2">
+      <c r="B151" s="23"/>
+      <c r="C151" s="23"/>
+      <c r="D151" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="152" spans="2:7" ht="187" x14ac:dyDescent="0.2">
+      <c r="B152" s="23"/>
+      <c r="C152" s="23"/>
+      <c r="D152" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="153" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B153" s="23"/>
+      <c r="C153" s="23" t="s">
+        <v>818</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="154" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B154" s="23"/>
+      <c r="C154" s="23"/>
+      <c r="D154" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="155" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B155" s="23"/>
+      <c r="C155" s="23"/>
+      <c r="D155" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="156" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B156" s="23"/>
+      <c r="C156" s="52" t="s">
+        <v>836</v>
+      </c>
+      <c r="D156" t="s">
+        <v>827</v>
+      </c>
+      <c r="E156" t="s">
+        <v>828</v>
+      </c>
+      <c r="F156" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="157" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B157" s="23"/>
+      <c r="C157" s="52"/>
+      <c r="D157" t="s">
+        <v>830</v>
+      </c>
+      <c r="E157" t="s">
+        <v>831</v>
+      </c>
+      <c r="F157" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="158" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B158" s="23"/>
+      <c r="C158" s="52"/>
+      <c r="D158" t="s">
+        <v>833</v>
+      </c>
+      <c r="E158" t="s">
+        <v>834</v>
+      </c>
+      <c r="F158" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="159" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B159"/>
+      <c r="C159"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="C68:C70"/>
-    <mergeCell ref="C75:C79"/>
-    <mergeCell ref="C80:C82"/>
-    <mergeCell ref="C71:C74"/>
-    <mergeCell ref="B65:B82"/>
-    <mergeCell ref="C46:C55"/>
-    <mergeCell ref="B45:B55"/>
-    <mergeCell ref="C57:C64"/>
-    <mergeCell ref="B56:B64"/>
-    <mergeCell ref="A37:A82"/>
+  <mergeCells count="46">
+    <mergeCell ref="C147:C152"/>
+    <mergeCell ref="C153:C155"/>
+    <mergeCell ref="C156:C158"/>
+    <mergeCell ref="B146:B158"/>
+    <mergeCell ref="C124:C129"/>
+    <mergeCell ref="G124:G129"/>
+    <mergeCell ref="B106:B129"/>
+    <mergeCell ref="C138:C141"/>
+    <mergeCell ref="C142:C145"/>
+    <mergeCell ref="B137:B145"/>
+    <mergeCell ref="C107:C113"/>
+    <mergeCell ref="G107:G113"/>
+    <mergeCell ref="C114:C118"/>
+    <mergeCell ref="G114:G118"/>
+    <mergeCell ref="C119:C122"/>
+    <mergeCell ref="G119:G122"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="C38:C42"/>
+    <mergeCell ref="C43:C48"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C52:C56"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="C91:C93"/>
+    <mergeCell ref="C98:C102"/>
+    <mergeCell ref="C103:C105"/>
+    <mergeCell ref="C94:C97"/>
+    <mergeCell ref="B88:B105"/>
+    <mergeCell ref="C69:C78"/>
+    <mergeCell ref="B68:B78"/>
+    <mergeCell ref="C80:C87"/>
+    <mergeCell ref="B79:B87"/>
+    <mergeCell ref="A60:A105"/>
     <mergeCell ref="C33:C36"/>
     <mergeCell ref="B6:B36"/>
     <mergeCell ref="G6:G36"/>
     <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C38:C44"/>
-    <mergeCell ref="B37:B44"/>
+    <mergeCell ref="C61:C67"/>
+    <mergeCell ref="B60:B67"/>
     <mergeCell ref="C7:C15"/>
+    <mergeCell ref="B37:B59"/>
     <mergeCell ref="C16:C18"/>
     <mergeCell ref="C19:C23"/>
     <mergeCell ref="C24:C26"/>
@@ -6639,7 +12244,7 @@
       <c r="F3" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="34" t="s">
         <v>20</v>
       </c>
     </row>
@@ -6659,7 +12264,7 @@
       <c r="F4" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="34" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6679,7 +12284,7 @@
       <c r="F5" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="34" t="s">
         <v>22</v>
       </c>
     </row>
@@ -6699,7 +12304,7 @@
       <c r="F6" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="34" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6719,7 +12324,7 @@
       <c r="F7" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="34" t="s">
         <v>23</v>
       </c>
     </row>
@@ -6739,7 +12344,7 @@
       <c r="F8" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="34" t="s">
         <v>24</v>
       </c>
     </row>
@@ -6807,7 +12412,7 @@
       <c r="E12" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="F12" s="37" t="s">
         <v>326</v>
       </c>
     </row>

--- a/docs/fastapi_r.xlsx
+++ b/docs/fastapi_r.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olegsemenov/Programming/python-learning/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F348055-2464-E049-80E7-B980A516F573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B471B426-045D-A64C-90B0-270F3C53B3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12260" yWindow="0" windowWidth="16540" windowHeight="18000" xr2:uid="{DB6DF64F-D978-E741-A4F2-3D28923A7931}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{DB6DF64F-D978-E741-A4F2-3D28923A7931}"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
@@ -1335,7 +1335,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C38" authorId="0" shapeId="0" xr:uid="{94096CA2-FB57-9141-AC4E-76279B2DCAAC}">
+    <comment ref="C47" authorId="0" shapeId="0" xr:uid="{94096CA2-FB57-9141-AC4E-76279B2DCAAC}">
       <text>
         <r>
           <rPr>
@@ -1423,7 +1423,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E43" authorId="0" shapeId="0" xr:uid="{7017A811-C0C1-0B4E-8204-5EC8116A2259}">
+    <comment ref="E52" authorId="0" shapeId="0" xr:uid="{7017A811-C0C1-0B4E-8204-5EC8116A2259}">
       <text>
         <r>
           <rPr>
@@ -1479,7 +1479,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{ACF7B46A-3624-C54F-AF52-451AD3C814EF}">
+    <comment ref="E53" authorId="0" shapeId="0" xr:uid="{ACF7B46A-3624-C54F-AF52-451AD3C814EF}">
       <text>
         <r>
           <rPr>
@@ -1556,7 +1556,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{FF7613C8-3E84-504E-BF56-30EAA59D6A90}">
+    <comment ref="E54" authorId="0" shapeId="0" xr:uid="{FF7613C8-3E84-504E-BF56-30EAA59D6A90}">
       <text>
         <r>
           <rPr>
@@ -1612,7 +1612,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E46" authorId="0" shapeId="0" xr:uid="{4F518038-8351-2045-910E-F340D5B0B148}">
+    <comment ref="E55" authorId="0" shapeId="0" xr:uid="{4F518038-8351-2045-910E-F340D5B0B148}">
       <text>
         <r>
           <rPr>
@@ -1699,7 +1699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{ADFB62FC-15C6-1147-9C5D-C88443DDCB68}">
+    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{ADFB62FC-15C6-1147-9C5D-C88443DDCB68}">
       <text>
         <r>
           <rPr>
@@ -1818,7 +1818,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{2A8BEF6E-0974-C64B-A703-1B32723F8274}">
+    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{2A8BEF6E-0974-C64B-A703-1B32723F8274}">
       <text>
         <r>
           <rPr>
@@ -1842,7 +1842,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F50" authorId="0" shapeId="0" xr:uid="{FFDF18D6-A0BA-B741-B2D2-8197211031C9}">
+    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{FFDF18D6-A0BA-B741-B2D2-8197211031C9}">
       <text>
         <r>
           <rPr>
@@ -1886,7 +1886,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G50" authorId="0" shapeId="0" xr:uid="{5BBCE5EB-5DF3-214C-B8F4-189C657130A8}">
+    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{5BBCE5EB-5DF3-214C-B8F4-189C657130A8}">
       <text>
         <r>
           <rPr>
@@ -1930,7 +1930,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{797FFEB0-1BDB-DC45-96C4-3633B4A0E0AF}">
+    <comment ref="E60" authorId="0" shapeId="0" xr:uid="{797FFEB0-1BDB-DC45-96C4-3633B4A0E0AF}">
       <text>
         <r>
           <rPr>
@@ -1975,7 +1975,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{ACB31994-ABD7-724E-8CE3-9C0F81833EE6}">
+    <comment ref="F60" authorId="0" shapeId="0" xr:uid="{ACB31994-ABD7-724E-8CE3-9C0F81833EE6}">
       <text>
         <r>
           <rPr>
@@ -1989,7 +1989,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E53" authorId="0" shapeId="0" xr:uid="{063D4608-F1FB-E64D-A80B-3543EFCB31A1}">
+    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{063D4608-F1FB-E64D-A80B-3543EFCB31A1}">
       <text>
         <r>
           <rPr>
@@ -2117,7 +2117,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F56" authorId="0" shapeId="0" xr:uid="{582A033B-0E38-7644-B973-7F589A7A9A1E}">
+    <comment ref="F65" authorId="0" shapeId="0" xr:uid="{582A033B-0E38-7644-B973-7F589A7A9A1E}">
       <text>
         <r>
           <rPr>
@@ -2207,7 +2207,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F57" authorId="0" shapeId="0" xr:uid="{FEB292ED-75A5-8941-8DE9-FE9C8E82C5C1}">
+    <comment ref="F66" authorId="0" shapeId="0" xr:uid="{FEB292ED-75A5-8941-8DE9-FE9C8E82C5C1}">
       <text>
         <r>
           <rPr>
@@ -2221,7 +2221,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{7A9F1DDD-F5A7-7648-81F8-1FAB3EE4476C}">
+    <comment ref="F67" authorId="0" shapeId="0" xr:uid="{7A9F1DDD-F5A7-7648-81F8-1FAB3EE4476C}">
       <text>
         <r>
           <rPr>
@@ -2235,7 +2235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{D2024832-91A7-EE44-8F61-220DD6EE415C}">
+    <comment ref="F68" authorId="0" shapeId="0" xr:uid="{D2024832-91A7-EE44-8F61-220DD6EE415C}">
       <text>
         <r>
           <rPr>
@@ -2281,7 +2281,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B60" authorId="0" shapeId="0" xr:uid="{52272BEA-EF55-1F42-A915-6124A59280F6}">
+    <comment ref="B69" authorId="0" shapeId="0" xr:uid="{52272BEA-EF55-1F42-A915-6124A59280F6}">
       <text>
         <r>
           <rPr>
@@ -2496,7 +2496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D61" authorId="0" shapeId="0" xr:uid="{6517C201-1D9F-604C-BB43-58D412DE9651}">
+    <comment ref="D70" authorId="0" shapeId="0" xr:uid="{6517C201-1D9F-604C-BB43-58D412DE9651}">
       <text>
         <r>
           <rPr>
@@ -2543,7 +2543,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B68" authorId="0" shapeId="0" xr:uid="{3F9C09F8-6073-9042-BC4B-3EB85A669FF0}">
+    <comment ref="B77" authorId="0" shapeId="0" xr:uid="{3F9C09F8-6073-9042-BC4B-3EB85A669FF0}">
       <text>
         <r>
           <rPr>
@@ -2694,7 +2694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D68" authorId="0" shapeId="0" xr:uid="{529E9708-50AC-6C4D-802E-FB35FCABDD60}">
+    <comment ref="D77" authorId="0" shapeId="0" xr:uid="{529E9708-50AC-6C4D-802E-FB35FCABDD60}">
       <text>
         <r>
           <rPr>
@@ -2971,7 +2971,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G69" authorId="0" shapeId="0" xr:uid="{57DF489B-7F6A-C247-8161-6B5F41C4A2A8}">
+    <comment ref="G78" authorId="0" shapeId="0" xr:uid="{57DF489B-7F6A-C247-8161-6B5F41C4A2A8}">
       <text>
         <r>
           <rPr>
@@ -3653,7 +3653,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B88" authorId="0" shapeId="0" xr:uid="{675AD5D9-5A3C-5142-B786-623C00472942}">
+    <comment ref="B97" authorId="0" shapeId="0" xr:uid="{675AD5D9-5A3C-5142-B786-623C00472942}">
       <text>
         <r>
           <rPr>
@@ -3779,7 +3779,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{4F116D38-60DF-8D41-81E8-4CBFF51643EF}">
+    <comment ref="E115" authorId="0" shapeId="0" xr:uid="{4F116D38-60DF-8D41-81E8-4CBFF51643EF}">
       <text>
         <r>
           <rPr>
@@ -4391,27 +4391,381 @@
         </r>
       </text>
     </comment>
-    <comment ref="B146" authorId="0" shapeId="0" xr:uid="{E36A3629-E2CB-FD4F-8631-B6F8A84CA1AD}">
+    <comment ref="B155" authorId="0" shapeId="0" xr:uid="{E36A3629-E2CB-FD4F-8631-B6F8A84CA1AD}">
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Microsoft Office User:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">
 </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>💡</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Дополнительно
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">FastAPI </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>кэширует зависимости</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> в рамках одного запроса (если </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">use_cache=True).
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Отлично интегрируется с </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Pydantic</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>ORM</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>middleware</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Аналог паттерна </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>IoC / Dependency Injection Container</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>из крупных фреймворков (</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>NestJS, Spring).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F168" authorId="0" shapeId="0" xr:uid="{8D64FDC5-7F5E-5C48-BA68-68A2CF3F78B5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>🔍</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Что происходит:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Security(oauth2_scheme) </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">указывает </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">FastAPI </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">использовать схему </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">OAuth2.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Swagger UI </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">автоматически добавит кнопку </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Authorize</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Токен передаётся в заголовке </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Authorization: Bearer &lt;token&gt;.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Если токен неверный — выбрасывается 401.</t>
         </r>
       </text>
     </comment>
@@ -5167,7 +5521,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="879">
   <si>
     <t>Термин</t>
   </si>
@@ -8116,6 +8470,9 @@
     <t>Depends</t>
   </si>
   <si>
+    <t>Security</t>
+  </si>
+  <si>
     <t>from fastapi import Request</t>
   </si>
   <si>
@@ -8970,12 +9327,161 @@
   <si>
     <t>Сравнение: способы применения</t>
   </si>
+  <si>
+    <t>Security ведёт себя как Depends, но:
+	•	передаёт параметры безопасности в OpenAPI (Swagger UI);
+	•	поддерживает несколько схем аутентификации одновременно;
+	•	автоматически обрабатывает авторизацию (например, токен доступа).</t>
+  </si>
+  <si>
+    <t>from fastapi import Security</t>
+  </si>
+  <si>
+    <t>from fastapi import FastAPI, Security, HTTPException
+from fastapi.security import OAuth2PasswordBearer
+app = FastAPI()
+# Определяем схему авторизации
+oauth2_scheme = OAuth2PasswordBearer(tokenUrl="token")
+@app.get("/users/me")
+def read_current_user(token: str = Security(oauth2_scheme)):
+    if token != "secrettoken123":
+        raise HTTPException(status_code=401, detail="Invalid token")
+    return {"user": "Alice", "token": token}</t>
+  </si>
+  <si>
+    <t>Критерий</t>
+  </si>
+  <si>
+    <t>Предназначение</t>
+  </si>
+  <si>
+    <t>Любые зависимости</t>
+  </si>
+  <si>
+    <t>Только для безопасности</t>
+  </si>
+  <si>
+    <t>OpenAPI-документация</t>
+  </si>
+  <si>
+    <t>Не добавляет схемы авторизации</t>
+  </si>
+  <si>
+    <t>Добавляет</t>
+  </si>
+  <si>
+    <t>Поддержка нескольких схем</t>
+  </si>
+  <si>
+    <t>Нет</t>
+  </si>
+  <si>
+    <t>Да</t>
+  </si>
+  <si>
+    <t>Пример использования</t>
+  </si>
+  <si>
+    <t>Depends(get_db)</t>
+  </si>
+  <si>
+    <t>prefix</t>
+  </si>
+  <si>
+    <t>Общий префикс для всех маршрутов роутера (например, /users).</t>
+  </si>
+  <si>
+    <t>tags</t>
+  </si>
+  <si>
+    <t>List[str]</t>
+  </si>
+  <si>
+    <t>Список тегов для документации OpenAPI.</t>
+  </si>
+  <si>
+    <t>dependencies</t>
+  </si>
+  <si>
+    <t>List[Depends]</t>
+  </si>
+  <si>
+    <t>Зависимости, применяемые ко всем маршрутам роутера.</t>
+  </si>
+  <si>
+    <t>default_response_class</t>
+  </si>
+  <si>
+    <t>Type[Response]</t>
+  </si>
+  <si>
+    <t>Устанавливает класс ответа по умолчанию (например, JSONResponse).</t>
+  </si>
+  <si>
+    <t>Dict[int, Dict]</t>
+  </si>
+  <si>
+    <t>Общие описания ответов (например, {404: {"description": "Not found"}}).</t>
+  </si>
+  <si>
+    <t>route_class</t>
+  </si>
+  <si>
+    <t>Type[APIRoute]</t>
+  </si>
+  <si>
+    <t>Кастомный класс для маршрутов.</t>
+  </si>
+  <si>
+    <t>on_startup</t>
+  </si>
+  <si>
+    <t>List[Callable]</t>
+  </si>
+  <si>
+    <t>Список функций, вызываемых при запуске приложения.</t>
+  </si>
+  <si>
+    <t>on_shutdown</t>
+  </si>
+  <si>
+    <t>Список функций, вызываемых при остановке приложения.</t>
+  </si>
+  <si>
+    <t>include_in_schema</t>
+  </si>
+  <si>
+    <t>Если False, роуты не будут отображаться в Swagger UI.</t>
+  </si>
+  <si>
+    <t>Параметры</t>
+  </si>
+  <si>
+    <t>from fastapi import APIRouter
+router = APIRouter(
+    prefix="/users",
+    tags=["users"],
+    responses={404: {"description": "User not found"}},
+)
+@router.get("/")
+def get_users():
+    return [{"id": 1, "name": "Alice"}]
+@router.get("/{user_id}")
+def get_user(user_id: int):
+    return {"id": user_id, "name": "Alice"}</t>
+  </si>
+  <si>
+    <t>from fastapi import FastAPI
+from users.router import router as users_router
+app = FastAPI()
+app.include_router(users_router)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -9011,12 +9517,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -9104,7 +9604,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -9186,12 +9686,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -9220,6 +9729,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -9337,7 +9847,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -9356,6 +9866,21 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9671,7 +10196,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A0BD9ED-BBA3-C242-AD3C-6BF28F005CA3}">
-  <dimension ref="A2:K159"/>
+  <dimension ref="A2:K168"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="4"/>
@@ -9679,7 +10204,7 @@
     <col min="3" max="3" width="32.5" style="4" customWidth="1"/>
     <col min="4" max="4" width="36.33203125" style="4" customWidth="1"/>
     <col min="5" max="5" width="36.6640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="35.6640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="44.1640625" style="4" customWidth="1"/>
     <col min="7" max="7" width="41.33203125" customWidth="1"/>
     <col min="8" max="9" width="41.33203125" style="4" customWidth="1"/>
     <col min="10" max="10" width="10.83203125" style="4"/>
@@ -9708,2483 +10233,2734 @@
       </c>
     </row>
     <row r="3" spans="2:7" s="2" customFormat="1" ht="221" x14ac:dyDescent="0.2">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="10"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="2:7" s="2" customFormat="1" ht="85" x14ac:dyDescent="0.2">
-      <c r="B4" s="12"/>
-      <c r="C4" s="33" t="s">
+      <c r="B4" s="13"/>
+      <c r="C4" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="34" t="s">
         <v>319</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="G4" s="10"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="2:7" s="2" customFormat="1" ht="221" x14ac:dyDescent="0.2">
-      <c r="B5" s="13"/>
-      <c r="C5" s="33" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="34" t="s">
         <v>322</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="34" t="s">
         <v>323</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="34" t="s">
         <v>324</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="34" t="s">
         <v>325</v>
       </c>
-      <c r="G5" s="10"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="2:7" ht="272" x14ac:dyDescent="0.2">
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="26" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B7" s="31"/>
-      <c r="C7" s="15" t="s">
+      <c r="B7" s="32"/>
+      <c r="C7" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="37" t="s">
         <v>313</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="28"/>
     </row>
     <row r="8" spans="2:7" ht="136" x14ac:dyDescent="0.2">
-      <c r="B8" s="31"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="36" t="s">
+      <c r="B8" s="32"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="37" t="s">
         <v>314</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="28"/>
     </row>
     <row r="9" spans="2:7" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="31"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="36" t="s">
+      <c r="B9" s="32"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="37" t="s">
         <v>311</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="36" t="s">
         <v>307</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="28"/>
     </row>
     <row r="10" spans="2:7" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="31"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="36" t="s">
+      <c r="B10" s="32"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="37" t="s">
         <v>316</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="36" t="s">
         <v>308</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="28"/>
     </row>
     <row r="11" spans="2:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="B11" s="31"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="36" t="s">
+      <c r="B11" s="32"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="36" t="s">
         <v>309</v>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="28"/>
     </row>
     <row r="12" spans="2:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="B12" s="31"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="36" t="s">
+      <c r="B12" s="32"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="37" t="s">
         <v>315</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="F12" s="36" t="s">
         <v>310</v>
       </c>
-      <c r="G12" s="27"/>
+      <c r="G12" s="28"/>
     </row>
     <row r="13" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B13" s="31"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="26" t="s">
+      <c r="B13" s="32"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="G13" s="27"/>
+      <c r="G13" s="28"/>
     </row>
     <row r="14" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B14" s="31"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="26" t="s">
+      <c r="B14" s="32"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="27" t="s">
         <v>539</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="15" t="s">
         <v>540</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="28"/>
     </row>
     <row r="15" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B15" s="31"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="26" t="s">
+      <c r="B15" s="32"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="27" t="s">
         <v>541</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="15" t="s">
         <v>542</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="G15" s="27"/>
+      <c r="G15" s="28"/>
     </row>
     <row r="16" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B16" s="31"/>
-      <c r="C16" s="15" t="s">
+      <c r="B16" s="32"/>
+      <c r="C16" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="G16" s="27"/>
+      <c r="G16" s="28"/>
     </row>
     <row r="17" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B17" s="31"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="14" t="s">
+      <c r="B17" s="32"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="G17" s="27"/>
+      <c r="G17" s="28"/>
     </row>
     <row r="18" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B18" s="31"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="14" t="s">
+      <c r="B18" s="32"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="G18" s="27"/>
+      <c r="G18" s="28"/>
     </row>
     <row r="19" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B19" s="31"/>
-      <c r="C19" s="15" t="s">
+      <c r="B19" s="32"/>
+      <c r="C19" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="G19" s="27"/>
+      <c r="G19" s="28"/>
     </row>
     <row r="20" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B20" s="31"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="14" t="s">
+      <c r="B20" s="32"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="G20" s="27"/>
+      <c r="G20" s="28"/>
     </row>
     <row r="21" spans="2:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="B21" s="31"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="14" t="s">
+      <c r="B21" s="32"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="15" t="s">
         <v>543</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="15" t="s">
         <v>544</v>
       </c>
-      <c r="F21" s="14"/>
-      <c r="G21" s="27"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="28"/>
     </row>
     <row r="22" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B22" s="31"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="14" t="s">
+      <c r="B22" s="32"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="15" t="s">
         <v>545</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="15" t="s">
         <v>546</v>
       </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="27"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="28"/>
     </row>
     <row r="23" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B23" s="31"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="14" t="s">
+      <c r="B23" s="32"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="G23" s="27"/>
+      <c r="G23" s="28"/>
     </row>
     <row r="24" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B24" s="31"/>
-      <c r="C24" s="15" t="s">
+      <c r="B24" s="32"/>
+      <c r="C24" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="47" t="s">
         <v>227</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="47" t="s">
         <v>228</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="47" t="s">
         <v>229</v>
       </c>
-      <c r="G24" s="27"/>
+      <c r="G24" s="28"/>
     </row>
     <row r="25" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B25" s="31"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="14" t="s">
+      <c r="B25" s="32"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="G25" s="27"/>
+      <c r="G25" s="28"/>
     </row>
     <row r="26" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B26" s="31"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="14" t="s">
+      <c r="B26" s="32"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="G26" s="27"/>
+      <c r="G26" s="28"/>
     </row>
     <row r="27" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B27" s="31"/>
-      <c r="C27" s="15" t="s">
+      <c r="B27" s="32"/>
+      <c r="C27" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="G27" s="27"/>
+      <c r="G27" s="28"/>
     </row>
     <row r="28" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B28" s="31"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="14" t="s">
+      <c r="B28" s="32"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="G28" s="27"/>
+      <c r="G28" s="28"/>
     </row>
     <row r="29" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B29" s="31"/>
-      <c r="C29" s="15" t="s">
+      <c r="B29" s="32"/>
+      <c r="C29" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="15" t="s">
         <v>548</v>
       </c>
-      <c r="G29" s="27"/>
+      <c r="G29" s="28"/>
     </row>
     <row r="30" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B30" s="31"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="14" t="s">
+      <c r="B30" s="32"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="15" t="s">
         <v>547</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="28"/>
     </row>
     <row r="31" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B31" s="31"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="14" t="s">
+      <c r="B31" s="32"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="27"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="28"/>
     </row>
     <row r="32" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B32" s="31"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="14" t="s">
+      <c r="B32" s="32"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="27"/>
-    </row>
-    <row r="33" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B33" s="31"/>
-      <c r="C33" s="15" t="s">
+      <c r="F32" s="15"/>
+      <c r="G32" s="28"/>
+    </row>
+    <row r="33" spans="2:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="B33" s="32"/>
+      <c r="C33" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="F33" s="14"/>
-      <c r="G33" s="27"/>
-    </row>
-    <row r="34" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B34" s="31"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="14" t="s">
+      <c r="F33" s="15"/>
+      <c r="G33" s="28"/>
+    </row>
+    <row r="34" spans="2:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="B34" s="32"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="27"/>
-    </row>
-    <row r="35" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B35" s="31"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="14" t="s">
+      <c r="F34" s="15"/>
+      <c r="G34" s="28"/>
+    </row>
+    <row r="35" spans="2:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="B35" s="32"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="F35" s="14"/>
-      <c r="G35" s="27"/>
-    </row>
-    <row r="36" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B36" s="32"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="14" t="s">
+      <c r="F35" s="15"/>
+      <c r="G35" s="28"/>
+    </row>
+    <row r="36" spans="2:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="B36" s="33"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="29"/>
-    </row>
-    <row r="37" spans="2:7" ht="204" x14ac:dyDescent="0.2">
-      <c r="B37" s="30" t="s">
+      <c r="F36" s="15"/>
+      <c r="G36" s="30"/>
+    </row>
+    <row r="37" spans="2:8" ht="204" x14ac:dyDescent="0.2">
+      <c r="B37" s="31" t="s">
         <v>552</v>
       </c>
-      <c r="C37" s="39" t="s">
+      <c r="C37" s="40" t="s">
         <v>555</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="15" t="s">
         <v>553</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="15" t="s">
         <v>554</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="15" t="s">
         <v>556</v>
       </c>
-      <c r="G37" s="44"/>
-    </row>
-    <row r="38" spans="2:7" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="31"/>
-      <c r="C38" s="15" t="s">
+      <c r="G37" s="45"/>
+    </row>
+    <row r="38" spans="2:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="B38" s="32"/>
+      <c r="C38" s="16" t="s">
+        <v>876</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>853</v>
+      </c>
+      <c r="E38" t="s">
+        <v>105</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="G38" s="26" t="s">
+        <v>877</v>
+      </c>
+      <c r="H38" s="63" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="B39" s="32"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="10" t="s">
+        <v>855</v>
+      </c>
+      <c r="E39" t="s">
+        <v>856</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="G39" s="28"/>
+      <c r="H39" s="63"/>
+    </row>
+    <row r="40" spans="2:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="B40" s="32"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="10" t="s">
+        <v>858</v>
+      </c>
+      <c r="E40" t="s">
+        <v>859</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="G40" s="28"/>
+      <c r="H40" s="63"/>
+    </row>
+    <row r="41" spans="2:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="B41" s="32"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="10" t="s">
+        <v>861</v>
+      </c>
+      <c r="E41" t="s">
+        <v>862</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="G41" s="28"/>
+      <c r="H41" s="63"/>
+    </row>
+    <row r="42" spans="2:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="B42" s="32"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="E42" t="s">
+        <v>864</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="G42" s="28"/>
+      <c r="H42" s="63"/>
+    </row>
+    <row r="43" spans="2:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="B43" s="32"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="10" t="s">
+        <v>866</v>
+      </c>
+      <c r="E43" t="s">
+        <v>867</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="G43" s="28"/>
+      <c r="H43" s="63"/>
+    </row>
+    <row r="44" spans="2:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="B44" s="32"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="10" t="s">
+        <v>869</v>
+      </c>
+      <c r="E44" t="s">
+        <v>870</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="G44" s="28"/>
+      <c r="H44" s="63"/>
+    </row>
+    <row r="45" spans="2:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="B45" s="32"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="10" t="s">
+        <v>872</v>
+      </c>
+      <c r="E45" t="s">
+        <v>870</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="G45" s="28"/>
+      <c r="H45" s="63"/>
+    </row>
+    <row r="46" spans="2:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="B46" s="32"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="10" t="s">
+        <v>874</v>
+      </c>
+      <c r="E46" t="s">
+        <v>111</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="G46" s="30"/>
+      <c r="H46" s="63"/>
+    </row>
+    <row r="47" spans="2:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="32"/>
+      <c r="C47" s="16" t="s">
         <v>557</v>
       </c>
-      <c r="D38" s="45" t="s">
+      <c r="D47" s="46" t="s">
         <v>562</v>
       </c>
-      <c r="E38" s="46" t="s">
+      <c r="E47" s="47" t="s">
         <v>563</v>
       </c>
-      <c r="F38" s="46" t="s">
+      <c r="F47" s="47" t="s">
         <v>564</v>
       </c>
-      <c r="G38" s="44"/>
-    </row>
-    <row r="39" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B39" s="31"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="45" t="s">
+      <c r="G47" s="45"/>
+    </row>
+    <row r="48" spans="2:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="B48" s="32"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="46" t="s">
         <v>565</v>
       </c>
-      <c r="E39" s="46" t="s">
+      <c r="E48" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="F39" s="46" t="s">
+      <c r="F48" s="47" t="s">
         <v>566</v>
       </c>
-      <c r="G39" s="44"/>
-    </row>
-    <row r="40" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B40" s="31"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="45" t="s">
+      <c r="G48" s="45"/>
+    </row>
+    <row r="49" spans="2:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="B49" s="32"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="46" t="s">
         <v>567</v>
       </c>
-      <c r="E40" s="46" t="s">
+      <c r="E49" s="47" t="s">
         <v>568</v>
       </c>
-      <c r="F40" s="46" t="s">
+      <c r="F49" s="47" t="s">
         <v>569</v>
       </c>
-      <c r="G40" s="44"/>
-    </row>
-    <row r="41" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B41" s="31"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="45" t="s">
+      <c r="G49" s="45"/>
+    </row>
+    <row r="50" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B50" s="32"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="46" t="s">
         <v>570</v>
       </c>
-      <c r="E41" s="46" t="s">
+      <c r="E50" s="47" t="s">
         <v>571</v>
       </c>
-      <c r="F41" s="46" t="s">
+      <c r="F50" s="47" t="s">
         <v>572</v>
       </c>
-      <c r="G41" s="44"/>
-    </row>
-    <row r="42" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B42" s="31"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="45" t="s">
+      <c r="G50" s="45"/>
+    </row>
+    <row r="51" spans="2:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="B51" s="32"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="46" t="s">
         <v>573</v>
       </c>
-      <c r="E42" s="46" t="s">
+      <c r="E51" s="47" t="s">
         <v>574</v>
       </c>
-      <c r="F42" s="46" t="s">
+      <c r="F51" s="47" t="s">
         <v>575</v>
       </c>
-      <c r="G42" s="44"/>
-    </row>
-    <row r="43" spans="2:7" ht="85" x14ac:dyDescent="0.2">
-      <c r="B43" s="31"/>
-      <c r="C43" s="15" t="s">
+      <c r="G51" s="45"/>
+    </row>
+    <row r="52" spans="2:7" ht="85" x14ac:dyDescent="0.2">
+      <c r="B52" s="32"/>
+      <c r="C52" s="16" t="s">
         <v>558</v>
       </c>
-      <c r="D43" s="48" t="s">
+      <c r="D52" s="49" t="s">
         <v>580</v>
       </c>
-      <c r="E43" s="47" t="s">
+      <c r="E52" s="48" t="s">
         <v>576</v>
       </c>
-      <c r="F43" s="47" t="s">
+      <c r="F52" s="48" t="s">
         <v>577</v>
       </c>
-      <c r="G43" s="44"/>
-    </row>
-    <row r="44" spans="2:7" ht="85" x14ac:dyDescent="0.2">
-      <c r="B44" s="31"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="14" t="s">
+      <c r="G52" s="45"/>
+    </row>
+    <row r="53" spans="2:7" ht="85" x14ac:dyDescent="0.2">
+      <c r="B53" s="32"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="15" t="s">
         <v>581</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E53" s="15" t="s">
         <v>578</v>
       </c>
-      <c r="F44" s="35" t="s">
+      <c r="F53" s="36" t="s">
         <v>579</v>
       </c>
-      <c r="G44" s="44"/>
-    </row>
-    <row r="45" spans="2:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="B45" s="31"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="35" t="s">
+      <c r="G53" s="45"/>
+    </row>
+    <row r="54" spans="2:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="B54" s="32"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="36" t="s">
         <v>582</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E54" s="15" t="s">
         <v>583</v>
       </c>
-      <c r="F45" s="35" t="s">
+      <c r="F54" s="36" t="s">
         <v>584</v>
       </c>
-      <c r="G45" s="44"/>
-    </row>
-    <row r="46" spans="2:7" ht="153" x14ac:dyDescent="0.2">
-      <c r="B46" s="31"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="35" t="s">
+      <c r="G54" s="45"/>
+    </row>
+    <row r="55" spans="2:7" ht="153" x14ac:dyDescent="0.2">
+      <c r="B55" s="32"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="36" t="s">
         <v>585</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E55" s="15" t="s">
         <v>586</v>
       </c>
-      <c r="F46" s="35" t="s">
+      <c r="F55" s="36" t="s">
         <v>587</v>
       </c>
-      <c r="G46" s="44"/>
-    </row>
-    <row r="47" spans="2:7" ht="136" x14ac:dyDescent="0.2">
-      <c r="B47" s="31"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="49" t="s">
+      <c r="G55" s="45"/>
+    </row>
+    <row r="56" spans="2:7" ht="119" x14ac:dyDescent="0.2">
+      <c r="B56" s="32"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="50" t="s">
         <v>588</v>
       </c>
-      <c r="E47" s="46" t="s">
+      <c r="E56" s="47" t="s">
         <v>589</v>
       </c>
-      <c r="F47" s="49" t="s">
+      <c r="F56" s="50" t="s">
         <v>590</v>
       </c>
-      <c r="G47" s="44"/>
-    </row>
-    <row r="48" spans="2:7" ht="119" x14ac:dyDescent="0.2">
-      <c r="B48" s="31"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="14" t="s">
+      <c r="G56" s="45"/>
+    </row>
+    <row r="57" spans="2:7" ht="119" x14ac:dyDescent="0.2">
+      <c r="B57" s="32"/>
+      <c r="C57" s="17"/>
+      <c r="D57" s="15" t="s">
         <v>592</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E57" s="15" t="s">
         <v>591</v>
       </c>
-      <c r="F48" s="35" t="s">
+      <c r="F57" s="36" t="s">
         <v>593</v>
       </c>
-      <c r="G48" s="44"/>
-    </row>
-    <row r="49" spans="1:7" ht="289" x14ac:dyDescent="0.2">
-      <c r="B49" s="31"/>
-      <c r="C49" s="15" t="s">
+      <c r="G57" s="45"/>
+    </row>
+    <row r="58" spans="2:7" ht="289" x14ac:dyDescent="0.2">
+      <c r="B58" s="32"/>
+      <c r="C58" s="16" t="s">
         <v>559</v>
       </c>
-      <c r="D49" s="46" t="s">
+      <c r="D58" s="47" t="s">
         <v>594</v>
       </c>
-      <c r="E49" s="46" t="s">
+      <c r="E58" s="47" t="s">
         <v>595</v>
       </c>
-      <c r="F49" s="46" t="s">
+      <c r="F58" s="47" t="s">
         <v>596</v>
       </c>
-      <c r="G49" s="44"/>
-    </row>
-    <row r="50" spans="1:7" ht="255" x14ac:dyDescent="0.2">
-      <c r="B50" s="31"/>
-      <c r="C50" s="28"/>
-      <c r="D50" s="14" t="s">
+      <c r="G58" s="45"/>
+    </row>
+    <row r="59" spans="2:7" ht="221" x14ac:dyDescent="0.2">
+      <c r="B59" s="32"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="15" t="s">
         <v>597</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="E59" s="15" t="s">
         <v>598</v>
       </c>
-      <c r="F50" s="14" t="s">
+      <c r="F59" s="15" t="s">
         <v>599</v>
       </c>
-      <c r="G50" s="44"/>
-    </row>
-    <row r="51" spans="1:7" ht="170" x14ac:dyDescent="0.2">
-      <c r="B51" s="31"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="14" t="s">
+      <c r="G59" s="45"/>
+    </row>
+    <row r="60" spans="2:7" ht="170" x14ac:dyDescent="0.2">
+      <c r="B60" s="32"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="15" t="s">
         <v>602</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E60" s="15" t="s">
         <v>600</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F60" s="15" t="s">
         <v>601</v>
       </c>
-      <c r="G51" s="44"/>
-    </row>
-    <row r="52" spans="1:7" ht="238" x14ac:dyDescent="0.2">
-      <c r="B52" s="31"/>
-      <c r="C52" s="15" t="s">
+      <c r="G60" s="45"/>
+    </row>
+    <row r="61" spans="2:7" ht="221" x14ac:dyDescent="0.2">
+      <c r="B61" s="32"/>
+      <c r="C61" s="16" t="s">
         <v>560</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D61" s="15" t="s">
         <v>603</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E61" s="15" t="s">
         <v>604</v>
       </c>
-      <c r="F52" s="14" t="s">
+      <c r="F61" s="15" t="s">
         <v>605</v>
       </c>
-      <c r="G52" s="44"/>
-    </row>
-    <row r="53" spans="1:7" ht="119" x14ac:dyDescent="0.2">
-      <c r="B53" s="31"/>
-      <c r="C53" s="28"/>
-      <c r="D53" s="50" t="s">
+      <c r="G61" s="45"/>
+    </row>
+    <row r="62" spans="2:7" ht="119" x14ac:dyDescent="0.2">
+      <c r="B62" s="32"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="51" t="s">
         <v>606</v>
       </c>
-      <c r="E53" s="46" t="s">
+      <c r="E62" s="47" t="s">
         <v>607</v>
       </c>
-      <c r="F53" s="49" t="s">
+      <c r="F62" s="50" t="s">
         <v>608</v>
       </c>
-      <c r="G53" s="44"/>
-    </row>
-    <row r="54" spans="1:7" ht="204" x14ac:dyDescent="0.2">
-      <c r="B54" s="31"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="35" t="s">
+      <c r="G62" s="45"/>
+    </row>
+    <row r="63" spans="2:7" ht="187" x14ac:dyDescent="0.2">
+      <c r="B63" s="32"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="36" t="s">
         <v>609</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E63" s="15" t="s">
         <v>610</v>
       </c>
-      <c r="F54" s="35" t="s">
+      <c r="F63" s="36" t="s">
         <v>611</v>
       </c>
-      <c r="G54" s="44"/>
-    </row>
-    <row r="55" spans="1:7" ht="170" x14ac:dyDescent="0.2">
-      <c r="B55" s="31"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="35" t="s">
+      <c r="G63" s="45"/>
+    </row>
+    <row r="64" spans="2:7" ht="170" x14ac:dyDescent="0.2">
+      <c r="B64" s="32"/>
+      <c r="C64" s="29"/>
+      <c r="D64" s="36" t="s">
         <v>612</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E64" s="15" t="s">
         <v>613</v>
       </c>
-      <c r="F55" s="35" t="s">
+      <c r="F64" s="36" t="s">
         <v>614</v>
       </c>
-      <c r="G55" s="44"/>
-    </row>
-    <row r="56" spans="1:7" ht="272" x14ac:dyDescent="0.2">
-      <c r="B56" s="31"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="14" t="s">
+      <c r="G64" s="45"/>
+    </row>
+    <row r="65" spans="1:7" ht="221" x14ac:dyDescent="0.2">
+      <c r="B65" s="32"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="15" t="s">
         <v>617</v>
       </c>
-      <c r="E56" s="14" t="s">
+      <c r="E65" s="15" t="s">
         <v>615</v>
       </c>
-      <c r="F56" s="35" t="s">
+      <c r="F65" s="36" t="s">
         <v>616</v>
       </c>
-      <c r="G56" s="44"/>
-    </row>
-    <row r="57" spans="1:7" ht="221" x14ac:dyDescent="0.2">
-      <c r="B57" s="31"/>
-      <c r="C57" s="15" t="s">
+      <c r="G65" s="45"/>
+    </row>
+    <row r="66" spans="1:7" ht="204" x14ac:dyDescent="0.2">
+      <c r="B66" s="32"/>
+      <c r="C66" s="16" t="s">
         <v>561</v>
       </c>
-      <c r="D57" s="46" t="s">
+      <c r="D66" s="47" t="s">
         <v>618</v>
       </c>
-      <c r="E57" s="46" t="s">
+      <c r="E66" s="47" t="s">
         <v>619</v>
       </c>
-      <c r="F57" s="49" t="s">
+      <c r="F66" s="50" t="s">
         <v>620</v>
       </c>
-      <c r="G57" s="44"/>
-    </row>
-    <row r="58" spans="1:7" ht="289" x14ac:dyDescent="0.2">
-      <c r="B58" s="31"/>
-      <c r="C58" s="28"/>
-      <c r="D58" s="14" t="s">
+      <c r="G66" s="45"/>
+    </row>
+    <row r="67" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+      <c r="B67" s="32"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="15" t="s">
         <v>621</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="E67" s="15" t="s">
         <v>622</v>
       </c>
-      <c r="F58" s="14" t="s">
+      <c r="F67" s="15" t="s">
         <v>623</v>
       </c>
-      <c r="G58" s="44"/>
-    </row>
-    <row r="59" spans="1:7" ht="272" x14ac:dyDescent="0.2">
-      <c r="B59" s="32"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="14" t="s">
+      <c r="G67" s="45"/>
+    </row>
+    <row r="68" spans="1:7" ht="221" x14ac:dyDescent="0.2">
+      <c r="B68" s="33"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="15" t="s">
         <v>624</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="E68" s="15" t="s">
         <v>625</v>
       </c>
-      <c r="F59" s="14" t="s">
+      <c r="F68" s="15" t="s">
         <v>626</v>
       </c>
-      <c r="G59" s="44"/>
-    </row>
-    <row r="60" spans="1:7" ht="306" x14ac:dyDescent="0.2">
-      <c r="A60" s="40" t="s">
+      <c r="G68" s="45"/>
+    </row>
+    <row r="69" spans="1:7" ht="306" x14ac:dyDescent="0.2">
+      <c r="A69" s="62" t="s">
         <v>391</v>
       </c>
-      <c r="B60" s="18" t="s">
+      <c r="B69" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C69" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D69" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="E69" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="F60" s="17" t="s">
+      <c r="F69" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="G60" s="17" t="s">
+      <c r="G69" s="18" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A61" s="40"/>
-      <c r="B61" s="18"/>
-      <c r="C61" s="40" t="s">
+    <row r="70" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A70" s="62"/>
+      <c r="B70" s="19"/>
+      <c r="C70" s="41" t="s">
         <v>334</v>
       </c>
-      <c r="D61" s="41" t="s">
+      <c r="D70" s="42" t="s">
         <v>335</v>
       </c>
-      <c r="E61" s="17" t="s">
+      <c r="E70" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F61" s="17" t="s">
+      <c r="F70" s="18" t="s">
         <v>336</v>
       </c>
-      <c r="G61" s="17" t="s">
+      <c r="G70" s="18" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A62" s="40"/>
-      <c r="B62" s="18"/>
-      <c r="C62" s="40"/>
-      <c r="D62" s="41" t="s">
+    <row r="71" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A71" s="62"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="41"/>
+      <c r="D71" s="42" t="s">
         <v>338</v>
       </c>
-      <c r="E62" s="17" t="s">
+      <c r="E71" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F62" s="17" t="s">
+      <c r="F71" s="18" t="s">
         <v>339</v>
       </c>
-      <c r="G62" s="17" t="s">
+      <c r="G71" s="18" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A63" s="40"/>
-      <c r="B63" s="18"/>
-      <c r="C63" s="40"/>
-      <c r="D63" s="41" t="s">
+    <row r="72" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A72" s="62"/>
+      <c r="B72" s="19"/>
+      <c r="C72" s="41"/>
+      <c r="D72" s="42" t="s">
         <v>340</v>
       </c>
-      <c r="E63" s="17" t="s">
+      <c r="E72" s="18" t="s">
         <v>341</v>
       </c>
-      <c r="F63" s="17" t="s">
+      <c r="F72" s="18" t="s">
         <v>342</v>
       </c>
-      <c r="G63" s="17" t="s">
+      <c r="G72" s="18" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A64" s="40"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="40"/>
-      <c r="D64" s="41" t="s">
+    <row r="73" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A73" s="62"/>
+      <c r="B73" s="19"/>
+      <c r="C73" s="41"/>
+      <c r="D73" s="42" t="s">
         <v>344</v>
       </c>
-      <c r="E64" s="17" t="s">
+      <c r="E73" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="F64" s="17" t="s">
+      <c r="F73" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="G64" s="17" t="s">
+      <c r="G73" s="18" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A65" s="40"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="40"/>
-      <c r="D65" s="41" t="s">
+    <row r="74" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A74" s="62"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="41"/>
+      <c r="D74" s="42" t="s">
         <v>347</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E74" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="F65" s="17" t="s">
+      <c r="F74" s="18" t="s">
         <v>348</v>
       </c>
-      <c r="G65" s="17" t="s">
+      <c r="G74" s="18" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A66" s="40"/>
-      <c r="B66" s="18"/>
-      <c r="C66" s="40"/>
-      <c r="D66" s="41" t="s">
+    <row r="75" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A75" s="62"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="41"/>
+      <c r="D75" s="42" t="s">
         <v>350</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E75" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="F66" s="17" t="s">
+      <c r="F75" s="18" t="s">
         <v>351</v>
       </c>
-      <c r="G66" s="17" t="s">
+      <c r="G75" s="18" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A67" s="40"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="40"/>
-      <c r="D67" s="41" t="s">
+    <row r="76" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A76" s="62"/>
+      <c r="B76" s="19"/>
+      <c r="C76" s="41"/>
+      <c r="D76" s="42" t="s">
         <v>353</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E76" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="F67" s="17" t="s">
+      <c r="F76" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="G67" s="17" t="s">
+      <c r="G76" s="18" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="40"/>
-      <c r="B68" s="18" t="s">
+    <row r="77" spans="1:7" ht="409" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="62"/>
+      <c r="B77" s="19" t="s">
         <v>359</v>
       </c>
-      <c r="C68" s="17" t="s">
+      <c r="C77" s="18" t="s">
         <v>357</v>
       </c>
-      <c r="D68" s="17" t="s">
+      <c r="D77" s="18" t="s">
         <v>358</v>
       </c>
-      <c r="E68" s="17" t="s">
+      <c r="E77" s="18" t="s">
         <v>360</v>
       </c>
-      <c r="F68" s="17" t="s">
+      <c r="F77" s="18" t="s">
         <v>361</v>
       </c>
-      <c r="G68" s="17" t="s">
+      <c r="G77" s="18" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A69" s="40"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="40" t="s">
+    <row r="78" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A78" s="62"/>
+      <c r="B78" s="19"/>
+      <c r="C78" s="41" t="s">
         <v>390</v>
       </c>
-      <c r="D69" s="41" t="s">
+      <c r="D78" s="42" t="s">
         <v>329</v>
       </c>
-      <c r="E69" s="17" t="s">
+      <c r="E78" s="18" t="s">
         <v>362</v>
       </c>
-      <c r="F69" s="17" t="s">
+      <c r="F78" s="18" t="s">
         <v>363</v>
       </c>
-      <c r="G69" s="42" t="s">
+      <c r="G78" s="43" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A70" s="40"/>
-      <c r="B70" s="18"/>
-      <c r="C70" s="40"/>
-      <c r="D70" s="41" t="s">
+    <row r="79" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A79" s="62"/>
+      <c r="B79" s="19"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="42" t="s">
         <v>364</v>
       </c>
-      <c r="E70" s="17" t="s">
+      <c r="E79" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="F70" s="17" t="s">
+      <c r="F79" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="G70" s="43"/>
-    </row>
-    <row r="71" spans="1:7" ht="102" x14ac:dyDescent="0.2">
-      <c r="A71" s="40"/>
-      <c r="B71" s="18"/>
-      <c r="C71" s="40"/>
-      <c r="D71" s="41" t="s">
+      <c r="G79" s="44"/>
+    </row>
+    <row r="80" spans="1:7" ht="102" x14ac:dyDescent="0.2">
+      <c r="A80" s="62"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="41"/>
+      <c r="D80" s="42" t="s">
         <v>367</v>
       </c>
-      <c r="E71" s="17" t="s">
+      <c r="E80" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="F71" s="17" t="s">
+      <c r="F80" s="18" t="s">
         <v>369</v>
       </c>
-      <c r="G71" s="17" t="s">
+      <c r="G80" s="18" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A72" s="40"/>
-      <c r="B72" s="18"/>
-      <c r="C72" s="40"/>
-      <c r="D72" s="41" t="s">
+    <row r="81" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A81" s="62"/>
+      <c r="B81" s="19"/>
+      <c r="C81" s="41"/>
+      <c r="D81" s="42" t="s">
         <v>370</v>
       </c>
-      <c r="E72" s="17" t="s">
+      <c r="E81" s="18" t="s">
         <v>371</v>
       </c>
-      <c r="F72" s="17" t="s">
+      <c r="F81" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="G72" s="22"/>
-    </row>
-    <row r="73" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A73" s="40"/>
-      <c r="B73" s="18"/>
-      <c r="C73" s="40"/>
-      <c r="D73" s="41" t="s">
+      <c r="G81" s="23"/>
+    </row>
+    <row r="82" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A82" s="62"/>
+      <c r="B82" s="19"/>
+      <c r="C82" s="41"/>
+      <c r="D82" s="42" t="s">
         <v>373</v>
       </c>
-      <c r="E73" s="17" t="s">
+      <c r="E82" s="18" t="s">
         <v>374</v>
       </c>
-      <c r="F73" s="17" t="s">
+      <c r="F82" s="18" t="s">
         <v>375</v>
       </c>
-      <c r="G73" s="22"/>
-    </row>
-    <row r="74" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A74" s="40"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="40"/>
-      <c r="D74" s="41" t="s">
+      <c r="G82" s="23"/>
+    </row>
+    <row r="83" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A83" s="62"/>
+      <c r="B83" s="19"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="42" t="s">
         <v>376</v>
       </c>
-      <c r="E74" s="17" t="s">
+      <c r="E83" s="18" t="s">
         <v>377</v>
       </c>
-      <c r="F74" s="17" t="s">
+      <c r="F83" s="18" t="s">
         <v>378</v>
       </c>
-      <c r="G74" s="22"/>
-    </row>
-    <row r="75" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A75" s="40"/>
-      <c r="B75" s="18"/>
-      <c r="C75" s="40"/>
-      <c r="D75" s="41" t="s">
+      <c r="G83" s="23"/>
+    </row>
+    <row r="84" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A84" s="62"/>
+      <c r="B84" s="19"/>
+      <c r="C84" s="41"/>
+      <c r="D84" s="42" t="s">
         <v>379</v>
       </c>
-      <c r="E75" s="17" t="s">
+      <c r="E84" s="18" t="s">
         <v>380</v>
       </c>
-      <c r="F75" s="17" t="s">
+      <c r="F84" s="18" t="s">
         <v>381</v>
       </c>
-      <c r="G75" s="22"/>
-    </row>
-    <row r="76" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A76" s="40"/>
-      <c r="B76" s="18"/>
-      <c r="C76" s="40"/>
-      <c r="D76" s="41" t="s">
+      <c r="G84" s="23"/>
+    </row>
+    <row r="85" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A85" s="62"/>
+      <c r="B85" s="19"/>
+      <c r="C85" s="41"/>
+      <c r="D85" s="42" t="s">
         <v>382</v>
       </c>
-      <c r="E76" s="17" t="s">
+      <c r="E85" s="18" t="s">
         <v>383</v>
       </c>
-      <c r="F76" s="17" t="s">
+      <c r="F85" s="18" t="s">
         <v>384</v>
       </c>
-      <c r="G76" s="22"/>
-    </row>
-    <row r="77" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A77" s="40"/>
-      <c r="B77" s="18"/>
-      <c r="C77" s="40"/>
-      <c r="D77" s="41" t="s">
+      <c r="G85" s="23"/>
+    </row>
+    <row r="86" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A86" s="62"/>
+      <c r="B86" s="19"/>
+      <c r="C86" s="41"/>
+      <c r="D86" s="42" t="s">
         <v>385</v>
       </c>
-      <c r="E77" s="17" t="s">
+      <c r="E86" s="18" t="s">
         <v>386</v>
       </c>
-      <c r="F77" s="17" t="s">
+      <c r="F86" s="18" t="s">
         <v>387</v>
       </c>
-      <c r="G77" s="22"/>
-    </row>
-    <row r="78" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A78" s="40"/>
-      <c r="B78" s="18"/>
-      <c r="C78" s="40"/>
-      <c r="D78" s="41" t="s">
+      <c r="G86" s="23"/>
+    </row>
+    <row r="87" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A87" s="62"/>
+      <c r="B87" s="19"/>
+      <c r="C87" s="41"/>
+      <c r="D87" s="42" t="s">
         <v>388</v>
       </c>
-      <c r="E78" s="17" t="s">
+      <c r="E87" s="18" t="s">
         <v>389</v>
       </c>
-      <c r="F78" s="17" t="s">
+      <c r="F87" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="G78" s="22"/>
-    </row>
-    <row r="79" spans="1:7" ht="221" x14ac:dyDescent="0.2">
-      <c r="A79" s="40"/>
-      <c r="B79" s="18" t="s">
+      <c r="G87" s="23"/>
+    </row>
+    <row r="88" spans="1:7" ht="221" x14ac:dyDescent="0.2">
+      <c r="A88" s="62"/>
+      <c r="B88" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="C79" s="17" t="s">
+      <c r="C88" s="18" t="s">
         <v>393</v>
       </c>
-      <c r="D79" s="17" t="s">
+      <c r="D88" s="18" t="s">
         <v>394</v>
       </c>
-      <c r="E79" s="17" t="s">
+      <c r="E88" s="18" t="s">
         <v>395</v>
       </c>
-      <c r="F79" s="17" t="s">
+      <c r="F88" s="18" t="s">
         <v>396</v>
       </c>
-      <c r="G79" s="17" t="s">
+      <c r="G88" s="18" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80" s="40"/>
-      <c r="B80" s="18"/>
-      <c r="C80" s="40" t="s">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" s="62"/>
+      <c r="B89" s="19"/>
+      <c r="C89" s="41" t="s">
         <v>495</v>
       </c>
-      <c r="D80" s="22" t="s">
+      <c r="D89" s="23" t="s">
         <v>397</v>
       </c>
-      <c r="E80" s="22">
+      <c r="E89" s="23">
         <v>200</v>
       </c>
-      <c r="F80" s="22" t="s">
+      <c r="F89" s="23" t="s">
         <v>398</v>
       </c>
-      <c r="G80" s="22"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81" s="40"/>
-      <c r="B81" s="18"/>
-      <c r="C81" s="40"/>
-      <c r="D81" s="22" t="s">
+      <c r="G89" s="23"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" s="62"/>
+      <c r="B90" s="19"/>
+      <c r="C90" s="41"/>
+      <c r="D90" s="23" t="s">
         <v>399</v>
       </c>
-      <c r="E81" s="22">
+      <c r="E90" s="23">
         <v>201</v>
       </c>
-      <c r="F81" s="22" t="s">
+      <c r="F90" s="23" t="s">
         <v>400</v>
       </c>
-      <c r="G81" s="22"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A82" s="40"/>
-      <c r="B82" s="18"/>
-      <c r="C82" s="40"/>
-      <c r="D82" s="22" t="s">
+      <c r="G90" s="23"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A91" s="62"/>
+      <c r="B91" s="19"/>
+      <c r="C91" s="41"/>
+      <c r="D91" s="23" t="s">
         <v>401</v>
       </c>
-      <c r="E82" s="22">
+      <c r="E91" s="23">
         <v>204</v>
       </c>
-      <c r="F82" s="22" t="s">
+      <c r="F91" s="23" t="s">
         <v>402</v>
       </c>
-      <c r="G82" s="22"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" s="40"/>
-      <c r="B83" s="18"/>
-      <c r="C83" s="40"/>
-      <c r="D83" s="22" t="s">
+      <c r="G91" s="23"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92" s="62"/>
+      <c r="B92" s="19"/>
+      <c r="C92" s="41"/>
+      <c r="D92" s="23" t="s">
         <v>403</v>
       </c>
-      <c r="E83" s="22">
+      <c r="E92" s="23">
         <v>400</v>
       </c>
-      <c r="F83" s="22" t="s">
+      <c r="F92" s="23" t="s">
         <v>404</v>
       </c>
-      <c r="G83" s="22"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84" s="40"/>
-      <c r="B84" s="18"/>
-      <c r="C84" s="40"/>
-      <c r="D84" s="22" t="s">
+      <c r="G92" s="23"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" s="62"/>
+      <c r="B93" s="19"/>
+      <c r="C93" s="41"/>
+      <c r="D93" s="23" t="s">
         <v>405</v>
       </c>
-      <c r="E84" s="22">
+      <c r="E93" s="23">
         <v>401</v>
       </c>
-      <c r="F84" s="22" t="s">
+      <c r="F93" s="23" t="s">
         <v>406</v>
       </c>
-      <c r="G84" s="22"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" s="40"/>
-      <c r="B85" s="18"/>
-      <c r="C85" s="40"/>
-      <c r="D85" s="22" t="s">
+      <c r="G93" s="23"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94" s="62"/>
+      <c r="B94" s="19"/>
+      <c r="C94" s="41"/>
+      <c r="D94" s="23" t="s">
         <v>407</v>
       </c>
-      <c r="E85" s="22">
+      <c r="E94" s="23">
         <v>403</v>
       </c>
-      <c r="F85" s="22" t="s">
+      <c r="F94" s="23" t="s">
         <v>408</v>
       </c>
-      <c r="G85" s="22"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A86" s="40"/>
-      <c r="B86" s="18"/>
-      <c r="C86" s="40"/>
-      <c r="D86" s="22" t="s">
+      <c r="G94" s="23"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" s="62"/>
+      <c r="B95" s="19"/>
+      <c r="C95" s="41"/>
+      <c r="D95" s="23" t="s">
         <v>409</v>
       </c>
-      <c r="E86" s="22">
+      <c r="E95" s="23">
         <v>404</v>
       </c>
-      <c r="F86" s="22" t="s">
+      <c r="F95" s="23" t="s">
         <v>410</v>
       </c>
-      <c r="G86" s="22"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A87" s="40"/>
-      <c r="B87" s="18"/>
-      <c r="C87" s="40"/>
-      <c r="D87" s="22" t="s">
+      <c r="G95" s="23"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A96" s="62"/>
+      <c r="B96" s="19"/>
+      <c r="C96" s="41"/>
+      <c r="D96" s="23" t="s">
         <v>411</v>
       </c>
-      <c r="E87" s="22">
+      <c r="E96" s="23">
         <v>500</v>
       </c>
-      <c r="F87" s="22" t="s">
+      <c r="F96" s="23" t="s">
         <v>412</v>
       </c>
-      <c r="G87" s="22"/>
-    </row>
-    <row r="88" spans="1:7" ht="340" x14ac:dyDescent="0.2">
-      <c r="A88" s="40"/>
-      <c r="B88" s="18" t="s">
+      <c r="G96" s="23"/>
+    </row>
+    <row r="97" spans="1:7" ht="340" x14ac:dyDescent="0.2">
+      <c r="A97" s="62"/>
+      <c r="B97" s="19" t="s">
         <v>496</v>
       </c>
-      <c r="C88" s="17" t="s">
+      <c r="C97" s="18" t="s">
         <v>538</v>
       </c>
-      <c r="D88" s="17" t="s">
+      <c r="D97" s="18" t="s">
         <v>549</v>
       </c>
-      <c r="E88" s="17" t="s">
+      <c r="E97" s="18" t="s">
         <v>536</v>
       </c>
-      <c r="F88" s="17" t="s">
+      <c r="F97" s="18" t="s">
         <v>537</v>
       </c>
-      <c r="G88" s="22"/>
-    </row>
-    <row r="89" spans="1:7" ht="85" x14ac:dyDescent="0.2">
-      <c r="A89" s="40"/>
-      <c r="B89" s="18"/>
-      <c r="C89" s="40" t="s">
+      <c r="G97" s="23"/>
+    </row>
+    <row r="98" spans="1:7" ht="85" x14ac:dyDescent="0.2">
+      <c r="A98" s="62"/>
+      <c r="B98" s="19"/>
+      <c r="C98" s="41" t="s">
         <v>501</v>
       </c>
-      <c r="D89" s="17" t="s">
+      <c r="D98" s="18" t="s">
         <v>497</v>
       </c>
-      <c r="E89" s="17" t="s">
+      <c r="E98" s="18" t="s">
         <v>498</v>
       </c>
-      <c r="F89" s="17"/>
-      <c r="G89" s="22"/>
-    </row>
-    <row r="90" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A90" s="40"/>
-      <c r="B90" s="18"/>
-      <c r="C90" s="40"/>
-      <c r="D90" s="17" t="s">
+      <c r="F98" s="18"/>
+      <c r="G98" s="23"/>
+    </row>
+    <row r="99" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A99" s="62"/>
+      <c r="B99" s="19"/>
+      <c r="C99" s="41"/>
+      <c r="D99" s="18" t="s">
         <v>499</v>
       </c>
-      <c r="E90" s="17" t="s">
+      <c r="E99" s="18" t="s">
         <v>500</v>
       </c>
-      <c r="F90" s="17"/>
-      <c r="G90" s="22"/>
-    </row>
-    <row r="91" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A91" s="40"/>
-      <c r="B91" s="18"/>
-      <c r="C91" s="40" t="s">
+      <c r="F99" s="18"/>
+      <c r="G99" s="23"/>
+    </row>
+    <row r="100" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A100" s="62"/>
+      <c r="B100" s="19"/>
+      <c r="C100" s="41" t="s">
         <v>502</v>
       </c>
-      <c r="D91" s="17" t="s">
+      <c r="D100" s="18" t="s">
         <v>503</v>
       </c>
-      <c r="E91" s="17" t="s">
+      <c r="E100" s="18" t="s">
         <v>504</v>
       </c>
-      <c r="F91" s="17"/>
-      <c r="G91" s="22"/>
-    </row>
-    <row r="92" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A92" s="40"/>
-      <c r="B92" s="18"/>
-      <c r="C92" s="40"/>
-      <c r="D92" s="17" t="s">
+      <c r="F100" s="18"/>
+      <c r="G100" s="23"/>
+    </row>
+    <row r="101" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A101" s="62"/>
+      <c r="B101" s="19"/>
+      <c r="C101" s="41"/>
+      <c r="D101" s="18" t="s">
         <v>505</v>
       </c>
-      <c r="E92" s="17" t="s">
+      <c r="E101" s="18" t="s">
         <v>506</v>
       </c>
-      <c r="F92" s="17"/>
-      <c r="G92" s="22"/>
-    </row>
-    <row r="93" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A93" s="40"/>
-      <c r="B93" s="18"/>
-      <c r="C93" s="40"/>
-      <c r="D93" s="17" t="s">
+      <c r="F101" s="18"/>
+      <c r="G101" s="23"/>
+    </row>
+    <row r="102" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A102" s="62"/>
+      <c r="B102" s="19"/>
+      <c r="C102" s="41"/>
+      <c r="D102" s="18" t="s">
         <v>507</v>
       </c>
-      <c r="E93" s="17" t="s">
+      <c r="E102" s="18" t="s">
         <v>508</v>
       </c>
-      <c r="F93" s="17"/>
-      <c r="G93" s="22"/>
-    </row>
-    <row r="94" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A94" s="40"/>
-      <c r="B94" s="18"/>
-      <c r="C94" s="40" t="s">
+      <c r="F102" s="18"/>
+      <c r="G102" s="23"/>
+    </row>
+    <row r="103" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A103" s="62"/>
+      <c r="B103" s="19"/>
+      <c r="C103" s="41" t="s">
         <v>509</v>
       </c>
-      <c r="D94" s="17" t="s">
+      <c r="D103" s="18" t="s">
         <v>510</v>
       </c>
-      <c r="E94" s="17" t="s">
+      <c r="E103" s="18" t="s">
         <v>511</v>
       </c>
-      <c r="F94" s="17"/>
-      <c r="G94" s="22"/>
-    </row>
-    <row r="95" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A95" s="40"/>
-      <c r="B95" s="18"/>
-      <c r="C95" s="40"/>
-      <c r="D95" s="17" t="s">
+      <c r="F103" s="18"/>
+      <c r="G103" s="23"/>
+    </row>
+    <row r="104" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A104" s="62"/>
+      <c r="B104" s="19"/>
+      <c r="C104" s="41"/>
+      <c r="D104" s="18" t="s">
         <v>512</v>
       </c>
-      <c r="E95" s="17" t="s">
+      <c r="E104" s="18" t="s">
         <v>513</v>
       </c>
-      <c r="F95" s="17"/>
-      <c r="G95" s="22"/>
-    </row>
-    <row r="96" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A96" s="40"/>
-      <c r="B96" s="18"/>
-      <c r="C96" s="40"/>
-      <c r="D96" s="17" t="s">
+      <c r="F104" s="18"/>
+      <c r="G104" s="23"/>
+    </row>
+    <row r="105" spans="1:7" ht="51" x14ac:dyDescent="0.2">
+      <c r="A105" s="62"/>
+      <c r="B105" s="19"/>
+      <c r="C105" s="41"/>
+      <c r="D105" s="18" t="s">
         <v>514</v>
       </c>
-      <c r="E96" s="17" t="s">
+      <c r="E105" s="18" t="s">
         <v>515</v>
       </c>
-      <c r="F96" s="17"/>
-      <c r="G96" s="22"/>
-    </row>
-    <row r="97" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A97" s="40"/>
-      <c r="B97" s="18"/>
-      <c r="C97" s="40"/>
-      <c r="D97" s="17" t="s">
+      <c r="F105" s="18"/>
+      <c r="G105" s="23"/>
+    </row>
+    <row r="106" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A106" s="62"/>
+      <c r="B106" s="19"/>
+      <c r="C106" s="41"/>
+      <c r="D106" s="18" t="s">
         <v>516</v>
       </c>
-      <c r="E97" s="17" t="s">
+      <c r="E106" s="18" t="s">
         <v>517</v>
       </c>
-      <c r="F97" s="17"/>
-      <c r="G97" s="22"/>
-    </row>
-    <row r="98" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A98" s="40"/>
-      <c r="B98" s="18"/>
-      <c r="C98" s="40" t="s">
+      <c r="F106" s="18"/>
+      <c r="G106" s="23"/>
+    </row>
+    <row r="107" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="A107" s="62"/>
+      <c r="B107" s="19"/>
+      <c r="C107" s="41" t="s">
         <v>518</v>
       </c>
-      <c r="D98" s="17" t="s">
+      <c r="D107" s="18" t="s">
         <v>519</v>
       </c>
-      <c r="E98" s="17" t="s">
+      <c r="E107" s="18" t="s">
         <v>520</v>
       </c>
-      <c r="F98" s="17"/>
-      <c r="G98" s="22"/>
-    </row>
-    <row r="99" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A99" s="40"/>
-      <c r="B99" s="18"/>
-      <c r="C99" s="40"/>
-      <c r="D99" s="17" t="s">
+      <c r="F107" s="18"/>
+      <c r="G107" s="23"/>
+    </row>
+    <row r="108" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A108" s="62"/>
+      <c r="B108" s="19"/>
+      <c r="C108" s="41"/>
+      <c r="D108" s="18" t="s">
         <v>521</v>
       </c>
-      <c r="E99" s="17" t="s">
+      <c r="E108" s="18" t="s">
         <v>522</v>
       </c>
-      <c r="F99" s="17"/>
-      <c r="G99" s="22"/>
-    </row>
-    <row r="100" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A100" s="40"/>
-      <c r="B100" s="18"/>
-      <c r="C100" s="40"/>
-      <c r="D100" s="17" t="s">
+      <c r="F108" s="18"/>
+      <c r="G108" s="23"/>
+    </row>
+    <row r="109" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A109" s="62"/>
+      <c r="B109" s="19"/>
+      <c r="C109" s="41"/>
+      <c r="D109" s="18" t="s">
         <v>523</v>
       </c>
-      <c r="E100" s="17" t="s">
+      <c r="E109" s="18" t="s">
         <v>524</v>
       </c>
-      <c r="F100" s="17"/>
-      <c r="G100" s="22"/>
-    </row>
-    <row r="101" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A101" s="40"/>
-      <c r="B101" s="18"/>
-      <c r="C101" s="40"/>
-      <c r="D101" s="17" t="s">
+      <c r="F109" s="18"/>
+      <c r="G109" s="23"/>
+    </row>
+    <row r="110" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A110" s="62"/>
+      <c r="B110" s="19"/>
+      <c r="C110" s="41"/>
+      <c r="D110" s="18" t="s">
         <v>525</v>
       </c>
-      <c r="E101" s="17" t="s">
+      <c r="E110" s="18" t="s">
         <v>526</v>
       </c>
-      <c r="F101" s="17"/>
-      <c r="G101" s="22"/>
-    </row>
-    <row r="102" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A102" s="40"/>
-      <c r="B102" s="18"/>
-      <c r="C102" s="40"/>
-      <c r="D102" s="17" t="s">
+      <c r="F110" s="18"/>
+      <c r="G110" s="23"/>
+    </row>
+    <row r="111" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A111" s="62"/>
+      <c r="B111" s="19"/>
+      <c r="C111" s="41"/>
+      <c r="D111" s="18" t="s">
         <v>527</v>
       </c>
-      <c r="E102" s="17" t="s">
+      <c r="E111" s="18" t="s">
         <v>528</v>
       </c>
-      <c r="F102" s="17"/>
-      <c r="G102" s="22"/>
-    </row>
-    <row r="103" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A103" s="40"/>
-      <c r="B103" s="18"/>
-      <c r="C103" s="40" t="s">
+      <c r="F111" s="18"/>
+      <c r="G111" s="23"/>
+    </row>
+    <row r="112" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A112" s="62"/>
+      <c r="B112" s="19"/>
+      <c r="C112" s="41" t="s">
         <v>529</v>
       </c>
-      <c r="D103" s="17" t="s">
+      <c r="D112" s="18" t="s">
         <v>530</v>
       </c>
-      <c r="E103" s="17" t="s">
+      <c r="E112" s="18" t="s">
         <v>531</v>
       </c>
-      <c r="F103" s="17"/>
-      <c r="G103" s="22"/>
-    </row>
-    <row r="104" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A104" s="40"/>
-      <c r="B104" s="18"/>
-      <c r="C104" s="40"/>
-      <c r="D104" s="17" t="s">
+      <c r="F112" s="18"/>
+      <c r="G112" s="23"/>
+    </row>
+    <row r="113" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A113" s="62"/>
+      <c r="B113" s="19"/>
+      <c r="C113" s="41"/>
+      <c r="D113" s="18" t="s">
         <v>532</v>
       </c>
-      <c r="E104" s="17" t="s">
+      <c r="E113" s="18" t="s">
         <v>533</v>
       </c>
-      <c r="F104" s="17"/>
-      <c r="G104" s="22"/>
-    </row>
-    <row r="105" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A105" s="40"/>
-      <c r="B105" s="18"/>
-      <c r="C105" s="40"/>
-      <c r="D105" s="17" t="s">
+      <c r="F113" s="18"/>
+      <c r="G113" s="23"/>
+    </row>
+    <row r="114" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A114" s="62"/>
+      <c r="B114" s="19"/>
+      <c r="C114" s="41"/>
+      <c r="D114" s="18" t="s">
         <v>534</v>
       </c>
-      <c r="E105" s="17" t="s">
+      <c r="E114" s="18" t="s">
         <v>535</v>
       </c>
-      <c r="F105" s="17"/>
-      <c r="G105" s="22"/>
-    </row>
-    <row r="106" spans="1:7" ht="272" x14ac:dyDescent="0.2">
-      <c r="A106" s="4" t="s">
+      <c r="F114" s="18"/>
+      <c r="G114" s="23"/>
+    </row>
+    <row r="115" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+      <c r="A115" s="60" t="s">
         <v>627</v>
       </c>
-      <c r="B106" s="38" t="s">
+      <c r="B115" s="39" t="s">
         <v>628</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C115" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="E115" s="52" t="s">
+        <v>635</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="G115" s="57" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A116" s="61"/>
+      <c r="B116" s="24"/>
+      <c r="C116" s="53" t="s">
+        <v>636</v>
+      </c>
+      <c r="D116" t="s">
+        <v>637</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="F116" t="s">
+        <v>639</v>
+      </c>
+      <c r="G116" s="54" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A117" s="61"/>
+      <c r="B117" s="24"/>
+      <c r="C117" s="53"/>
+      <c r="D117" t="s">
+        <v>640</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="F117" t="s">
+        <v>642</v>
+      </c>
+      <c r="G117" s="55"/>
+    </row>
+    <row r="118" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A118" s="61"/>
+      <c r="B118" s="24"/>
+      <c r="C118" s="53"/>
+      <c r="D118" t="s">
+        <v>643</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="F118" t="s">
+        <v>645</v>
+      </c>
+      <c r="G118" s="55"/>
+    </row>
+    <row r="119" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A119" s="61"/>
+      <c r="B119" s="24"/>
+      <c r="C119" s="53"/>
+      <c r="D119" t="s">
+        <v>101</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="F119" t="s">
+        <v>647</v>
+      </c>
+      <c r="G119" s="55"/>
+    </row>
+    <row r="120" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A120" s="61"/>
+      <c r="B120" s="24"/>
+      <c r="C120" s="53"/>
+      <c r="D120" t="s">
+        <v>648</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="F120" t="s">
+        <v>650</v>
+      </c>
+      <c r="G120" s="55"/>
+    </row>
+    <row r="121" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A121" s="61"/>
+      <c r="B121" s="24"/>
+      <c r="C121" s="53"/>
+      <c r="D121" t="s">
+        <v>651</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="F121" t="s">
+        <v>653</v>
+      </c>
+      <c r="G121" s="55"/>
+    </row>
+    <row r="122" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A122" s="61"/>
+      <c r="B122" s="24"/>
+      <c r="C122" s="53"/>
+      <c r="D122" t="s">
+        <v>654</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="F122" t="s">
+        <v>656</v>
+      </c>
+      <c r="G122" s="55"/>
+    </row>
+    <row r="123" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A123" s="61"/>
+      <c r="B123" s="24"/>
+      <c r="C123" s="24" t="s">
+        <v>658</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="G123" s="54" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A124" s="61"/>
+      <c r="B124" s="24"/>
+      <c r="C124" s="24"/>
+      <c r="D124" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="G124" s="55"/>
+    </row>
+    <row r="125" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A125" s="61"/>
+      <c r="B125" s="24"/>
+      <c r="C125" s="24"/>
+      <c r="D125" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="G125" s="55"/>
+    </row>
+    <row r="126" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A126" s="61"/>
+      <c r="B126" s="24"/>
+      <c r="C126" s="24"/>
+      <c r="D126" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="G126" s="55"/>
+    </row>
+    <row r="127" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A127" s="61"/>
+      <c r="B127" s="24"/>
+      <c r="C127" s="24"/>
+      <c r="D127" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="G127" s="55"/>
+    </row>
+    <row r="128" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="61"/>
+      <c r="B128" s="24"/>
+      <c r="C128" s="24" t="s">
+        <v>680</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="G128" s="54" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="61"/>
+      <c r="B129" s="24"/>
+      <c r="C129" s="24"/>
+      <c r="D129" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="G129" s="56"/>
+    </row>
+    <row r="130" spans="1:11" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="61"/>
+      <c r="B130" s="24"/>
+      <c r="C130" s="24"/>
+      <c r="D130" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="G130" s="56"/>
+    </row>
+    <row r="131" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="61"/>
+      <c r="B131" s="24"/>
+      <c r="C131" s="24"/>
+      <c r="D131" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="G131" s="56"/>
+    </row>
+    <row r="132" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="A132" s="61"/>
+      <c r="B132" s="24"/>
+      <c r="C132" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="D132" t="s">
+        <v>683</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="G132" s="57" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A133" s="61"/>
+      <c r="B133" s="24"/>
+      <c r="C133" s="24" t="s">
+        <v>686</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="G133" s="54" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A134" s="61"/>
+      <c r="B134" s="24"/>
+      <c r="C134" s="24"/>
+      <c r="D134" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="G134" s="55"/>
+    </row>
+    <row r="135" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A135" s="61"/>
+      <c r="B135" s="24"/>
+      <c r="C135" s="24"/>
+      <c r="D135" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="G135" s="55"/>
+    </row>
+    <row r="136" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A136" s="61"/>
+      <c r="B136" s="24"/>
+      <c r="C136" s="24"/>
+      <c r="D136" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="G136" s="55"/>
+    </row>
+    <row r="137" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A137" s="61"/>
+      <c r="B137" s="24"/>
+      <c r="C137" s="24"/>
+      <c r="D137" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="G137" s="55"/>
+    </row>
+    <row r="138" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A138" s="61"/>
+      <c r="B138" s="24"/>
+      <c r="C138" s="24"/>
+      <c r="D138" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="G138" s="55"/>
+    </row>
+    <row r="139" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="A139" s="61"/>
+      <c r="B139" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="E139" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="F139" s="57" t="s">
+        <v>705</v>
+      </c>
+      <c r="G139" t="s">
+        <v>701</v>
+      </c>
+      <c r="H139" t="s">
+        <v>715</v>
+      </c>
+      <c r="I139" t="s">
+        <v>716</v>
+      </c>
+      <c r="J139" t="s">
+        <v>717</v>
+      </c>
+      <c r="K139" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="A140" s="61"/>
+      <c r="B140" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="F140" s="57" t="s">
+        <v>710</v>
+      </c>
+      <c r="G140" t="s">
+        <v>706</v>
+      </c>
+      <c r="H140" t="s">
+        <v>719</v>
+      </c>
+      <c r="I140" t="s">
+        <v>720</v>
+      </c>
+      <c r="J140" t="s">
+        <v>721</v>
+      </c>
+      <c r="K140" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="A141" s="61"/>
+      <c r="B141" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="G141" t="s">
+        <v>711</v>
+      </c>
+      <c r="H141" t="s">
+        <v>723</v>
+      </c>
+      <c r="I141" t="s">
+        <v>724</v>
+      </c>
+      <c r="J141" t="s">
+        <v>629</v>
+      </c>
+      <c r="K141" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" ht="187" x14ac:dyDescent="0.2">
+      <c r="A142" s="61"/>
+      <c r="B142" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="F142" s="57" t="s">
+        <v>731</v>
+      </c>
+      <c r="G142" t="s">
+        <v>727</v>
+      </c>
+      <c r="H142" t="s">
+        <v>747</v>
+      </c>
+      <c r="I142" t="s">
+        <v>748</v>
+      </c>
+      <c r="J142" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" ht="136" x14ac:dyDescent="0.2">
+      <c r="A143" s="61"/>
+      <c r="B143" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="F143" s="57" t="s">
+        <v>736</v>
+      </c>
+      <c r="G143" t="s">
+        <v>732</v>
+      </c>
+      <c r="H143" t="s">
+        <v>750</v>
+      </c>
+      <c r="I143" t="s">
+        <v>751</v>
+      </c>
+      <c r="J143" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" ht="102" x14ac:dyDescent="0.2">
+      <c r="A144" s="61"/>
+      <c r="B144" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="F144" s="57" t="s">
+        <v>741</v>
+      </c>
+      <c r="G144" t="s">
+        <v>737</v>
+      </c>
+      <c r="H144" t="s">
+        <v>753</v>
+      </c>
+      <c r="I144" t="s">
+        <v>754</v>
+      </c>
+      <c r="J144" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="A145" s="61"/>
+      <c r="B145" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="F145" s="57" t="s">
+        <v>746</v>
+      </c>
+      <c r="G145" t="s">
+        <v>742</v>
+      </c>
+      <c r="H145" t="s">
+        <v>660</v>
+      </c>
+      <c r="I145" t="s">
+        <v>756</v>
+      </c>
+      <c r="J145" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="238" x14ac:dyDescent="0.2">
+      <c r="A146" s="61"/>
+      <c r="B146" s="24" t="s">
+        <v>629</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="E146" s="57" t="s">
+        <v>783</v>
+      </c>
+      <c r="F146" s="57" t="s">
+        <v>779</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="H146" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="I146" s="57" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A147" s="61"/>
+      <c r="B147" s="24"/>
+      <c r="C147" s="24" t="s">
+        <v>769</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="G147" s="58" t="s">
+        <v>784</v>
+      </c>
+      <c r="H147" s="58" t="s">
+        <v>785</v>
+      </c>
+      <c r="I147" s="58" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A148" s="61"/>
+      <c r="B148" s="24"/>
+      <c r="C148" s="24"/>
+      <c r="D148" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="G148" s="25" t="s">
+        <v>786</v>
+      </c>
+      <c r="H148" s="25" t="s">
+        <v>670</v>
+      </c>
+      <c r="I148" s="25" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A149" s="61"/>
+      <c r="B149" s="24"/>
+      <c r="C149" s="24"/>
+      <c r="D149" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="G149" s="25" t="s">
+        <v>788</v>
+      </c>
+      <c r="H149" s="25" t="s">
+        <v>789</v>
+      </c>
+      <c r="I149" s="25" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A150" s="61"/>
+      <c r="B150" s="24"/>
+      <c r="C150" s="24"/>
+      <c r="D150" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="G150" s="25" t="s">
+        <v>791</v>
+      </c>
+      <c r="H150" s="25" t="s">
+        <v>792</v>
+      </c>
+      <c r="I150" s="25" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A151" s="61"/>
+      <c r="B151" s="24"/>
+      <c r="C151" s="24" t="s">
+        <v>770</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="G151" s="25" t="s">
+        <v>794</v>
+      </c>
+      <c r="H151" s="25" t="s">
+        <v>795</v>
+      </c>
+      <c r="I151" s="25" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A152" s="61"/>
+      <c r="B152" s="24"/>
+      <c r="C152" s="24"/>
+      <c r="D152" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A153" s="61"/>
+      <c r="B153" s="24"/>
+      <c r="C153" s="24"/>
+      <c r="D153" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A154" s="61"/>
+      <c r="B154" s="24"/>
+      <c r="C154" s="24"/>
+      <c r="D154" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="272" x14ac:dyDescent="0.2">
+      <c r="A155" s="61"/>
+      <c r="B155" s="24" t="s">
+        <v>630</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="G155" s="4" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="136" x14ac:dyDescent="0.2">
+      <c r="A156" s="61"/>
+      <c r="B156" s="24"/>
+      <c r="C156" s="24" t="s">
+        <v>827</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="255" x14ac:dyDescent="0.2">
+      <c r="A157" s="61"/>
+      <c r="B157" s="24"/>
+      <c r="C157" s="24"/>
+      <c r="D157" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="187" x14ac:dyDescent="0.2">
+      <c r="A158" s="61"/>
+      <c r="B158" s="24"/>
+      <c r="C158" s="24"/>
+      <c r="D158" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="E158" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A159" s="61"/>
+      <c r="B159" s="24"/>
+      <c r="C159" s="24"/>
+      <c r="D159" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="E159" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="187" x14ac:dyDescent="0.2">
+      <c r="A160" s="61"/>
+      <c r="B160" s="24"/>
+      <c r="C160" s="24"/>
+      <c r="D160" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="E160" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="187" x14ac:dyDescent="0.2">
+      <c r="A161" s="61"/>
+      <c r="B161" s="24"/>
+      <c r="C161" s="24"/>
+      <c r="D161" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="E161" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A162" s="61"/>
+      <c r="B162" s="24"/>
+      <c r="C162" s="24" t="s">
+        <v>819</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="G162" s="58" t="s">
+        <v>841</v>
+      </c>
+      <c r="H162" s="58" t="s">
+        <v>630</v>
+      </c>
+      <c r="I162" s="58" t="s">
         <v>631</v>
       </c>
-      <c r="D106" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="E106" s="51" t="s">
-        <v>634</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="G106" s="56" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B107" s="23"/>
-      <c r="C107" s="52" t="s">
-        <v>635</v>
-      </c>
-      <c r="D107" t="s">
-        <v>636</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="F107" t="s">
-        <v>638</v>
-      </c>
-      <c r="G107" s="53" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B108" s="23"/>
-      <c r="C108" s="52"/>
-      <c r="D108" t="s">
-        <v>639</v>
-      </c>
-      <c r="E108" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="F108" t="s">
-        <v>641</v>
-      </c>
-      <c r="G108" s="54"/>
-    </row>
-    <row r="109" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B109" s="23"/>
-      <c r="C109" s="52"/>
-      <c r="D109" t="s">
-        <v>642</v>
-      </c>
-      <c r="E109" s="4" t="s">
-        <v>643</v>
-      </c>
-      <c r="F109" t="s">
-        <v>644</v>
-      </c>
-      <c r="G109" s="54"/>
-    </row>
-    <row r="110" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B110" s="23"/>
-      <c r="C110" s="52"/>
-      <c r="D110" t="s">
-        <v>101</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>645</v>
-      </c>
-      <c r="F110" t="s">
-        <v>646</v>
-      </c>
-      <c r="G110" s="54"/>
-    </row>
-    <row r="111" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B111" s="23"/>
-      <c r="C111" s="52"/>
-      <c r="D111" t="s">
-        <v>647</v>
-      </c>
-      <c r="E111" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="F111" t="s">
-        <v>649</v>
-      </c>
-      <c r="G111" s="54"/>
-    </row>
-    <row r="112" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B112" s="23"/>
-      <c r="C112" s="52"/>
-      <c r="D112" t="s">
-        <v>650</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="F112" t="s">
-        <v>652</v>
-      </c>
-      <c r="G112" s="54"/>
-    </row>
-    <row r="113" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B113" s="23"/>
-      <c r="C113" s="52"/>
-      <c r="D113" t="s">
-        <v>653</v>
-      </c>
-      <c r="E113" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="F113" t="s">
-        <v>655</v>
-      </c>
-      <c r="G113" s="54"/>
-    </row>
-    <row r="114" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B114" s="23"/>
-      <c r="C114" s="23" t="s">
-        <v>657</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="E114" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="G114" s="53" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="115" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B115" s="23"/>
-      <c r="C115" s="23"/>
-      <c r="D115" s="4" t="s">
-        <v>659</v>
-      </c>
-      <c r="E115" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="G115" s="54"/>
-    </row>
-    <row r="116" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B116" s="23"/>
-      <c r="C116" s="23"/>
-      <c r="D116" s="4" t="s">
-        <v>661</v>
-      </c>
-      <c r="E116" s="4" t="s">
-        <v>662</v>
-      </c>
-      <c r="G116" s="54"/>
-    </row>
-    <row r="117" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B117" s="23"/>
-      <c r="C117" s="23"/>
-      <c r="D117" s="4" t="s">
-        <v>663</v>
-      </c>
-      <c r="E117" s="4" t="s">
-        <v>664</v>
-      </c>
-      <c r="G117" s="54"/>
-    </row>
-    <row r="118" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B118" s="23"/>
-      <c r="C118" s="23"/>
-      <c r="D118" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="E118" s="4" t="s">
-        <v>666</v>
-      </c>
-      <c r="G118" s="54"/>
-    </row>
-    <row r="119" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="23"/>
-      <c r="C119" s="23" t="s">
-        <v>679</v>
-      </c>
-      <c r="D119" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="E119" s="4" t="s">
-        <v>669</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="G119" s="53" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="120" spans="2:7" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="23"/>
-      <c r="C120" s="23"/>
-      <c r="D120" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="E120" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="G120" s="55"/>
-    </row>
-    <row r="121" spans="2:7" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="23"/>
-      <c r="C121" s="23"/>
-      <c r="D121" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="E121" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="G121" s="55"/>
-    </row>
-    <row r="122" spans="2:7" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B122" s="23"/>
-      <c r="C122" s="23"/>
-      <c r="D122" s="4" t="s">
-        <v>676</v>
-      </c>
-      <c r="E122" s="4" t="s">
-        <v>677</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="G122" s="55"/>
-    </row>
-    <row r="123" spans="2:7" ht="136" x14ac:dyDescent="0.2">
-      <c r="B123" s="23"/>
-      <c r="C123" s="4" t="s">
-        <v>681</v>
-      </c>
-      <c r="D123" t="s">
-        <v>682</v>
-      </c>
-      <c r="E123" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="G123" s="56" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="124" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B124" s="23"/>
-      <c r="C124" s="23" t="s">
-        <v>685</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>686</v>
-      </c>
-      <c r="E124" s="4" t="s">
-        <v>687</v>
-      </c>
-      <c r="G124" s="53" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="125" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B125" s="23"/>
-      <c r="C125" s="23"/>
-      <c r="D125" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="E125" s="4" t="s">
-        <v>689</v>
-      </c>
-      <c r="G125" s="54"/>
-    </row>
-    <row r="126" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B126" s="23"/>
-      <c r="C126" s="23"/>
-      <c r="D126" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="E126" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="G126" s="54"/>
-    </row>
-    <row r="127" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B127" s="23"/>
-      <c r="C127" s="23"/>
-      <c r="D127" s="4" t="s">
-        <v>692</v>
-      </c>
-      <c r="E127" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="G127" s="54"/>
-    </row>
-    <row r="128" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B128" s="23"/>
-      <c r="C128" s="23"/>
-      <c r="D128" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="E128" s="4" t="s">
-        <v>695</v>
-      </c>
-      <c r="G128" s="54"/>
-    </row>
-    <row r="129" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B129" s="23"/>
-      <c r="C129" s="23"/>
-      <c r="D129" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="E129" s="4" t="s">
-        <v>697</v>
-      </c>
-      <c r="G129" s="54"/>
-    </row>
-    <row r="130" spans="2:11" ht="187" x14ac:dyDescent="0.2">
-      <c r="B130" s="4" t="s">
-        <v>700</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>701</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>702</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>703</v>
-      </c>
-      <c r="F130" s="56" t="s">
-        <v>704</v>
-      </c>
-      <c r="G130" t="s">
-        <v>700</v>
-      </c>
-      <c r="H130" t="s">
-        <v>714</v>
-      </c>
-      <c r="I130" t="s">
-        <v>715</v>
-      </c>
-      <c r="J130" t="s">
-        <v>716</v>
-      </c>
-      <c r="K130" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="131" spans="2:11" ht="153" x14ac:dyDescent="0.2">
-      <c r="B131" s="4" t="s">
-        <v>705</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>706</v>
-      </c>
-      <c r="D131" s="4" t="s">
-        <v>707</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="F131" s="56" t="s">
-        <v>709</v>
-      </c>
-      <c r="G131" t="s">
-        <v>705</v>
-      </c>
-      <c r="H131" t="s">
-        <v>718</v>
-      </c>
-      <c r="I131" t="s">
-        <v>719</v>
-      </c>
-      <c r="J131" t="s">
-        <v>720</v>
-      </c>
-      <c r="K131" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="132" spans="2:11" ht="136" x14ac:dyDescent="0.2">
-      <c r="B132" s="4" t="s">
-        <v>710</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>711</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="E132" s="4" t="s">
-        <v>713</v>
-      </c>
-      <c r="F132" s="4" t="s">
-        <v>725</v>
-      </c>
-      <c r="G132" t="s">
-        <v>710</v>
-      </c>
-      <c r="H132" t="s">
-        <v>722</v>
-      </c>
-      <c r="I132" t="s">
-        <v>723</v>
-      </c>
-      <c r="J132" t="s">
-        <v>629</v>
-      </c>
-      <c r="K132" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="133" spans="2:11" ht="187" x14ac:dyDescent="0.2">
-      <c r="B133" s="4" t="s">
-        <v>726</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>727</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="E133" s="4" t="s">
-        <v>729</v>
-      </c>
-      <c r="F133" s="56" t="s">
-        <v>730</v>
-      </c>
-      <c r="G133" t="s">
-        <v>726</v>
-      </c>
-      <c r="H133" t="s">
-        <v>746</v>
-      </c>
-      <c r="I133" t="s">
-        <v>747</v>
-      </c>
-      <c r="J133" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="134" spans="2:11" ht="136" x14ac:dyDescent="0.2">
-      <c r="B134" s="4" t="s">
-        <v>731</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>732</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>734</v>
-      </c>
-      <c r="F134" s="56" t="s">
-        <v>735</v>
-      </c>
-      <c r="G134" t="s">
-        <v>731</v>
-      </c>
-      <c r="H134" t="s">
-        <v>749</v>
-      </c>
-      <c r="I134" t="s">
-        <v>750</v>
-      </c>
-      <c r="J134" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="135" spans="2:11" ht="102" x14ac:dyDescent="0.2">
-      <c r="B135" s="4" t="s">
-        <v>736</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>738</v>
-      </c>
-      <c r="E135" s="4" t="s">
-        <v>739</v>
-      </c>
-      <c r="F135" s="56" t="s">
-        <v>740</v>
-      </c>
-      <c r="G135" t="s">
-        <v>736</v>
-      </c>
-      <c r="H135" t="s">
-        <v>752</v>
-      </c>
-      <c r="I135" t="s">
-        <v>753</v>
-      </c>
-      <c r="J135" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="136" spans="2:11" ht="102" x14ac:dyDescent="0.2">
-      <c r="B136" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>742</v>
-      </c>
-      <c r="D136" s="4" t="s">
-        <v>743</v>
-      </c>
-      <c r="E136" s="4" t="s">
-        <v>744</v>
-      </c>
-      <c r="F136" s="56" t="s">
-        <v>745</v>
-      </c>
-      <c r="G136" t="s">
-        <v>741</v>
-      </c>
-      <c r="H136" t="s">
-        <v>659</v>
-      </c>
-      <c r="I136" t="s">
-        <v>755</v>
-      </c>
-      <c r="J136" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="137" spans="2:11" ht="238" x14ac:dyDescent="0.2">
-      <c r="B137" s="23" t="s">
-        <v>629</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>758</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>757</v>
-      </c>
-      <c r="E137" s="56" t="s">
-        <v>782</v>
-      </c>
-      <c r="F137" s="56" t="s">
-        <v>778</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>779</v>
-      </c>
-      <c r="H137" s="4" t="s">
-        <v>780</v>
-      </c>
-      <c r="I137" s="56" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="138" spans="2:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="B138" s="23"/>
-      <c r="C138" s="23" t="s">
-        <v>768</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>759</v>
-      </c>
-      <c r="E138" s="4" t="s">
-        <v>760</v>
-      </c>
-      <c r="F138" s="4" t="s">
-        <v>761</v>
-      </c>
-      <c r="G138" s="57" t="s">
-        <v>783</v>
-      </c>
-      <c r="H138" s="57" t="s">
-        <v>784</v>
-      </c>
-      <c r="I138" s="57" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="139" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B139" s="23"/>
-      <c r="C139" s="23"/>
-      <c r="D139" s="4" t="s">
-        <v>762</v>
-      </c>
-      <c r="E139" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F139" s="4" t="s">
-        <v>763</v>
-      </c>
-      <c r="G139" s="24" t="s">
-        <v>785</v>
-      </c>
-      <c r="H139" s="24" t="s">
-        <v>669</v>
-      </c>
-      <c r="I139" s="24" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="140" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B140" s="23"/>
-      <c r="C140" s="23"/>
-      <c r="D140" s="4" t="s">
-        <v>764</v>
-      </c>
-      <c r="E140" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>765</v>
-      </c>
-      <c r="G140" s="24" t="s">
-        <v>787</v>
-      </c>
-      <c r="H140" s="24" t="s">
-        <v>788</v>
-      </c>
-      <c r="I140" s="24" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="141" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B141" s="23"/>
-      <c r="C141" s="23"/>
-      <c r="D141" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="E141" s="4" t="s">
-        <v>766</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>767</v>
-      </c>
-      <c r="G141" s="24" t="s">
-        <v>790</v>
-      </c>
-      <c r="H141" s="24" t="s">
-        <v>791</v>
-      </c>
-      <c r="I141" s="24" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="142" spans="2:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="B142" s="23"/>
-      <c r="C142" s="23" t="s">
-        <v>769</v>
-      </c>
-      <c r="D142" s="4" t="s">
-        <v>770</v>
-      </c>
-      <c r="E142" s="4" t="s">
-        <v>669</v>
-      </c>
-      <c r="F142" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="G142" s="24" t="s">
-        <v>793</v>
-      </c>
-      <c r="H142" s="24" t="s">
-        <v>794</v>
-      </c>
-      <c r="I142" s="24" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="143" spans="2:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="B143" s="23"/>
-      <c r="C143" s="23"/>
-      <c r="D143" s="4" t="s">
-        <v>772</v>
-      </c>
-      <c r="E143" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F143" s="4" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="144" spans="2:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="B144" s="23"/>
-      <c r="C144" s="23"/>
-      <c r="D144" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="E144" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F144" s="4" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="145" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B145" s="23"/>
-      <c r="C145" s="23"/>
-      <c r="D145" s="4" t="s">
-        <v>776</v>
-      </c>
-      <c r="E145" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F145" s="4" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="146" spans="2:7" ht="272" x14ac:dyDescent="0.2">
-      <c r="B146" s="23" t="s">
-        <v>630</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>796</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>797</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>798</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>799</v>
-      </c>
-      <c r="G146" s="4" t="s">
+    </row>
+    <row r="163" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A163" s="61"/>
+      <c r="B163" s="24"/>
+      <c r="C163" s="24"/>
+      <c r="D163" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="E163" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="G163" s="25" t="s">
+        <v>842</v>
+      </c>
+      <c r="H163" s="25" t="s">
+        <v>843</v>
+      </c>
+      <c r="I163" s="25" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A164" s="61"/>
+      <c r="B164" s="24"/>
+      <c r="C164" s="24"/>
+      <c r="D164" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="E164" s="4" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="147" spans="2:7" ht="136" x14ac:dyDescent="0.2">
-      <c r="B147" s="23"/>
-      <c r="C147" s="23" t="s">
-        <v>826</v>
-      </c>
-      <c r="D147" s="4" t="s">
-        <v>800</v>
-      </c>
-      <c r="E147" s="4" t="s">
-        <v>801</v>
-      </c>
-      <c r="F147" s="4" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="148" spans="2:7" ht="255" x14ac:dyDescent="0.2">
-      <c r="B148" s="23"/>
-      <c r="C148" s="23"/>
-      <c r="D148" s="4" t="s">
-        <v>803</v>
-      </c>
-      <c r="E148" s="4" t="s">
-        <v>804</v>
-      </c>
-      <c r="F148" s="4" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="149" spans="2:7" ht="187" x14ac:dyDescent="0.2">
-      <c r="B149" s="23"/>
-      <c r="C149" s="23"/>
-      <c r="D149" s="4" t="s">
-        <v>806</v>
-      </c>
-      <c r="E149" s="4" t="s">
-        <v>807</v>
-      </c>
-      <c r="F149" s="4" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="150" spans="2:7" ht="119" x14ac:dyDescent="0.2">
-      <c r="B150" s="23"/>
-      <c r="C150" s="23"/>
-      <c r="D150" s="4" t="s">
-        <v>809</v>
-      </c>
-      <c r="E150" s="4" t="s">
-        <v>810</v>
-      </c>
-      <c r="F150" s="4" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="151" spans="2:7" ht="187" x14ac:dyDescent="0.2">
-      <c r="B151" s="23"/>
-      <c r="C151" s="23"/>
-      <c r="D151" s="4" t="s">
-        <v>812</v>
-      </c>
-      <c r="E151" s="4" t="s">
-        <v>813</v>
-      </c>
-      <c r="F151" s="4" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="152" spans="2:7" ht="187" x14ac:dyDescent="0.2">
-      <c r="B152" s="23"/>
-      <c r="C152" s="23"/>
-      <c r="D152" s="4" t="s">
-        <v>815</v>
-      </c>
-      <c r="E152" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="F152" s="4" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="153" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B153" s="23"/>
-      <c r="C153" s="23" t="s">
-        <v>818</v>
-      </c>
-      <c r="D153" s="4" t="s">
-        <v>819</v>
-      </c>
-      <c r="E153" s="4" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="154" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B154" s="23"/>
-      <c r="C154" s="23"/>
-      <c r="D154" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="E154" s="4" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="155" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B155" s="23"/>
-      <c r="C155" s="23"/>
-      <c r="D155" s="4" t="s">
-        <v>823</v>
-      </c>
-      <c r="E155" s="4" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="156" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B156" s="23"/>
-      <c r="C156" s="52" t="s">
+      <c r="G164" s="25" t="s">
+        <v>845</v>
+      </c>
+      <c r="H164" s="25" t="s">
+        <v>846</v>
+      </c>
+      <c r="I164" s="25" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A165" s="61"/>
+      <c r="B165" s="24"/>
+      <c r="C165" s="53" t="s">
+        <v>837</v>
+      </c>
+      <c r="D165" t="s">
+        <v>828</v>
+      </c>
+      <c r="E165" t="s">
+        <v>829</v>
+      </c>
+      <c r="F165" t="s">
+        <v>830</v>
+      </c>
+      <c r="G165" s="25" t="s">
+        <v>848</v>
+      </c>
+      <c r="H165" s="25" t="s">
+        <v>849</v>
+      </c>
+      <c r="I165" s="25" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A166" s="61"/>
+      <c r="B166" s="24"/>
+      <c r="C166" s="53"/>
+      <c r="D166" t="s">
+        <v>831</v>
+      </c>
+      <c r="E166" t="s">
+        <v>832</v>
+      </c>
+      <c r="F166" t="s">
+        <v>833</v>
+      </c>
+      <c r="G166" s="25" t="s">
+        <v>851</v>
+      </c>
+      <c r="H166" s="25" t="s">
+        <v>852</v>
+      </c>
+      <c r="I166" s="25"/>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A167" s="61"/>
+      <c r="B167" s="24"/>
+      <c r="C167" s="53"/>
+      <c r="D167" t="s">
+        <v>834</v>
+      </c>
+      <c r="E167" t="s">
+        <v>835</v>
+      </c>
+      <c r="F167" t="s">
         <v>836</v>
       </c>
-      <c r="D156" t="s">
-        <v>827</v>
-      </c>
-      <c r="E156" t="s">
-        <v>828</v>
-      </c>
-      <c r="F156" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="157" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B157" s="23"/>
-      <c r="C157" s="52"/>
-      <c r="D157" t="s">
-        <v>830</v>
-      </c>
-      <c r="E157" t="s">
-        <v>831</v>
-      </c>
-      <c r="F157" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="158" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B158" s="23"/>
-      <c r="C158" s="52"/>
-      <c r="D158" t="s">
-        <v>833</v>
-      </c>
-      <c r="E158" t="s">
-        <v>834</v>
-      </c>
-      <c r="F158" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="159" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B159"/>
-      <c r="C159"/>
+    </row>
+    <row r="168" spans="1:9" ht="340" x14ac:dyDescent="0.2">
+      <c r="A168" s="61"/>
+      <c r="B168" s="59" t="s">
+        <v>631</v>
+      </c>
+      <c r="C168" t="s">
+        <v>839</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>840</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="46">
-    <mergeCell ref="C147:C152"/>
-    <mergeCell ref="C153:C155"/>
-    <mergeCell ref="C156:C158"/>
-    <mergeCell ref="B146:B158"/>
-    <mergeCell ref="C124:C129"/>
-    <mergeCell ref="G124:G129"/>
-    <mergeCell ref="B106:B129"/>
-    <mergeCell ref="C138:C141"/>
-    <mergeCell ref="C142:C145"/>
-    <mergeCell ref="B137:B145"/>
-    <mergeCell ref="C107:C113"/>
-    <mergeCell ref="G107:G113"/>
-    <mergeCell ref="C114:C118"/>
-    <mergeCell ref="G114:G118"/>
-    <mergeCell ref="C119:C122"/>
-    <mergeCell ref="G119:G122"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="C38:C42"/>
-    <mergeCell ref="C43:C48"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C52:C56"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="C91:C93"/>
-    <mergeCell ref="C98:C102"/>
-    <mergeCell ref="C103:C105"/>
-    <mergeCell ref="C94:C97"/>
-    <mergeCell ref="B88:B105"/>
-    <mergeCell ref="C69:C78"/>
-    <mergeCell ref="B68:B78"/>
-    <mergeCell ref="C80:C87"/>
-    <mergeCell ref="B79:B87"/>
-    <mergeCell ref="A60:A105"/>
+  <mergeCells count="50">
+    <mergeCell ref="H38:H46"/>
+    <mergeCell ref="C156:C161"/>
+    <mergeCell ref="C162:C164"/>
+    <mergeCell ref="C165:C167"/>
+    <mergeCell ref="B155:B167"/>
+    <mergeCell ref="A115:A168"/>
+    <mergeCell ref="C133:C138"/>
+    <mergeCell ref="G133:G138"/>
+    <mergeCell ref="B115:B138"/>
+    <mergeCell ref="C147:C150"/>
+    <mergeCell ref="C151:C154"/>
+    <mergeCell ref="B146:B154"/>
+    <mergeCell ref="C116:C122"/>
+    <mergeCell ref="G116:G122"/>
+    <mergeCell ref="C123:C127"/>
+    <mergeCell ref="G123:G127"/>
+    <mergeCell ref="C128:C131"/>
+    <mergeCell ref="G128:G131"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="C47:C51"/>
+    <mergeCell ref="C52:C57"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="C61:C65"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="C100:C102"/>
+    <mergeCell ref="C107:C111"/>
+    <mergeCell ref="C112:C114"/>
+    <mergeCell ref="C103:C106"/>
+    <mergeCell ref="B97:B114"/>
+    <mergeCell ref="C78:C87"/>
+    <mergeCell ref="B77:B87"/>
+    <mergeCell ref="C89:C96"/>
+    <mergeCell ref="B88:B96"/>
+    <mergeCell ref="A69:A114"/>
     <mergeCell ref="C33:C36"/>
     <mergeCell ref="B6:B36"/>
     <mergeCell ref="G6:G36"/>
     <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C61:C67"/>
-    <mergeCell ref="B60:B67"/>
+    <mergeCell ref="C70:C76"/>
+    <mergeCell ref="B69:B76"/>
     <mergeCell ref="C7:C15"/>
-    <mergeCell ref="B37:B59"/>
+    <mergeCell ref="B37:B68"/>
+    <mergeCell ref="C38:C46"/>
+    <mergeCell ref="G38:G46"/>
     <mergeCell ref="C16:C18"/>
     <mergeCell ref="C19:C23"/>
     <mergeCell ref="C24:C26"/>
@@ -12244,7 +13020,7 @@
       <c r="F3" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="35" t="s">
         <v>20</v>
       </c>
     </row>
@@ -12264,7 +13040,7 @@
       <c r="F4" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="35" t="s">
         <v>21</v>
       </c>
     </row>
@@ -12284,7 +13060,7 @@
       <c r="F5" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="35" t="s">
         <v>22</v>
       </c>
     </row>
@@ -12304,7 +13080,7 @@
       <c r="F6" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="35" t="s">
         <v>10</v>
       </c>
     </row>
@@ -12324,7 +13100,7 @@
       <c r="F7" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="G7" s="34" t="s">
+      <c r="G7" s="35" t="s">
         <v>23</v>
       </c>
     </row>
@@ -12344,7 +13120,7 @@
       <c r="F8" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="G8" s="34" t="s">
+      <c r="G8" s="35" t="s">
         <v>24</v>
       </c>
     </row>
@@ -12412,7 +13188,7 @@
       <c r="E12" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="F12" s="37" t="s">
+      <c r="F12" s="38" t="s">
         <v>326</v>
       </c>
     </row>
@@ -13121,19 +13897,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -13141,962 +13917,962 @@
       </c>
     </row>
     <row r="3" spans="2:7" customFormat="1" ht="204" x14ac:dyDescent="0.2">
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="15" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="4" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B4" s="19"/>
-      <c r="C4" s="19" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="21"/>
+      <c r="G4" s="22"/>
     </row>
     <row r="5" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="14" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="22"/>
     </row>
     <row r="6" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="14" t="s">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="21"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="22"/>
     </row>
     <row r="7" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="14" t="s">
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="21"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="22"/>
     </row>
     <row r="8" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="14" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="21"/>
+      <c r="G8" s="22"/>
     </row>
     <row r="9" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="14" t="s">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="21"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="22"/>
     </row>
     <row r="10" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="14" t="s">
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="21"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="22"/>
     </row>
     <row r="11" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="14" t="s">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="G11" s="21"/>
+      <c r="G11" s="22"/>
     </row>
     <row r="12" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="14" t="s">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="G12" s="21"/>
+      <c r="G12" s="22"/>
     </row>
     <row r="13" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="14" t="s">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="20"/>
-      <c r="G13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="22"/>
     </row>
     <row r="14" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="14" t="s">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="21"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="22"/>
     </row>
     <row r="15" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="14" t="s">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="21"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="22"/>
     </row>
     <row r="16" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="14" t="s">
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="21"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="22"/>
     </row>
     <row r="17" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="14" t="s">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="G17" s="21"/>
+      <c r="G17" s="22"/>
     </row>
     <row r="18" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="14" t="s">
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="21"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="22"/>
     </row>
     <row r="19" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="14" t="s">
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="14"/>
-      <c r="G19" s="21"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="22"/>
     </row>
     <row r="20" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="14" t="s">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="G20" s="21"/>
+      <c r="G20" s="22"/>
     </row>
     <row r="21" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="14" t="s">
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="F21" s="14"/>
-      <c r="G21" s="21"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="22"/>
     </row>
     <row r="22" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="14" t="s">
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="21"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="22"/>
     </row>
     <row r="23" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="14" t="s">
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="14"/>
-      <c r="G23" s="21"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="22"/>
     </row>
     <row r="24" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="14" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="21"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="22"/>
     </row>
     <row r="25" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="14" t="s">
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="21"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="22"/>
     </row>
     <row r="26" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="14" t="s">
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="F26" s="14"/>
-      <c r="G26" s="21"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="22"/>
     </row>
     <row r="27" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="14" t="s">
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="F27" s="14"/>
-      <c r="G27" s="21"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="22"/>
     </row>
     <row r="28" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="14" t="s">
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="F28" s="14"/>
-      <c r="G28" s="21"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="22"/>
     </row>
     <row r="29" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="14" t="s">
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="14"/>
-      <c r="G29" s="21"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="22"/>
     </row>
     <row r="30" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="14" t="s">
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="21"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="22"/>
     </row>
     <row r="31" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="14" t="s">
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="21"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="22"/>
     </row>
     <row r="32" spans="2:7" customFormat="1" ht="306" x14ac:dyDescent="0.2">
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="G32" s="22"/>
+      <c r="G32" s="23"/>
     </row>
     <row r="33" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B33" s="18"/>
-      <c r="C33" s="18" t="s">
+      <c r="B33" s="19"/>
+      <c r="C33" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="G33" s="22"/>
+      <c r="G33" s="23"/>
     </row>
     <row r="34" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="17" t="s">
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F34" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="22"/>
+      <c r="G34" s="23"/>
     </row>
     <row r="35" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="17" t="s">
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="G35" s="22"/>
+      <c r="G35" s="23"/>
     </row>
     <row r="36" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="17" t="s">
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F36" s="17" t="s">
+      <c r="F36" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="G36" s="22"/>
+      <c r="G36" s="23"/>
     </row>
     <row r="37" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="17" t="s">
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="G37" s="22"/>
+      <c r="G37" s="23"/>
     </row>
     <row r="38" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="17" t="s">
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F38" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G38" s="22"/>
+      <c r="G38" s="23"/>
     </row>
     <row r="39" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="17" t="s">
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="G39" s="22"/>
+      <c r="G39" s="23"/>
     </row>
     <row r="40" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="17" t="s">
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F40" s="17" t="s">
+      <c r="F40" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G40" s="22"/>
+      <c r="G40" s="23"/>
     </row>
     <row r="41" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="17" t="s">
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F41" s="17" t="s">
+      <c r="F41" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="G41" s="22"/>
+      <c r="G41" s="23"/>
     </row>
     <row r="42" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="17" t="s">
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="F42" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="G42" s="22"/>
+      <c r="G42" s="23"/>
     </row>
     <row r="43" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="17" t="s">
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F43" s="17" t="s">
+      <c r="F43" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="G43" s="22"/>
+      <c r="G43" s="23"/>
     </row>
     <row r="44" spans="2:7" customFormat="1" ht="388" x14ac:dyDescent="0.2">
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14" t="s">
+      <c r="E44" s="15"/>
+      <c r="F44" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="G44" s="21"/>
+      <c r="G44" s="22"/>
     </row>
     <row r="45" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B45" s="19"/>
-      <c r="C45" s="19" t="s">
+      <c r="B45" s="20"/>
+      <c r="C45" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="F45" s="14"/>
-      <c r="G45" s="21"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="22"/>
     </row>
     <row r="46" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="14" t="s">
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="F46" s="14"/>
-      <c r="G46" s="21"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="22"/>
     </row>
     <row r="47" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="14" t="s">
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="F47" s="14"/>
-      <c r="G47" s="21"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="22"/>
     </row>
     <row r="48" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="14" t="s">
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="F48" s="14"/>
-      <c r="G48" s="21"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="22"/>
     </row>
     <row r="49" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="14" t="s">
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="E49" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="F49" s="14"/>
-      <c r="G49" s="21"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="22"/>
     </row>
     <row r="50" spans="2:7" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="14" t="s">
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="E50" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="F50" s="14"/>
-      <c r="G50" s="21"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="22"/>
     </row>
     <row r="51" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="14" t="s">
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E51" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="F51" s="14"/>
-      <c r="G51" s="21"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="22"/>
     </row>
     <row r="52" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="14" t="s">
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E52" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="F52" s="14"/>
-      <c r="G52" s="21"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="22"/>
     </row>
     <row r="53" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B53" s="19"/>
-      <c r="C53" s="19" t="s">
+      <c r="B53" s="20"/>
+      <c r="C53" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="G53" s="21"/>
+      <c r="G53" s="22"/>
     </row>
     <row r="54" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="14" t="s">
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E54" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="F54" s="14" t="s">
+      <c r="F54" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="G54" s="21"/>
+      <c r="G54" s="22"/>
     </row>
     <row r="55" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="14" t="s">
+      <c r="B55" s="20"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E55" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="F55" s="14" t="s">
+      <c r="F55" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="G55" s="21"/>
+      <c r="G55" s="22"/>
     </row>
     <row r="56" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="14" t="s">
+      <c r="B56" s="20"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="E56" s="14" t="s">
+      <c r="E56" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="14" t="s">
+      <c r="F56" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="G56" s="21"/>
+      <c r="G56" s="22"/>
     </row>
     <row r="57" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="14" t="s">
+      <c r="B57" s="20"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="E57" s="14" t="s">
+      <c r="E57" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="F57" s="14" t="s">
+      <c r="F57" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="G57" s="21"/>
+      <c r="G57" s="22"/>
     </row>
     <row r="58" spans="2:7" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="14" t="s">
+      <c r="B58" s="20"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="E58" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="F58" s="14" t="s">
+      <c r="F58" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="G58" s="21"/>
+      <c r="G58" s="22"/>
     </row>
     <row r="59" spans="2:7" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="14" t="s">
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="E59" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="F59" s="14" t="s">
+      <c r="F59" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="G59" s="21"/>
+      <c r="G59" s="22"/>
     </row>
     <row r="60" spans="2:7" ht="272" x14ac:dyDescent="0.2">
-      <c r="B60" s="18" t="s">
+      <c r="B60" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D60" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="E60" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="F60" s="17" t="s">
+      <c r="F60" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="G60" s="22"/>
+      <c r="G60" s="23"/>
     </row>
     <row r="61" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B61" s="18"/>
-      <c r="C61" s="18" t="s">
+      <c r="B61" s="19"/>
+      <c r="C61" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D61" s="17" t="s">
+      <c r="D61" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="E61" s="17" t="s">
+      <c r="E61" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="F61" s="17" t="s">
+      <c r="F61" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="G61" s="22"/>
+      <c r="G61" s="23"/>
     </row>
     <row r="62" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B62" s="18"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="17" t="s">
+      <c r="B62" s="19"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="E62" s="17" t="s">
+      <c r="E62" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F62" s="17" t="s">
+      <c r="F62" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="G62" s="22"/>
+      <c r="G62" s="23"/>
     </row>
     <row r="63" spans="2:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="17" t="s">
+      <c r="B63" s="19"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E63" s="17" t="s">
+      <c r="E63" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="F63" s="17" t="s">
+      <c r="F63" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="G63" s="22"/>
+      <c r="G63" s="23"/>
     </row>
     <row r="64" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="17" t="s">
+      <c r="B64" s="19"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="E64" s="17" t="s">
+      <c r="E64" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F64" s="17" t="s">
+      <c r="F64" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="G64" s="22"/>
+      <c r="G64" s="23"/>
     </row>
     <row r="65" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="17" t="s">
+      <c r="B65" s="19"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E65" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="F65" s="17" t="s">
+      <c r="F65" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="G65" s="22"/>
+      <c r="G65" s="23"/>
     </row>
     <row r="66" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="17" t="s">
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F66" s="17" t="s">
+      <c r="F66" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G66" s="22"/>
+      <c r="G66" s="23"/>
     </row>
     <row r="67" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B67" s="18"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="17" t="s">
+      <c r="B67" s="19"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E67" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F67" s="17" t="s">
+      <c r="F67" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="G67" s="22"/>
+      <c r="G67" s="23"/>
     </row>
     <row r="68" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="17" t="s">
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="E68" s="17" t="s">
+      <c r="E68" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F68" s="17" t="s">
+      <c r="F68" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="G68" s="22"/>
+      <c r="G68" s="23"/>
     </row>
     <row r="69" spans="2:7" ht="153" x14ac:dyDescent="0.2">
-      <c r="B69" s="19" t="s">
+      <c r="B69" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14" t="s">
+      <c r="C69" s="15"/>
+      <c r="D69" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="E69" s="14" t="s">
+      <c r="E69" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F69" s="14" t="s">
+      <c r="F69" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="G69" s="14" t="s">
+      <c r="G69" s="15" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="70" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B70" s="19"/>
-      <c r="C70" s="20" t="s">
+      <c r="B70" s="20"/>
+      <c r="C70" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="D70" s="14" t="s">
+      <c r="D70" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="E70" s="14" t="s">
+      <c r="E70" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="F70" s="14"/>
-      <c r="G70" s="21"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="22"/>
     </row>
     <row r="71" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B71" s="19"/>
-      <c r="C71" s="20"/>
-      <c r="D71" s="14" t="s">
+      <c r="B71" s="20"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="E71" s="14" t="s">
+      <c r="E71" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="F71" s="14"/>
-      <c r="G71" s="21"/>
+      <c r="F71" s="15"/>
+      <c r="G71" s="22"/>
     </row>
     <row r="72" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B72" s="19"/>
-      <c r="C72" s="20"/>
-      <c r="D72" s="14" t="s">
+      <c r="B72" s="20"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="E72" s="14" t="s">
+      <c r="E72" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="F72" s="14"/>
-      <c r="G72" s="21"/>
+      <c r="F72" s="15"/>
+      <c r="G72" s="22"/>
     </row>
     <row r="73" spans="2:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="B73" s="19"/>
-      <c r="C73" s="20"/>
-      <c r="D73" s="14" t="s">
+      <c r="B73" s="20"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="E73" s="14" t="s">
+      <c r="E73" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="F73" s="14"/>
-      <c r="G73" s="21"/>
+      <c r="F73" s="15"/>
+      <c r="G73" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="13">
